--- a/外网端源码/E楼交接班容量报表空模板.xlsx
+++ b/外网端源码/E楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="491">
   <si>
     <t>班次</t>
   </si>
@@ -3558,27 +3558,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE209"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.7727272727273" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7685185185185" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1090909090909" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1111111111111" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
     <col min="20" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="12.3363636363636" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.3333333333333" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4733,8 +4733,12 @@
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
       <c r="E27" s="29"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="89"/>
+      <c r="F27" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="89" t="s">
+        <v>15</v>
+      </c>
       <c r="H27" s="29"/>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
@@ -4746,8 +4750,12 @@
       <c r="P27" s="29"/>
       <c r="Q27" s="29"/>
       <c r="R27" s="29"/>
-      <c r="S27" s="68"/>
-      <c r="T27" s="68"/>
+      <c r="S27" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="T27" s="68" t="s">
+        <v>15</v>
+      </c>
       <c r="U27" s="29"/>
       <c r="V27" s="29"/>
       <c r="W27" s="29"/>
@@ -5167,15 +5175,11 @@
       <c r="K35" s="99" t="s">
         <v>75</v>
       </c>
-      <c r="L35" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="L35" s="101"/>
       <c r="M35" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="N35" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="N35" s="102"/>
       <c r="O35" s="52"/>
       <c r="P35" s="100" t="s">
         <v>74</v>
@@ -5198,15 +5202,11 @@
       <c r="X35" s="99" t="s">
         <v>75</v>
       </c>
-      <c r="Y35" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="Y35" s="101"/>
       <c r="Z35" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="AA35" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA35" s="101"/>
       <c r="AB35" s="84" t="s">
         <v>108</v>
       </c>
@@ -5246,15 +5246,11 @@
       <c r="K36" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="L36" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="L36" s="101"/>
       <c r="M36" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="N36" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="N36" s="102"/>
       <c r="O36" s="52"/>
       <c r="P36" s="99" t="s">
         <v>78</v>
@@ -5283,15 +5279,11 @@
       <c r="X36" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="Y36" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="Y36" s="101"/>
       <c r="Z36" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="AA36" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA36" s="101"/>
       <c r="AB36" s="84" t="s">
         <v>104</v>
       </c>
@@ -5370,15 +5362,13 @@
       <c r="K38" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="L38" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="L38" s="101"/>
       <c r="M38" s="99" t="s">
         <v>89</v>
       </c>
-      <c r="N38" s="102" t="e">
+      <c r="N38" s="102">
         <f>N35-N36</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="O38" s="52"/>
       <c r="P38" s="99" t="s">
@@ -5406,15 +5396,13 @@
       <c r="X38" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="Y38" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="Y38" s="101"/>
       <c r="Z38" s="99" t="s">
         <v>89</v>
       </c>
-      <c r="AA38" s="101" t="e">
+      <c r="AA38" s="101">
         <f>AA35-AA36</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AB38" s="84" t="s">
         <v>111</v>
@@ -5453,9 +5441,7 @@
       <c r="K39" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="L39" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="L39" s="101"/>
       <c r="M39" s="99" t="s">
         <v>95</v>
       </c>
@@ -5488,15 +5474,11 @@
       <c r="X39" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="Y39" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="Y39" s="101"/>
       <c r="Z39" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="AA39" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA39" s="101"/>
       <c r="AB39" s="84" t="s">
         <v>113</v>
       </c>
@@ -5532,9 +5514,9 @@
       <c r="K40" s="99" t="s">
         <v>100</v>
       </c>
-      <c r="L40" s="101" t="e">
+      <c r="L40" s="101">
         <f>L39-L35</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="M40" s="99" t="s">
         <v>101</v>
@@ -5566,16 +5548,14 @@
       <c r="X40" s="99" t="s">
         <v>100</v>
       </c>
-      <c r="Y40" s="101" t="e">
+      <c r="Y40" s="101">
         <f>Y39-Y35</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="99" t="s">
         <v>101</v>
       </c>
-      <c r="AA40" s="101" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA40" s="101"/>
       <c r="AB40" s="84" t="s">
         <v>115</v>
       </c>
@@ -5635,9 +5615,9 @@
       <c r="Z41" s="99" t="s">
         <v>105</v>
       </c>
-      <c r="AA41" s="101" t="e">
+      <c r="AA41" s="101">
         <f>AA39-AA40</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="76"/>
       <c r="AC41" s="77"/>
@@ -13747,7 +13727,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8dd37d9-0ad5-43ba-9e35-7d0bb24ed270}</x14:id>
+          <x14:id>{4abc857a-f3bf-4bb5-b876-c074c66cb71d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13759,7 +13739,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b0d436f5-3229-4e8e-a7be-071cc8361450}</x14:id>
+          <x14:id>{f3082f20-3107-4d48-87d9-92ccb7e18f3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13771,7 +13751,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be026398-f23f-47f9-a85d-b340982e0178}</x14:id>
+          <x14:id>{794d3c8e-1e94-422a-914e-12359c31eeca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13783,7 +13763,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{029df8e6-0956-4a91-916d-122e5f33b9c3}</x14:id>
+          <x14:id>{565d305c-37ff-4884-a8f7-089865bf4603}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13795,7 +13775,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8701642-e5a1-406e-ab30-8e7cc02d3054}</x14:id>
+          <x14:id>{8e28f837-0e6c-42c9-8593-4336690a5ef0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13807,7 +13787,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26e4c31b-1c51-4349-a562-5d18703bba34}</x14:id>
+          <x14:id>{1bed9b61-fed2-4462-88c5-628e5d3d5ae3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13819,7 +13799,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2c636625-5ee4-48b6-b562-4f7ef85fbce9}</x14:id>
+          <x14:id>{8000e590-2b20-4aac-bb0e-360128f5e292}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13831,7 +13811,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a2d6eea-828a-4650-b51d-2f302d9b1a82}</x14:id>
+          <x14:id>{d931f09f-c9c5-4caf-9885-0fb59803c44c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13845,7 +13825,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1a52e1de-6eb6-4d70-a9d8-60445feed595}</x14:id>
+          <x14:id>{7f88cf40-c017-4f86-9634-03780ae252bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13857,7 +13837,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cdd8209b-80ca-4136-a546-4feee398ccf6}</x14:id>
+          <x14:id>{46089256-1f83-4fb0-8992-d1b61f433b6b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13869,7 +13849,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7c9d5dfe-46d7-44a6-b475-56c7fe0ec83b}</x14:id>
+          <x14:id>{d17bcae5-5ce7-4039-a8e6-3e7d7f09c8bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13881,7 +13861,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0aa2ba4-66a0-48ae-b2fd-816b297697ae}</x14:id>
+          <x14:id>{2a7d5162-8f0e-486b-b9bd-f7bf8247e990}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13893,7 +13873,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5fb1dfb4-d6a7-4d46-bcc8-66d8c0fa52db}</x14:id>
+          <x14:id>{e0aaf361-555c-4d51-af5b-50634c6520db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13905,7 +13885,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f3ab93f-1540-436e-a3b5-73313e4187ab}</x14:id>
+          <x14:id>{822ab420-08ae-4916-8e9d-152d8328d5d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13917,7 +13897,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b904468-8224-4e3e-8598-90264cecb5ce}</x14:id>
+          <x14:id>{17eec315-2861-4b7e-b6b1-054062c9732f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13929,7 +13909,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3e298ad2-4e9e-4051-b80d-b7396a240037}</x14:id>
+          <x14:id>{7a0ae7c0-1022-4b29-a045-79e6ffe92c79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13943,7 +13923,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9aa3e44d-8053-4c56-868c-7f597fb234af}</x14:id>
+          <x14:id>{58cf2775-a060-48fc-9db2-753d97ea2413}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13955,7 +13935,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82900eb9-f94f-4a18-b6c2-8bcbc616ae4a}</x14:id>
+          <x14:id>{314fd1cb-e606-4277-8b1d-f638537ad927}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13967,7 +13947,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9bf4d7b7-3db2-4cd9-be29-3d856e10f757}</x14:id>
+          <x14:id>{41138edf-89c2-4545-8d9b-70a5b1ccd9c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13979,7 +13959,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7420a9d9-0f7c-44c3-8a61-0e3e5577ad3e}</x14:id>
+          <x14:id>{f37a751e-3f14-4e2a-8153-9f47d2395dc6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13991,7 +13971,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{303ca555-4201-42ed-9633-c7949e4d9294}</x14:id>
+          <x14:id>{40925116-b1d4-4ccd-8f76-aa2b5d609f84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14003,7 +13983,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eae7986d-503c-44a8-9171-bc3561b17299}</x14:id>
+          <x14:id>{609ee51d-a8a3-4f81-b972-bf577a3905af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14015,7 +13995,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42c6def2-d975-4e92-87ce-58609debe97c}</x14:id>
+          <x14:id>{730b6fb1-05a3-4526-91e0-5691aa59df6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14027,7 +14007,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20287a30-46b1-40f1-9081-a6c2a093b1a8}</x14:id>
+          <x14:id>{ef778a46-f4d2-442e-9796-8af926003073}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14041,7 +14021,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3202fa0b-f4ed-4171-b289-aec41fe50532}</x14:id>
+          <x14:id>{df0806ca-0efd-4d65-ba61-4f2cd965328e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14053,7 +14033,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{745b3fb3-b2da-495d-8f07-be9b757cf5fd}</x14:id>
+          <x14:id>{382589a2-5803-4a98-878c-85c7fc855e83}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14065,7 +14045,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e30146e-5cd1-493f-b54e-4e08fbae3eea}</x14:id>
+          <x14:id>{41102eee-0152-4ae8-8262-bb92b79d974e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14077,7 +14057,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aed28516-5b29-4e25-9c92-b3f9b3bc1f6b}</x14:id>
+          <x14:id>{d9e81d60-8b8c-46cf-8ebc-67f946e21547}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14089,7 +14069,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26e679be-149b-402d-934e-64533685dfe4}</x14:id>
+          <x14:id>{b77fc6c1-6f6f-40e9-9544-5255edee1417}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14101,7 +14081,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee212af3-5807-4713-9975-eb8868d806a7}</x14:id>
+          <x14:id>{19aaf16a-b545-42dc-84d7-dbffdbff822a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14113,7 +14093,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{35e391e1-ccb4-4956-9cfc-d631ef73bd00}</x14:id>
+          <x14:id>{190f1ffc-18db-4ed5-85b5-971fcdd80303}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14125,7 +14105,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6913ae6d-44f5-4cc4-842d-9c19918c096f}</x14:id>
+          <x14:id>{8655b60e-ed92-4e34-b696-3630538cc71c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14139,7 +14119,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1d0afa0a-fca3-4488-a9d4-785e71508049}</x14:id>
+          <x14:id>{749cf70d-83ae-4096-b4bc-c283cb76dd30}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14151,7 +14131,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f75b6ff3-9860-47e5-9d28-080d2b90a20a}</x14:id>
+          <x14:id>{e2a68314-628a-4de0-82a2-035956d400ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14163,7 +14143,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ef951a1-581d-459a-b5fc-c25d83f517de}</x14:id>
+          <x14:id>{59462c06-3612-4981-9782-d0b271f6c7f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14175,7 +14155,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2c4edd3-dcf1-4010-9994-04ae989354c0}</x14:id>
+          <x14:id>{771037c7-7f35-4e58-88ae-79f624de6a5a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14187,7 +14167,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06794649-bf22-42bd-922a-f8a03aefec74}</x14:id>
+          <x14:id>{609260af-2620-4488-8f97-adae49ad2338}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14199,7 +14179,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba91d3f2-b574-41df-98db-389b1a4aa89e}</x14:id>
+          <x14:id>{b24643f1-127c-461f-909b-1780ef2b02cb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14211,7 +14191,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7acf6793-72e5-4515-9d50-406fab175039}</x14:id>
+          <x14:id>{b49b4d19-7f23-454f-b293-7c27a4ad4d93}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14223,7 +14203,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4bd42acc-397b-4f0e-9235-9dab75ccde1b}</x14:id>
+          <x14:id>{1260ad13-0cc2-45ec-97b0-7101936371e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14237,7 +14217,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61983b95-1bc7-45bf-a7e1-0d77a4be1697}</x14:id>
+          <x14:id>{6ec52697-66e8-48e6-9911-504c70e0c0e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14249,7 +14229,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2256cc2f-038c-4121-8614-58c08f36139a}</x14:id>
+          <x14:id>{ec084eff-f02a-476d-8b08-ef58948a0628}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14261,7 +14241,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ccfacc4-2e98-4aeb-a8f9-d2e87436df17}</x14:id>
+          <x14:id>{e4d227df-c65f-47f8-a781-8c43c5ce6358}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14273,7 +14253,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e9f8857-0abc-4084-af13-fcec883be745}</x14:id>
+          <x14:id>{ca5a4b4d-03a7-42b4-9978-4732f60d0f7e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14285,7 +14265,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d0bf7fc-46d4-4127-a1c2-289fae48076c}</x14:id>
+          <x14:id>{37a1ee8d-33e6-4e86-9727-fea308272140}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14297,7 +14277,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{561b35bf-f1ac-4a7d-bca2-203b680b519d}</x14:id>
+          <x14:id>{32132eab-564e-4dc5-9dc9-296c5a1e6e03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14309,7 +14289,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{900016d7-d64c-4f8e-bda0-7d9f370628b1}</x14:id>
+          <x14:id>{2aa4c89d-c345-4841-a983-1e699c6fd3d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14321,7 +14301,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7c9ef0f-bf41-4dfb-b749-c2f229d5b122}</x14:id>
+          <x14:id>{59473855-7026-49b9-8cf2-8ca5958fe56e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14335,7 +14315,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{613aa387-d0b6-45cb-b3cd-1d9d32ddfd5d}</x14:id>
+          <x14:id>{4c0be875-1e73-41e6-b89c-fc3ab882a13c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14347,7 +14327,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16c7c2d2-7e07-4860-aa0f-0efd88aa3683}</x14:id>
+          <x14:id>{136cea1d-8874-4769-b407-4ec92c7f4298}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14359,7 +14339,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53d60f3b-8c98-4283-bb23-3603259cc149}</x14:id>
+          <x14:id>{32179bf7-df89-49bc-ab50-83ecb6db1246}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14371,7 +14351,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f104416-c5d5-47bc-ad2f-bf622e99b789}</x14:id>
+          <x14:id>{5d7029e5-d451-40d8-b0c9-9c64787e70b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14383,7 +14363,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2beb57a7-a286-4c26-bfeb-66e8108b93c6}</x14:id>
+          <x14:id>{d11fd8e3-3ac4-4c3f-9be9-243a57f940c9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14395,7 +14375,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d54625bc-01b6-4e8f-862e-9be617c7b7ab}</x14:id>
+          <x14:id>{11e5f813-9422-43ab-a14b-a02653526773}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14407,7 +14387,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f89376e1-71a2-45df-b009-60b6b96f1f50}</x14:id>
+          <x14:id>{b79cb2b0-13ca-4f04-a313-d7d2e5a1671b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14419,7 +14399,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e1c1f213-9562-492f-849e-236a6fbd0afe}</x14:id>
+          <x14:id>{6bceec41-c76e-4db6-bef2-3bc769d46356}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14433,7 +14413,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd660bf2-c44c-4355-8b61-67fd74d67f4d}</x14:id>
+          <x14:id>{04e038ae-c0ee-4e04-9a0e-39e20d5f6a1b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14447,7 +14427,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d7b01846-ff5f-481e-94e6-fb0a080b2058}</x14:id>
+          <x14:id>{365ee957-22b9-42f6-be9f-f189169ee293}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14461,7 +14441,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00eb0ea0-78b5-4e5d-b53c-76495df8839b}</x14:id>
+          <x14:id>{cff02d77-6319-4dc6-9737-f7c66112b72f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14475,7 +14455,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6550637d-847b-4599-9131-1762b5cb3de1}</x14:id>
+          <x14:id>{4a06f551-b2e5-44e2-9534-a0768889a54e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14487,7 +14467,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8427225c-5b24-4584-bfd1-e11d4fccbedd}</x14:id>
+          <x14:id>{f56dda1d-eb16-420c-ac58-f42f44d60dcd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14499,7 +14479,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9654132b-b282-4a5b-a230-f7208da4e900}</x14:id>
+          <x14:id>{9d7f1b94-0f9f-4a43-a6d5-70bf32b66362}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14511,7 +14491,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{933bdeb4-44f9-44cf-ab09-b6005fc7e759}</x14:id>
+          <x14:id>{a2be7812-ea70-4f60-9ebe-d3a364abac1f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14523,7 +14503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a53b751-6b45-49a0-9e96-936c8e27db7e}</x14:id>
+          <x14:id>{3bcc6139-b457-4c12-a0bb-7af355907714}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14535,7 +14515,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4106a878-16bf-48eb-8b3b-0972440acf08}</x14:id>
+          <x14:id>{b13bd9c4-33a6-475d-9bcd-b5d3170a5d4c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14547,7 +14527,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb538c8a-81d7-4e6a-b8ad-bc38c7f210b0}</x14:id>
+          <x14:id>{ab0bdae3-ce79-4745-9258-97593fca2686}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14559,7 +14539,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d8862f3-0d74-4922-bb60-d1d261292f08}</x14:id>
+          <x14:id>{b1f24c4d-7c91-4ff5-9c5c-023b708e98ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14573,7 +14553,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1c19f651-ee91-4534-98cb-c3b3b089846e}</x14:id>
+          <x14:id>{58e115bf-bf42-48f0-bc4b-6a4df89d2896}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14585,7 +14565,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d636ca4-5be8-423d-b0b9-435b8e2c8b3a}</x14:id>
+          <x14:id>{bf2f1cbd-3698-4819-aa76-e0ef253636de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14599,7 +14579,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1720642c-3530-4294-b7a2-ef11d2537329}</x14:id>
+          <x14:id>{fafae96f-fb93-4211-a18e-39993e71a479}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14613,7 +14593,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c64afc50-7e6a-4843-84c9-f4849e154217}</x14:id>
+          <x14:id>{1a7c387e-1a12-4252-a27f-09a1fd4a94be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14625,7 +14605,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03801493-5bcb-47a5-bddc-85d8a7a74842}</x14:id>
+          <x14:id>{0f61c689-be11-497d-9b82-09cbaf3755c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14639,7 +14619,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e051b41-a042-40ef-a400-0d4fddd228d2}</x14:id>
+          <x14:id>{47a8839f-0892-4e3a-81e2-941c53e6faad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14651,7 +14631,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e684fbb5-17d2-4457-a3ae-6558557579ab}</x14:id>
+          <x14:id>{8fc4e5e6-a3f4-4ea9-8b2c-dc4c443e4516}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14665,7 +14645,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42403239-53de-48af-a42d-aa64ebacf436}</x14:id>
+          <x14:id>{f88cb0fb-32dd-43c1-b822-d6413f71308a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14679,7 +14659,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{742bfa9f-9d44-43dd-b116-ed385c276ca6}</x14:id>
+          <x14:id>{cddf6781-0c70-4cbf-84da-74de37731050}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14691,7 +14671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4996df7b-5f2d-4074-8b41-77825d0712d0}</x14:id>
+          <x14:id>{1728703a-1893-413a-8f6a-cf63c41d1feb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14705,7 +14685,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d9a26976-b2ba-49d8-8b04-d1fcac6ff96b}</x14:id>
+          <x14:id>{2c8cade6-5bc5-4824-a56c-3e84b2ea88cb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14719,7 +14699,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{48c576ba-f0fd-4b5c-b49d-b2c3f93b50e3}</x14:id>
+          <x14:id>{b990cf4c-3ab1-4fcd-a8cc-f125cf1733c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14731,7 +14711,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6938760b-39c8-44e2-8b84-d6851891aaff}</x14:id>
+          <x14:id>{c1a38c5b-5bed-4a65-baec-a23ce2c3ca3e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14743,7 +14723,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf8b3961-3bfa-4122-9fb2-16b5899749d5}</x14:id>
+          <x14:id>{a5fba692-f20a-433f-a036-1b3cc9429a63}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14757,7 +14737,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8cfe7356-68c5-4e73-b277-efd491d8053d}</x14:id>
+          <x14:id>{693bb30c-b94e-410f-b65e-04496ea150fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14769,7 +14749,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89675322-6524-47bc-8883-30daea2addbe}</x14:id>
+          <x14:id>{2e016f87-c5e6-4782-ade3-5e5705158f9a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14781,7 +14761,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62b2b25e-fc64-4ae1-ba88-6127f2947d66}</x14:id>
+          <x14:id>{8b0ebbff-acfb-49b2-bb78-e173f565542f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14795,7 +14775,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7ade4ec2-a1bb-408f-9912-c893c8175935}</x14:id>
+          <x14:id>{57a87fc6-1c17-44dd-9559-f824b0a18464}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14807,7 +14787,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bb90f6b2-d085-4350-87dd-e893eabd777c}</x14:id>
+          <x14:id>{fdfb43b2-0d11-4083-b48f-1227742f0db6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14844,7 +14824,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f8dd37d9-0ad5-43ba-9e35-7d0bb24ed270}">
+          <x14:cfRule type="dataBar" id="{4abc857a-f3bf-4bb5-b876-c074c66cb71d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14855,7 +14835,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b0d436f5-3229-4e8e-a7be-071cc8361450}">
+          <x14:cfRule type="dataBar" id="{f3082f20-3107-4d48-87d9-92ccb7e18f3a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14866,14 +14846,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{be026398-f23f-47f9-a85d-b340982e0178}">
+          <x14:cfRule type="dataBar" id="{794d3c8e-1e94-422a-914e-12359c31eeca}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{029df8e6-0956-4a91-916d-122e5f33b9c3}">
+          <x14:cfRule type="dataBar" id="{565d305c-37ff-4884-a8f7-089865bf4603}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14884,7 +14864,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c8701642-e5a1-406e-ab30-8e7cc02d3054}">
+          <x14:cfRule type="dataBar" id="{8e28f837-0e6c-42c9-8593-4336690a5ef0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14895,7 +14875,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{26e4c31b-1c51-4349-a562-5d18703bba34}">
+          <x14:cfRule type="dataBar" id="{1bed9b61-fed2-4462-88c5-628e5d3d5ae3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14906,7 +14886,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2c636625-5ee4-48b6-b562-4f7ef85fbce9}">
+          <x14:cfRule type="dataBar" id="{8000e590-2b20-4aac-bb0e-360128f5e292}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14915,7 +14895,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7a2d6eea-828a-4650-b51d-2f302d9b1a82}">
+          <x14:cfRule type="dataBar" id="{d931f09f-c9c5-4caf-9885-0fb59803c44c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14927,7 +14907,7 @@
           <xm:sqref>AD56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1a52e1de-6eb6-4d70-a9d8-60445feed595}">
+          <x14:cfRule type="dataBar" id="{7f88cf40-c017-4f86-9634-03780ae252bd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14938,7 +14918,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cdd8209b-80ca-4136-a546-4feee398ccf6}">
+          <x14:cfRule type="dataBar" id="{46089256-1f83-4fb0-8992-d1b61f433b6b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14949,14 +14929,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7c9d5dfe-46d7-44a6-b475-56c7fe0ec83b}">
+          <x14:cfRule type="dataBar" id="{d17bcae5-5ce7-4039-a8e6-3e7d7f09c8bf}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d0aa2ba4-66a0-48ae-b2fd-816b297697ae}">
+          <x14:cfRule type="dataBar" id="{2a7d5162-8f0e-486b-b9bd-f7bf8247e990}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14967,7 +14947,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5fb1dfb4-d6a7-4d46-bcc8-66d8c0fa52db}">
+          <x14:cfRule type="dataBar" id="{e0aaf361-555c-4d51-af5b-50634c6520db}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14978,7 +14958,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2f3ab93f-1540-436e-a3b5-73313e4187ab}">
+          <x14:cfRule type="dataBar" id="{822ab420-08ae-4916-8e9d-152d8328d5d3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14989,7 +14969,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0b904468-8224-4e3e-8598-90264cecb5ce}">
+          <x14:cfRule type="dataBar" id="{17eec315-2861-4b7e-b6b1-054062c9732f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14998,7 +14978,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3e298ad2-4e9e-4051-b80d-b7396a240037}">
+          <x14:cfRule type="dataBar" id="{7a0ae7c0-1022-4b29-a045-79e6ffe92c79}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15010,7 +14990,7 @@
           <xm:sqref>K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9aa3e44d-8053-4c56-868c-7f597fb234af}">
+          <x14:cfRule type="dataBar" id="{58cf2775-a060-48fc-9db2-753d97ea2413}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15021,7 +15001,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{82900eb9-f94f-4a18-b6c2-8bcbc616ae4a}">
+          <x14:cfRule type="dataBar" id="{314fd1cb-e606-4277-8b1d-f638537ad927}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15032,14 +15012,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9bf4d7b7-3db2-4cd9-be29-3d856e10f757}">
+          <x14:cfRule type="dataBar" id="{41138edf-89c2-4545-8d9b-70a5b1ccd9c4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7420a9d9-0f7c-44c3-8a61-0e3e5577ad3e}">
+          <x14:cfRule type="dataBar" id="{f37a751e-3f14-4e2a-8153-9f47d2395dc6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15050,7 +15030,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{303ca555-4201-42ed-9633-c7949e4d9294}">
+          <x14:cfRule type="dataBar" id="{40925116-b1d4-4ccd-8f76-aa2b5d609f84}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15061,7 +15041,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{eae7986d-503c-44a8-9171-bc3561b17299}">
+          <x14:cfRule type="dataBar" id="{609ee51d-a8a3-4f81-b972-bf577a3905af}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15072,7 +15052,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{42c6def2-d975-4e92-87ce-58609debe97c}">
+          <x14:cfRule type="dataBar" id="{730b6fb1-05a3-4526-91e0-5691aa59df6a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15081,7 +15061,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{20287a30-46b1-40f1-9081-a6c2a093b1a8}">
+          <x14:cfRule type="dataBar" id="{ef778a46-f4d2-442e-9796-8af926003073}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15093,7 +15073,7 @@
           <xm:sqref>AD60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3202fa0b-f4ed-4171-b289-aec41fe50532}">
+          <x14:cfRule type="dataBar" id="{df0806ca-0efd-4d65-ba61-4f2cd965328e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15104,7 +15084,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{745b3fb3-b2da-495d-8f07-be9b757cf5fd}">
+          <x14:cfRule type="dataBar" id="{382589a2-5803-4a98-878c-85c7fc855e83}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15115,14 +15095,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5e30146e-5cd1-493f-b54e-4e08fbae3eea}">
+          <x14:cfRule type="dataBar" id="{41102eee-0152-4ae8-8262-bb92b79d974e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aed28516-5b29-4e25-9c92-b3f9b3bc1f6b}">
+          <x14:cfRule type="dataBar" id="{d9e81d60-8b8c-46cf-8ebc-67f946e21547}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15133,7 +15113,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{26e679be-149b-402d-934e-64533685dfe4}">
+          <x14:cfRule type="dataBar" id="{b77fc6c1-6f6f-40e9-9544-5255edee1417}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15144,7 +15124,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ee212af3-5807-4713-9975-eb8868d806a7}">
+          <x14:cfRule type="dataBar" id="{19aaf16a-b545-42dc-84d7-dbffdbff822a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15155,7 +15135,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{35e391e1-ccb4-4956-9cfc-d631ef73bd00}">
+          <x14:cfRule type="dataBar" id="{190f1ffc-18db-4ed5-85b5-971fcdd80303}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15164,7 +15144,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6913ae6d-44f5-4cc4-842d-9c19918c096f}">
+          <x14:cfRule type="dataBar" id="{8655b60e-ed92-4e34-b696-3630538cc71c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15176,7 +15156,7 @@
           <xm:sqref>K61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1d0afa0a-fca3-4488-a9d4-785e71508049}">
+          <x14:cfRule type="dataBar" id="{749cf70d-83ae-4096-b4bc-c283cb76dd30}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15187,7 +15167,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f75b6ff3-9860-47e5-9d28-080d2b90a20a}">
+          <x14:cfRule type="dataBar" id="{e2a68314-628a-4de0-82a2-035956d400ce}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15198,14 +15178,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2ef951a1-581d-459a-b5fc-c25d83f517de}">
+          <x14:cfRule type="dataBar" id="{59462c06-3612-4981-9782-d0b271f6c7f6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e2c4edd3-dcf1-4010-9994-04ae989354c0}">
+          <x14:cfRule type="dataBar" id="{771037c7-7f35-4e58-88ae-79f624de6a5a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15216,7 +15196,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{06794649-bf22-42bd-922a-f8a03aefec74}">
+          <x14:cfRule type="dataBar" id="{609260af-2620-4488-8f97-adae49ad2338}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15227,7 +15207,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ba91d3f2-b574-41df-98db-389b1a4aa89e}">
+          <x14:cfRule type="dataBar" id="{b24643f1-127c-461f-909b-1780ef2b02cb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15238,7 +15218,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7acf6793-72e5-4515-9d50-406fab175039}">
+          <x14:cfRule type="dataBar" id="{b49b4d19-7f23-454f-b293-7c27a4ad4d93}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15247,7 +15227,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4bd42acc-397b-4f0e-9235-9dab75ccde1b}">
+          <x14:cfRule type="dataBar" id="{1260ad13-0cc2-45ec-97b0-7101936371e8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15259,7 +15239,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{61983b95-1bc7-45bf-a7e1-0d77a4be1697}">
+          <x14:cfRule type="dataBar" id="{6ec52697-66e8-48e6-9911-504c70e0c0e9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15270,7 +15250,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2256cc2f-038c-4121-8614-58c08f36139a}">
+          <x14:cfRule type="dataBar" id="{ec084eff-f02a-476d-8b08-ef58948a0628}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15281,14 +15261,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0ccfacc4-2e98-4aeb-a8f9-d2e87436df17}">
+          <x14:cfRule type="dataBar" id="{e4d227df-c65f-47f8-a781-8c43c5ce6358}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2e9f8857-0abc-4084-af13-fcec883be745}">
+          <x14:cfRule type="dataBar" id="{ca5a4b4d-03a7-42b4-9978-4732f60d0f7e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15299,7 +15279,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2d0bf7fc-46d4-4127-a1c2-289fae48076c}">
+          <x14:cfRule type="dataBar" id="{37a1ee8d-33e6-4e86-9727-fea308272140}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15310,7 +15290,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{561b35bf-f1ac-4a7d-bca2-203b680b519d}">
+          <x14:cfRule type="dataBar" id="{32132eab-564e-4dc5-9dc9-296c5a1e6e03}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15321,7 +15301,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{900016d7-d64c-4f8e-bda0-7d9f370628b1}">
+          <x14:cfRule type="dataBar" id="{2aa4c89d-c345-4841-a983-1e699c6fd3d6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15330,7 +15310,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b7c9ef0f-bf41-4dfb-b749-c2f229d5b122}">
+          <x14:cfRule type="dataBar" id="{59473855-7026-49b9-8cf2-8ca5958fe56e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15342,7 +15322,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{613aa387-d0b6-45cb-b3cd-1d9d32ddfd5d}">
+          <x14:cfRule type="dataBar" id="{4c0be875-1e73-41e6-b89c-fc3ab882a13c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15353,7 +15333,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{16c7c2d2-7e07-4860-aa0f-0efd88aa3683}">
+          <x14:cfRule type="dataBar" id="{136cea1d-8874-4769-b407-4ec92c7f4298}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15364,14 +15344,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{53d60f3b-8c98-4283-bb23-3603259cc149}">
+          <x14:cfRule type="dataBar" id="{32179bf7-df89-49bc-ab50-83ecb6db1246}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2f104416-c5d5-47bc-ad2f-bf622e99b789}">
+          <x14:cfRule type="dataBar" id="{5d7029e5-d451-40d8-b0c9-9c64787e70b6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15382,7 +15362,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2beb57a7-a286-4c26-bfeb-66e8108b93c6}">
+          <x14:cfRule type="dataBar" id="{d11fd8e3-3ac4-4c3f-9be9-243a57f940c9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15393,7 +15373,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d54625bc-01b6-4e8f-862e-9be617c7b7ab}">
+          <x14:cfRule type="dataBar" id="{11e5f813-9422-43ab-a14b-a02653526773}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15404,7 +15384,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f89376e1-71a2-45df-b009-60b6b96f1f50}">
+          <x14:cfRule type="dataBar" id="{b79cb2b0-13ca-4f04-a313-d7d2e5a1671b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15413,7 +15393,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e1c1f213-9562-492f-849e-236a6fbd0afe}">
+          <x14:cfRule type="dataBar" id="{6bceec41-c76e-4db6-bef2-3bc769d46356}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15425,7 +15405,7 @@
           <xm:sqref>K57:K58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd660bf2-c44c-4355-8b61-67fd74d67f4d}">
+          <x14:cfRule type="dataBar" id="{04e038ae-c0ee-4e04-9a0e-39e20d5f6a1b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15437,7 +15417,7 @@
           <xm:sqref>K187:K206</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d7b01846-ff5f-481e-94e6-fb0a080b2058}">
+          <x14:cfRule type="dataBar" id="{365ee957-22b9-42f6-be9f-f189169ee293}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15449,7 +15429,7 @@
           <xm:sqref>AD56:AE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00eb0ea0-78b5-4e5d-b53c-76495df8839b}">
+          <x14:cfRule type="dataBar" id="{cff02d77-6319-4dc6-9737-f7c66112b72f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15461,7 +15441,7 @@
           <xm:sqref>AD60:AE63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6550637d-847b-4599-9131-1762b5cb3de1}">
+          <x14:cfRule type="dataBar" id="{4a06f551-b2e5-44e2-9534-a0768889a54e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15472,7 +15452,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8427225c-5b24-4584-bfd1-e11d4fccbedd}">
+          <x14:cfRule type="dataBar" id="{f56dda1d-eb16-420c-ac58-f42f44d60dcd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15483,14 +15463,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9654132b-b282-4a5b-a230-f7208da4e900}">
+          <x14:cfRule type="dataBar" id="{9d7f1b94-0f9f-4a43-a6d5-70bf32b66362}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{933bdeb4-44f9-44cf-ab09-b6005fc7e759}">
+          <x14:cfRule type="dataBar" id="{a2be7812-ea70-4f60-9ebe-d3a364abac1f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15501,7 +15481,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3a53b751-6b45-49a0-9e96-936c8e27db7e}">
+          <x14:cfRule type="dataBar" id="{3bcc6139-b457-4c12-a0bb-7af355907714}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15512,7 +15492,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4106a878-16bf-48eb-8b3b-0972440acf08}">
+          <x14:cfRule type="dataBar" id="{b13bd9c4-33a6-475d-9bcd-b5d3170a5d4c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15523,7 +15503,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fb538c8a-81d7-4e6a-b8ad-bc38c7f210b0}">
+          <x14:cfRule type="dataBar" id="{ab0bdae3-ce79-4745-9258-97593fca2686}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15532,7 +15512,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2d8862f3-0d74-4922-bb60-d1d261292f08}">
+          <x14:cfRule type="dataBar" id="{b1f24c4d-7c91-4ff5-9c5c-023b708e98ff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15544,7 +15524,7 @@
           <xm:sqref>F67 F77 F87 F97 F107 F117 F127 F137 F147 F157 F167 F177</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1c19f651-ee91-4534-98cb-c3b3b089846e}">
+          <x14:cfRule type="dataBar" id="{58e115bf-bf42-48f0-bc4b-6a4df89d2896}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15553,7 +15533,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4d636ca4-5be8-423d-b0b9-435b8e2c8b3a}">
+          <x14:cfRule type="dataBar" id="{bf2f1cbd-3698-4819-aa76-e0ef253636de}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15565,7 +15545,7 @@
           <xm:sqref>K67:K77 K83:K97 K103:K117 K123:K137 K143:K157 K163:K177 K183:K186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1720642c-3530-4294-b7a2-ef11d2537329}">
+          <x14:cfRule type="dataBar" id="{fafae96f-fb93-4211-a18e-39993e71a479}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15577,7 +15557,7 @@
           <xm:sqref>Y67:Y77 Y83:Y97 Y103:Y120 Y123:Y139 Y143:Y158 Y163:Y177 Y183:Y186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c64afc50-7e6a-4843-84c9-f4849e154217}">
+          <x14:cfRule type="dataBar" id="{1a7c387e-1a12-4252-a27f-09a1fd4a94be}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15586,7 +15566,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{03801493-5bcb-47a5-bddc-85d8a7a74842}">
+          <x14:cfRule type="dataBar" id="{0f61c689-be11-497d-9b82-09cbaf3755c6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15598,14 +15578,14 @@
           <xm:sqref>AB67 AB87 AB107 AB127 AB147 AB167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e051b41-a042-40ef-a400-0d4fddd228d2}">
+          <x14:cfRule type="dataBar" id="{47a8839f-0892-4e3a-81e2-941c53e6faad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e684fbb5-17d2-4457-a3ae-6558557579ab}">
+          <x14:cfRule type="dataBar" id="{8fc4e5e6-a3f4-4ea9-8b2c-dc4c443e4516}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15617,7 +15597,7 @@
           <xm:sqref>AB67:AB77 AB83:AB97 AB103:AB120 AB123:AB139 AB143:AB158 AB163:AB177 AB183:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42403239-53de-48af-a42d-aa64ebacf436}">
+          <x14:cfRule type="dataBar" id="{f88cb0fb-32dd-43c1-b822-d6413f71308a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15629,7 +15609,7 @@
           <xm:sqref>AB67:AB77 AB83:AB97 AB103:AB117 AB123:AB137 AB143:AB157 AB163:AB177 AB183:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{742bfa9f-9d44-43dd-b116-ed385c276ca6}">
+          <x14:cfRule type="dataBar" id="{cddf6781-0c70-4cbf-84da-74de37731050}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15638,7 +15618,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4996df7b-5f2d-4074-8b41-77825d0712d0}">
+          <x14:cfRule type="dataBar" id="{1728703a-1893-413a-8f6a-cf63c41d1feb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15650,7 +15630,7 @@
           <xm:sqref>K78:K82 K98:K102 K118:K122 K138:K142 K158:K162 K178:K182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d9a26976-b2ba-49d8-8b04-d1fcac6ff96b}">
+          <x14:cfRule type="dataBar" id="{2c8cade6-5bc5-4824-a56c-3e84b2ea88cb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15662,14 +15642,14 @@
           <xm:sqref>Y78:Y82 Y98:Y102 Y118:Y122 Y138:Y142 Y158:Y162 Y178:Y182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{48c576ba-f0fd-4b5c-b49d-b2c3f93b50e3}">
+          <x14:cfRule type="dataBar" id="{b990cf4c-3ab1-4fcd-a8cc-f125cf1733c3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6938760b-39c8-44e2-8b84-d6851891aaff}">
+          <x14:cfRule type="dataBar" id="{c1a38c5b-5bed-4a65-baec-a23ce2c3ca3e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15678,7 +15658,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cf8b3961-3bfa-4122-9fb2-16b5899749d5}">
+          <x14:cfRule type="dataBar" id="{a5fba692-f20a-433f-a036-1b3cc9429a63}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15690,7 +15670,7 @@
           <xm:sqref>AB78:AB82 AB98:AB102 AB118:AB122 AB138:AB142 AB158:AB162 AB178:AB182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8cfe7356-68c5-4e73-b277-efd491d8053d}">
+          <x14:cfRule type="dataBar" id="{693bb30c-b94e-410f-b65e-04496ea150fa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15699,7 +15679,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{89675322-6524-47bc-8883-30daea2addbe}">
+          <x14:cfRule type="dataBar" id="{2e016f87-c5e6-4782-ade3-5e5705158f9a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15708,7 +15688,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{62b2b25e-fc64-4ae1-ba88-6127f2947d66}">
+          <x14:cfRule type="dataBar" id="{8b0ebbff-acfb-49b2-bb78-e173f565542f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15720,7 +15700,7 @@
           <xm:sqref>F187 F192 F197 F202</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7ade4ec2-a1bb-408f-9912-c893c8175935}">
+          <x14:cfRule type="dataBar" id="{57a87fc6-1c17-44dd-9559-f824b0a18464}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15729,7 +15709,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bb90f6b2-d085-4350-87dd-e893eabd777c}">
+          <x14:cfRule type="dataBar" id="{fdfb43b2-0d11-4083-b48f-1227742f0db6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15750,12 +15730,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/E楼交接班容量报表空模板.xlsx
+++ b/外网端源码/E楼交接班容量报表空模板.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="493">
   <si>
     <t>班次</t>
   </si>
@@ -4691,7 +4691,10 @@
       <c r="M26" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="N26" s="92"/>
+      <c r="N26" s="92">
+        <f>I29</f>
+        <v>0</v>
+      </c>
       <c r="O26" s="54"/>
       <c r="P26" s="83" t="s">
         <v>78</v>
@@ -4720,7 +4723,10 @@
       <c r="Z26" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="AA26" s="92"/>
+      <c r="AA26" s="92">
+        <f>V29</f>
+        <v>0</v>
+      </c>
       <c r="AB26" s="88" t="s">
         <v>84</v>
       </c>
@@ -5255,7 +5261,10 @@
       <c r="M36" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="N36" s="106"/>
+      <c r="N36" s="106">
+        <f>I39</f>
+        <v>0</v>
+      </c>
       <c r="O36" s="54"/>
       <c r="P36" s="103" t="s">
         <v>78</v>
@@ -5288,7 +5297,10 @@
       <c r="Z36" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="AA36" s="105"/>
+      <c r="AA36" s="105">
+        <f>V39</f>
+        <v>0</v>
+      </c>
       <c r="AB36" s="88" t="s">
         <v>104</v>
       </c>
@@ -5437,9 +5449,7 @@
       <c r="H39" s="103" t="s">
         <v>93</v>
       </c>
-      <c r="I39" s="105" t="s">
-        <v>15</v>
-      </c>
+      <c r="I39" s="105"/>
       <c r="J39" s="105" t="s">
         <v>15</v>
       </c>
@@ -5470,9 +5480,7 @@
       <c r="U39" s="103" t="s">
         <v>93</v>
       </c>
-      <c r="V39" s="105" t="s">
-        <v>15</v>
-      </c>
+      <c r="V39" s="105"/>
       <c r="W39" s="105" t="s">
         <v>15</v>
       </c>
@@ -6910,10 +6918,11 @@
         <v>0</v>
       </c>
       <c r="AC69" s="138">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="138">
+        <f>20-AC69</f>
         <v>20</v>
-      </c>
-      <c r="AD69" s="138">
-        <v>0</v>
       </c>
       <c r="AE69" s="138" t="s">
         <v>200</v>
@@ -7820,10 +7829,11 @@
         <v>0</v>
       </c>
       <c r="AC89" s="138">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="138">
+        <f>20-AC89</f>
         <v>20</v>
-      </c>
-      <c r="AD89" s="138">
-        <v>0</v>
       </c>
       <c r="AE89" s="138" t="s">
         <v>200</v>
@@ -8730,10 +8740,11 @@
         <v>0.0584415584415584</v>
       </c>
       <c r="AC109" s="138">
+        <v>0</v>
+      </c>
+      <c r="AD109" s="138">
+        <f>20-AC109</f>
         <v>20</v>
-      </c>
-      <c r="AD109" s="138">
-        <v>0</v>
       </c>
       <c r="AE109" s="138" t="s">
         <v>200</v>
@@ -9640,10 +9651,11 @@
         <v>0.590909090909091</v>
       </c>
       <c r="AC129" s="138">
+        <v>0</v>
+      </c>
+      <c r="AD129" s="138">
+        <f>20-AC129</f>
         <v>20</v>
-      </c>
-      <c r="AD129" s="138">
-        <v>0</v>
       </c>
       <c r="AE129" s="138" t="s">
         <v>200</v>
@@ -10550,10 +10562,11 @@
         <v>0</v>
       </c>
       <c r="AC149" s="138">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD149" s="138">
-        <v>14</v>
+        <f>20-AC149</f>
+        <v>20</v>
       </c>
       <c r="AE149" s="138" t="s">
         <v>200</v>
@@ -11460,10 +11473,11 @@
         <v>0</v>
       </c>
       <c r="AC169" s="147">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD169" s="147">
-        <v>12</v>
+        <f>20-AC169</f>
+        <v>20</v>
       </c>
       <c r="AE169" s="138" t="s">
         <v>200</v>
@@ -13846,7 +13860,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{489771ec-78c3-4707-bde7-12f2bf5def24}</x14:id>
+          <x14:id>{e81aa7cb-be2c-473b-9a26-e7ff17abccff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13858,7 +13872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{19c1fee5-d51b-4a94-bdc9-dcc765ded368}</x14:id>
+          <x14:id>{607366ff-e314-4f9b-857b-061e45830664}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13870,7 +13884,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{273560ca-e8ed-47d0-9004-a28e6da1ea40}</x14:id>
+          <x14:id>{429644d3-3cfd-4d55-bc6f-dc48fdfb7604}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13882,7 +13896,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc374757-db29-453a-b76f-f9d8ed50b9f8}</x14:id>
+          <x14:id>{1e2414fc-eddf-404e-8064-25908df78843}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13894,7 +13908,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c8ebec8-8311-4560-8691-3ffeb3b1ea88}</x14:id>
+          <x14:id>{eec50ee7-6dae-4c47-867a-dbc9bf938797}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13906,7 +13920,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ca9dc0c-c484-4602-b068-7bf73ae7549d}</x14:id>
+          <x14:id>{acc6a71a-c49c-4322-8998-cb4fffe8e619}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13918,7 +13932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f831bced-7367-4a3d-9f77-f0d36e92196c}</x14:id>
+          <x14:id>{3b59f97c-9aca-4de8-803d-38e7df80526f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13930,7 +13944,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90d4f910-8a7c-48d5-8b74-4dd1ff1d4614}</x14:id>
+          <x14:id>{69a90e79-0c6e-48c9-948c-94f497732beb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13944,7 +13958,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{de9fa947-96d5-49f7-805c-304c1ed2bf93}</x14:id>
+          <x14:id>{999246bd-fcc5-430a-bfaf-dbf0f3c6918d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13956,7 +13970,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{527576bf-6ad8-468f-a639-d929616eda6f}</x14:id>
+          <x14:id>{8be537db-ecd9-4be6-874a-4ea601f188df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13968,7 +13982,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f9ff8b1-6aa4-4bba-ae2e-4f7f94262ea3}</x14:id>
+          <x14:id>{42acd88f-ff0e-4c13-87f0-38dbe452ce64}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13980,7 +13994,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7653ee80-133f-4df9-96c4-b3f9ae32d249}</x14:id>
+          <x14:id>{54b3ceb8-aa9f-46f7-99a4-811a48cca552}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13992,7 +14006,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{14377c2f-66d5-4559-8f87-2bf27f469d92}</x14:id>
+          <x14:id>{4985c0b1-bde7-402c-a10f-1f090d9f2425}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14004,7 +14018,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{516aa4a8-cb3e-4b7b-9637-ebc9f8585b06}</x14:id>
+          <x14:id>{5b332b9c-ab16-44d7-a327-df87c96863e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14016,7 +14030,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0c90b85-3dda-4c01-be68-4adb70d8a0e6}</x14:id>
+          <x14:id>{6102e441-d88c-4081-8e0f-81231818b925}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14028,7 +14042,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13fe092d-665f-4bd4-a0cc-b8e20d023113}</x14:id>
+          <x14:id>{dd76a7cf-6b96-42ad-ab1d-67bc41c18047}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14042,7 +14056,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5464224e-c505-4f7b-abde-1d0d26f9dc28}</x14:id>
+          <x14:id>{8b319bbf-4f56-4c79-9ac7-eb8a150b9067}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14054,7 +14068,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{000595c7-1e2c-44ca-9126-52261b2da723}</x14:id>
+          <x14:id>{74ac4359-1f35-4d5f-987d-f54e56ac0890}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14066,7 +14080,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e6130ccd-6c8d-4905-859c-4a27a6b7772a}</x14:id>
+          <x14:id>{0ec2c37c-172f-46cb-b40f-f76a48b255fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14078,7 +14092,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{145f9db2-b247-47d2-9e26-fed1d94a6f0d}</x14:id>
+          <x14:id>{6a6e33b1-fed1-466a-8612-f3f2c98a5ee0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14090,7 +14104,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0dd6799-346d-4333-8713-8c58680e4e75}</x14:id>
+          <x14:id>{ab429ed2-661b-4a6f-bb5a-44766faa9883}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14102,7 +14116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{857864ec-ee56-4eed-91c5-2cdd3f2b79f2}</x14:id>
+          <x14:id>{16f3ef7f-fa9b-4996-a283-531f7401421c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14114,7 +14128,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8966a9ef-9b77-462a-82d0-710774e7e8e4}</x14:id>
+          <x14:id>{cdf20b77-e35d-4baf-9526-dbf45756b3e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14126,7 +14140,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8a1eaa5-fbc3-4e74-8a55-d7e7d49b7b39}</x14:id>
+          <x14:id>{b335a2d5-8c6c-48b8-bb22-56c9fa018db8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14140,7 +14154,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1553ff7-c963-41db-a4eb-060cb266c493}</x14:id>
+          <x14:id>{85f56e96-1659-4397-b782-a522c479860f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14152,7 +14166,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{54d2ab7f-2484-4842-824a-91524e9333a7}</x14:id>
+          <x14:id>{ee5e62e7-e7fc-4614-a632-dbfb76195043}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14164,7 +14178,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8d92c69-c33f-4cec-9e82-16cd15bdb6f9}</x14:id>
+          <x14:id>{dbe88aee-28ee-4640-99ac-dae923f86d4d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14176,7 +14190,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4dd509c8-d424-45e9-9bf1-d9a1956683cd}</x14:id>
+          <x14:id>{cf9ebbda-727a-48c5-bc04-aaad3d539b73}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14188,7 +14202,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{681b85f6-03e0-4d0a-adf8-fd61ac5b7f54}</x14:id>
+          <x14:id>{0e6e3902-845d-4b7e-911a-5e9989e92656}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14200,7 +14214,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2bd90df-74b3-4167-830a-deb981b04b90}</x14:id>
+          <x14:id>{9593fed4-060b-4c6f-a7d0-9280cfa88bd1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14212,7 +14226,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7fc3743c-e0a6-4995-a891-1e81217b77a8}</x14:id>
+          <x14:id>{d8fa2be3-0813-4357-8958-c5261e5e1ec5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14224,7 +14238,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c7bc139b-23f2-441e-9a8f-f38fa096f01e}</x14:id>
+          <x14:id>{f502eb5e-6efa-4219-8e08-6caa664df6a6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14238,7 +14252,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55be9825-5a59-4695-917e-7fbd94136f54}</x14:id>
+          <x14:id>{568d3161-e2aa-4f46-a430-41a555d0d84b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14250,7 +14264,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{821cbcce-03b2-41b8-bf60-306c63a31db7}</x14:id>
+          <x14:id>{4d840c12-7a16-473f-85e5-9ad0b150f6b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14262,7 +14276,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3edd6a2-a7ae-425c-a753-c82074d930c9}</x14:id>
+          <x14:id>{88a919d7-b070-4ddd-81f4-a594e55cac43}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14274,7 +14288,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{279ffa6a-174d-4dcd-b476-a5e3b058c8ad}</x14:id>
+          <x14:id>{fb877c83-4296-4612-b7c1-5cb7fea610a8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14286,7 +14300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3f68245-675c-425c-97d1-ee01bc00089e}</x14:id>
+          <x14:id>{2eee616b-5d81-4ffd-a9d3-0f904459bbbc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14298,7 +14312,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73b74af1-3502-43fa-b811-8ebc446db6bb}</x14:id>
+          <x14:id>{8e19afb2-df1f-4e51-8df3-3af986d2f116}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14310,7 +14324,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4bcde2e6-c787-431b-b57e-79fbcd44ae36}</x14:id>
+          <x14:id>{0f773ae2-57e0-4a86-b5f4-ea3c3eb849db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14322,7 +14336,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30f725ff-a7c5-4fac-9f20-85c53ab9c78b}</x14:id>
+          <x14:id>{4f90c8a8-eee9-4dfb-a67a-b32ec7d0176d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14336,7 +14350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5d946bc-f65f-4753-8aaf-54d96b48fa1b}</x14:id>
+          <x14:id>{76fc8c7d-be85-4d35-89cf-5944b1675599}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14348,7 +14362,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e29141e9-f053-448c-8aea-f920ed6cccfc}</x14:id>
+          <x14:id>{4dab22e7-06bd-46ec-9041-c38c3183e90a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14360,7 +14374,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4f42310-c7f8-4ed8-b692-d15529460bd0}</x14:id>
+          <x14:id>{fa6bf814-e24b-4238-98ac-dd528568c051}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14372,7 +14386,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bdf468da-75ef-4389-8434-72b1b71852e1}</x14:id>
+          <x14:id>{cd9daa61-330a-449b-8aee-01afde412bf1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14384,7 +14398,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99aa3b76-eca0-4c40-965a-a571c2876178}</x14:id>
+          <x14:id>{a04849f9-4210-4ffd-9440-7475f151111c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14396,7 +14410,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a553d35c-6fca-45c9-8400-fe1e8e91235b}</x14:id>
+          <x14:id>{2e4dca19-d764-43b2-9c8e-b5dd48c935f3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14408,7 +14422,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab94e137-781a-4292-a619-0e9775f7f950}</x14:id>
+          <x14:id>{87f83abb-bd4f-4c64-9a34-49483fdfe7e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14420,7 +14434,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2bfa5b4-aaf3-4989-9600-981976f7680e}</x14:id>
+          <x14:id>{296a0e4f-c385-4e49-af28-290ad153c631}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14434,7 +14448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7bb22888-fb1a-4dcf-8eae-71e0afb6059d}</x14:id>
+          <x14:id>{ebe442a4-b976-43b5-a5c1-a241c41ee2ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14446,7 +14460,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d53ebb90-5617-4cbf-9500-a8ea81fdc68a}</x14:id>
+          <x14:id>{56320c77-cdfb-4926-8288-76b018b10d84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14458,7 +14472,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51b1ab5a-1768-4d74-ab51-27f6a09fc5c6}</x14:id>
+          <x14:id>{29e55750-027b-4fed-b5db-36223b4262cb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14470,7 +14484,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{099bf8d8-e202-4caf-94b4-c3daff75adb3}</x14:id>
+          <x14:id>{aa7c311f-15c2-4b7b-943e-161150161323}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14482,7 +14496,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bdbccb95-df11-4074-a44b-a50b8e5d39cb}</x14:id>
+          <x14:id>{fc81220b-6a92-4091-a353-20c0d9a5a60e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14494,7 +14508,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ca60a51-4139-4837-be21-9324d8221230}</x14:id>
+          <x14:id>{7069645c-30cd-482a-8945-fc1f04461eca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14506,7 +14520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66503706-5cf0-4216-8e18-82a648e44121}</x14:id>
+          <x14:id>{898cd7da-c8ea-40f1-8e9a-806d7f6945b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14518,7 +14532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4b615bf-b6c4-4a08-aacf-456a8414d875}</x14:id>
+          <x14:id>{ac14da52-b71c-49e8-8fbc-43025f954510}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14532,7 +14546,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e5b8569-d4c0-41bc-9e5b-232bd65491c5}</x14:id>
+          <x14:id>{a1684ad2-e18a-4a36-acfd-41b24ffee10c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14546,7 +14560,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90575078-8f7a-48b6-8a67-24cf13bb7250}</x14:id>
+          <x14:id>{958089b0-ad58-4a94-b7a3-4daf4a5c569c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14560,7 +14574,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b6835af3-426c-4ebc-91c7-26aa8bbbe67d}</x14:id>
+          <x14:id>{379db16a-b4ce-43bd-9b38-3efb5b89835d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14574,7 +14588,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b246a5b6-c193-4512-81eb-243024531375}</x14:id>
+          <x14:id>{32206371-e472-4dda-935c-3d71cdae01f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14586,7 +14600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d2f9a4b-a891-451b-81b9-3725c234cd4b}</x14:id>
+          <x14:id>{3caec8dd-10b4-4d89-b38b-56a2e7852a1c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14598,7 +14612,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{221a659e-2ff3-4667-933f-daaf66ba603e}</x14:id>
+          <x14:id>{ed2952d4-3367-4760-ad47-d39f56c2f996}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14610,7 +14624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d3009d35-907b-49d9-891b-77b32d6660fa}</x14:id>
+          <x14:id>{8fbcccb9-c29e-4d07-89e1-44e099167717}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14622,7 +14636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4b5c87e-8e40-4f02-9c2f-6461feaf5519}</x14:id>
+          <x14:id>{5a390851-ebaf-4c4e-abcf-e93679d7948f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14634,7 +14648,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3330c789-9dd7-490e-a3b7-d88fceaa7261}</x14:id>
+          <x14:id>{6a7c9f3f-25a6-45d5-96fe-2ffbe68284bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14646,7 +14660,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26a4f0a3-5e14-4531-8767-6c61896eca48}</x14:id>
+          <x14:id>{5301e40d-0761-4284-8b14-37bb679c0b69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14658,7 +14672,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ece54310-3b8d-4f5e-9280-8a3fe32b12b6}</x14:id>
+          <x14:id>{12f87e8b-f359-4772-bb41-f62d65e8b3dd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14672,7 +14686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ce3aa55-dc0e-403a-8076-d5c1ee8c02b2}</x14:id>
+          <x14:id>{75ad03a0-8e72-47ff-a193-7cce0b89aa74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14684,7 +14698,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{356a31e6-4f7e-4c20-b47e-62922d784229}</x14:id>
+          <x14:id>{c64a43c1-3ae5-40c9-b589-020ca1dd00a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14698,7 +14712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c35d8f4c-11a5-411b-8c4b-82ef2a071a99}</x14:id>
+          <x14:id>{8ec49a28-b370-4fac-b640-1932e2f49933}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14712,7 +14726,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5914218-5a47-4d79-ba5e-5d8cce336a7a}</x14:id>
+          <x14:id>{4c0fdf8f-d7f6-42a3-b2fb-29c661dda80c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14724,7 +14738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8187efee-394b-4af3-9d3c-39298600e688}</x14:id>
+          <x14:id>{53bfc2fc-9310-493d-b329-b599172962a6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14738,7 +14752,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66edc105-c931-4435-a290-10e683b20464}</x14:id>
+          <x14:id>{8ca38345-d480-45da-b8ea-1a005da338e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14750,7 +14764,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bc8ddd38-d2f0-4b12-ab7e-f0180480a509}</x14:id>
+          <x14:id>{1369e301-62e4-4e1b-a6bd-27b45e60765e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14764,7 +14778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4726ca8-93a8-42db-bb68-11f5fb3c4de2}</x14:id>
+          <x14:id>{f1ee1300-8afe-4322-8cfe-a1bb78829b73}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14778,7 +14792,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d8199597-6d0d-480e-b67d-7c5db10c1433}</x14:id>
+          <x14:id>{23d7eb47-3831-4350-b261-11accb9971ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14790,7 +14804,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41029be4-1503-4104-8c1d-c2b92142a685}</x14:id>
+          <x14:id>{6bbb0353-a290-493d-ae69-162ffd534ffe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14804,7 +14818,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2307146e-e07d-44e3-bbe7-3bdabc877f93}</x14:id>
+          <x14:id>{3b5b268d-a5a6-48ce-b2c0-b146afbc0214}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14818,7 +14832,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f55db939-0909-4726-a92d-af2e573ff33f}</x14:id>
+          <x14:id>{a616a604-eb95-4ec3-ad20-8fa099904fda}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14830,7 +14844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79d7c617-c934-4852-ae12-d345eda47912}</x14:id>
+          <x14:id>{13e54fe7-4253-4788-8a49-090293778def}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14842,7 +14856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb24242f-59e2-4d42-b80d-b823c4ffd229}</x14:id>
+          <x14:id>{fe45dde1-db7d-42b7-81a0-e5ff6cc332a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14856,7 +14870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7c6e6227-d3f3-4f80-ab19-e002897a420a}</x14:id>
+          <x14:id>{0666ce47-5caa-4387-a5bf-b70b7316fef2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14868,7 +14882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e12dd716-df26-4bdf-aabf-ba5705bd4263}</x14:id>
+          <x14:id>{32d45b66-37c2-4e72-a67f-9555c84aa57d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14880,7 +14894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b434a534-36c4-4698-99fc-fee06ff6477b}</x14:id>
+          <x14:id>{11039150-8a86-4f61-89ef-0821e94848de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14894,7 +14908,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2694520c-7473-4c18-a15a-3601f71796b3}</x14:id>
+          <x14:id>{8916ec62-b8f7-4917-a10d-0449fc292335}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14906,7 +14920,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24645368-5f5b-443c-993c-480f9e73969c}</x14:id>
+          <x14:id>{e36f687b-dca9-47fa-8fd0-60dcd60cba6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14928,7 +14942,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:I6 P6:R6">
       <formula1>"A班,B班,C班,D班"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A51:B51 A11:B18 A20:B48 A49:B50">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A11:B18 A20:B51">
       <formula1>"A楼,B楼,C楼,D楼,E楼"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14943,7 +14957,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{489771ec-78c3-4707-bde7-12f2bf5def24}">
+          <x14:cfRule type="dataBar" id="{e81aa7cb-be2c-473b-9a26-e7ff17abccff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14952,7 +14966,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{19c1fee5-d51b-4a94-bdc9-dcc765ded368}">
+          <x14:cfRule type="dataBar" id="{607366ff-e314-4f9b-857b-061e45830664}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14961,7 +14975,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{273560ca-e8ed-47d0-9004-a28e6da1ea40}">
+          <x14:cfRule type="dataBar" id="{429644d3-3cfd-4d55-bc6f-dc48fdfb7604}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14972,7 +14986,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dc374757-db29-453a-b76f-f9d8ed50b9f8}">
+          <x14:cfRule type="dataBar" id="{1e2414fc-eddf-404e-8064-25908df78843}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14983,7 +14997,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3c8ebec8-8311-4560-8691-3ffeb3b1ea88}">
+          <x14:cfRule type="dataBar" id="{eec50ee7-6dae-4c47-867a-dbc9bf938797}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14994,14 +15008,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0ca9dc0c-c484-4602-b068-7bf73ae7549d}">
+          <x14:cfRule type="dataBar" id="{acc6a71a-c49c-4322-8998-cb4fffe8e619}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f831bced-7367-4a3d-9f77-f0d36e92196c}">
+          <x14:cfRule type="dataBar" id="{3b59f97c-9aca-4de8-803d-38e7df80526f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15012,7 +15026,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{90d4f910-8a7c-48d5-8b74-4dd1ff1d4614}">
+          <x14:cfRule type="dataBar" id="{69a90e79-0c6e-48c9-948c-94f497732beb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15026,7 +15040,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{de9fa947-96d5-49f7-805c-304c1ed2bf93}">
+          <x14:cfRule type="dataBar" id="{999246bd-fcc5-430a-bfaf-dbf0f3c6918d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15035,7 +15049,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{527576bf-6ad8-468f-a639-d929616eda6f}">
+          <x14:cfRule type="dataBar" id="{8be537db-ecd9-4be6-874a-4ea601f188df}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15044,7 +15058,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6f9ff8b1-6aa4-4bba-ae2e-4f7f94262ea3}">
+          <x14:cfRule type="dataBar" id="{42acd88f-ff0e-4c13-87f0-38dbe452ce64}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15055,7 +15069,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7653ee80-133f-4df9-96c4-b3f9ae32d249}">
+          <x14:cfRule type="dataBar" id="{54b3ceb8-aa9f-46f7-99a4-811a48cca552}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15066,7 +15080,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{14377c2f-66d5-4559-8f87-2bf27f469d92}">
+          <x14:cfRule type="dataBar" id="{4985c0b1-bde7-402c-a10f-1f090d9f2425}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15077,14 +15091,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{516aa4a8-cb3e-4b7b-9637-ebc9f8585b06}">
+          <x14:cfRule type="dataBar" id="{5b332b9c-ab16-44d7-a327-df87c96863e5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e0c90b85-3dda-4c01-be68-4adb70d8a0e6}">
+          <x14:cfRule type="dataBar" id="{6102e441-d88c-4081-8e0f-81231818b925}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15095,7 +15109,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{13fe092d-665f-4bd4-a0cc-b8e20d023113}">
+          <x14:cfRule type="dataBar" id="{dd76a7cf-6b96-42ad-ab1d-67bc41c18047}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15109,7 +15123,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5464224e-c505-4f7b-abde-1d0d26f9dc28}">
+          <x14:cfRule type="dataBar" id="{8b319bbf-4f56-4c79-9ac7-eb8a150b9067}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15118,7 +15132,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{000595c7-1e2c-44ca-9126-52261b2da723}">
+          <x14:cfRule type="dataBar" id="{74ac4359-1f35-4d5f-987d-f54e56ac0890}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15127,7 +15141,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e6130ccd-6c8d-4905-859c-4a27a6b7772a}">
+          <x14:cfRule type="dataBar" id="{0ec2c37c-172f-46cb-b40f-f76a48b255fa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15138,7 +15152,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{145f9db2-b247-47d2-9e26-fed1d94a6f0d}">
+          <x14:cfRule type="dataBar" id="{6a6e33b1-fed1-466a-8612-f3f2c98a5ee0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15149,7 +15163,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e0dd6799-346d-4333-8713-8c58680e4e75}">
+          <x14:cfRule type="dataBar" id="{ab429ed2-661b-4a6f-bb5a-44766faa9883}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15160,14 +15174,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{857864ec-ee56-4eed-91c5-2cdd3f2b79f2}">
+          <x14:cfRule type="dataBar" id="{16f3ef7f-fa9b-4996-a283-531f7401421c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8966a9ef-9b77-462a-82d0-710774e7e8e4}">
+          <x14:cfRule type="dataBar" id="{cdf20b77-e35d-4baf-9526-dbf45756b3e3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15178,7 +15192,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c8a1eaa5-fbc3-4e74-8a55-d7e7d49b7b39}">
+          <x14:cfRule type="dataBar" id="{b335a2d5-8c6c-48b8-bb22-56c9fa018db8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15192,7 +15206,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a1553ff7-c963-41db-a4eb-060cb266c493}">
+          <x14:cfRule type="dataBar" id="{85f56e96-1659-4397-b782-a522c479860f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15201,7 +15215,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{54d2ab7f-2484-4842-824a-91524e9333a7}">
+          <x14:cfRule type="dataBar" id="{ee5e62e7-e7fc-4614-a632-dbfb76195043}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15210,7 +15224,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c8d92c69-c33f-4cec-9e82-16cd15bdb6f9}">
+          <x14:cfRule type="dataBar" id="{dbe88aee-28ee-4640-99ac-dae923f86d4d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15221,7 +15235,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4dd509c8-d424-45e9-9bf1-d9a1956683cd}">
+          <x14:cfRule type="dataBar" id="{cf9ebbda-727a-48c5-bc04-aaad3d539b73}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15232,7 +15246,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{681b85f6-03e0-4d0a-adf8-fd61ac5b7f54}">
+          <x14:cfRule type="dataBar" id="{0e6e3902-845d-4b7e-911a-5e9989e92656}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15243,14 +15257,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b2bd90df-74b3-4167-830a-deb981b04b90}">
+          <x14:cfRule type="dataBar" id="{9593fed4-060b-4c6f-a7d0-9280cfa88bd1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7fc3743c-e0a6-4995-a891-1e81217b77a8}">
+          <x14:cfRule type="dataBar" id="{d8fa2be3-0813-4357-8958-c5261e5e1ec5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15261,7 +15275,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c7bc139b-23f2-441e-9a8f-f38fa096f01e}">
+          <x14:cfRule type="dataBar" id="{f502eb5e-6efa-4219-8e08-6caa664df6a6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15275,7 +15289,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55be9825-5a59-4695-917e-7fbd94136f54}">
+          <x14:cfRule type="dataBar" id="{568d3161-e2aa-4f46-a430-41a555d0d84b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15284,7 +15298,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{821cbcce-03b2-41b8-bf60-306c63a31db7}">
+          <x14:cfRule type="dataBar" id="{4d840c12-7a16-473f-85e5-9ad0b150f6b9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15293,7 +15307,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c3edd6a2-a7ae-425c-a753-c82074d930c9}">
+          <x14:cfRule type="dataBar" id="{88a919d7-b070-4ddd-81f4-a594e55cac43}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15304,7 +15318,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{279ffa6a-174d-4dcd-b476-a5e3b058c8ad}">
+          <x14:cfRule type="dataBar" id="{fb877c83-4296-4612-b7c1-5cb7fea610a8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15315,7 +15329,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a3f68245-675c-425c-97d1-ee01bc00089e}">
+          <x14:cfRule type="dataBar" id="{2eee616b-5d81-4ffd-a9d3-0f904459bbbc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15326,14 +15340,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{73b74af1-3502-43fa-b811-8ebc446db6bb}">
+          <x14:cfRule type="dataBar" id="{8e19afb2-df1f-4e51-8df3-3af986d2f116}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4bcde2e6-c787-431b-b57e-79fbcd44ae36}">
+          <x14:cfRule type="dataBar" id="{0f773ae2-57e0-4a86-b5f4-ea3c3eb849db}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15344,7 +15358,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{30f725ff-a7c5-4fac-9f20-85c53ab9c78b}">
+          <x14:cfRule type="dataBar" id="{4f90c8a8-eee9-4dfb-a67a-b32ec7d0176d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15358,7 +15372,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e5d946bc-f65f-4753-8aaf-54d96b48fa1b}">
+          <x14:cfRule type="dataBar" id="{76fc8c7d-be85-4d35-89cf-5944b1675599}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15367,7 +15381,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e29141e9-f053-448c-8aea-f920ed6cccfc}">
+          <x14:cfRule type="dataBar" id="{4dab22e7-06bd-46ec-9041-c38c3183e90a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15376,7 +15390,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f4f42310-c7f8-4ed8-b692-d15529460bd0}">
+          <x14:cfRule type="dataBar" id="{fa6bf814-e24b-4238-98ac-dd528568c051}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15387,7 +15401,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bdf468da-75ef-4389-8434-72b1b71852e1}">
+          <x14:cfRule type="dataBar" id="{cd9daa61-330a-449b-8aee-01afde412bf1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15398,7 +15412,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{99aa3b76-eca0-4c40-965a-a571c2876178}">
+          <x14:cfRule type="dataBar" id="{a04849f9-4210-4ffd-9440-7475f151111c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15409,14 +15423,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a553d35c-6fca-45c9-8400-fe1e8e91235b}">
+          <x14:cfRule type="dataBar" id="{2e4dca19-d764-43b2-9c8e-b5dd48c935f3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ab94e137-781a-4292-a619-0e9775f7f950}">
+          <x14:cfRule type="dataBar" id="{87f83abb-bd4f-4c64-9a34-49483fdfe7e1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15427,7 +15441,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b2bfa5b4-aaf3-4989-9600-981976f7680e}">
+          <x14:cfRule type="dataBar" id="{296a0e4f-c385-4e49-af28-290ad153c631}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15441,7 +15455,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7bb22888-fb1a-4dcf-8eae-71e0afb6059d}">
+          <x14:cfRule type="dataBar" id="{ebe442a4-b976-43b5-a5c1-a241c41ee2ad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15450,7 +15464,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d53ebb90-5617-4cbf-9500-a8ea81fdc68a}">
+          <x14:cfRule type="dataBar" id="{56320c77-cdfb-4926-8288-76b018b10d84}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15459,7 +15473,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{51b1ab5a-1768-4d74-ab51-27f6a09fc5c6}">
+          <x14:cfRule type="dataBar" id="{29e55750-027b-4fed-b5db-36223b4262cb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15470,7 +15484,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{099bf8d8-e202-4caf-94b4-c3daff75adb3}">
+          <x14:cfRule type="dataBar" id="{aa7c311f-15c2-4b7b-943e-161150161323}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15481,7 +15495,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bdbccb95-df11-4074-a44b-a50b8e5d39cb}">
+          <x14:cfRule type="dataBar" id="{fc81220b-6a92-4091-a353-20c0d9a5a60e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15492,14 +15506,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6ca60a51-4139-4837-be21-9324d8221230}">
+          <x14:cfRule type="dataBar" id="{7069645c-30cd-482a-8945-fc1f04461eca}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{66503706-5cf0-4216-8e18-82a648e44121}">
+          <x14:cfRule type="dataBar" id="{898cd7da-c8ea-40f1-8e9a-806d7f6945b0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15510,7 +15524,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c4b615bf-b6c4-4a08-aacf-456a8414d875}">
+          <x14:cfRule type="dataBar" id="{ac14da52-b71c-49e8-8fbc-43025f954510}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15524,7 +15538,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4e5b8569-d4c0-41bc-9e5b-232bd65491c5}">
+          <x14:cfRule type="dataBar" id="{a1684ad2-e18a-4a36-acfd-41b24ffee10c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15536,7 +15550,7 @@
           <xm:sqref>K189:K208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90575078-8f7a-48b6-8a67-24cf13bb7250}">
+          <x14:cfRule type="dataBar" id="{958089b0-ad58-4a94-b7a3-4daf4a5c569c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15548,7 +15562,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b6835af3-426c-4ebc-91c7-26aa8bbbe67d}">
+          <x14:cfRule type="dataBar" id="{379db16a-b4ce-43bd-9b38-3efb5b89835d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15560,7 +15574,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b246a5b6-c193-4512-81eb-243024531375}">
+          <x14:cfRule type="dataBar" id="{32206371-e472-4dda-935c-3d71cdae01f6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15569,7 +15583,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4d2f9a4b-a891-451b-81b9-3725c234cd4b}">
+          <x14:cfRule type="dataBar" id="{3caec8dd-10b4-4d89-b38b-56a2e7852a1c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15578,7 +15592,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{221a659e-2ff3-4667-933f-daaf66ba603e}">
+          <x14:cfRule type="dataBar" id="{ed2952d4-3367-4760-ad47-d39f56c2f996}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15589,7 +15603,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d3009d35-907b-49d9-891b-77b32d6660fa}">
+          <x14:cfRule type="dataBar" id="{8fbcccb9-c29e-4d07-89e1-44e099167717}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15600,7 +15614,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d4b5c87e-8e40-4f02-9c2f-6461feaf5519}">
+          <x14:cfRule type="dataBar" id="{5a390851-ebaf-4c4e-abcf-e93679d7948f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15611,14 +15625,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3330c789-9dd7-490e-a3b7-d88fceaa7261}">
+          <x14:cfRule type="dataBar" id="{6a7c9f3f-25a6-45d5-96fe-2ffbe68284bb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{26a4f0a3-5e14-4531-8767-6c61896eca48}">
+          <x14:cfRule type="dataBar" id="{5301e40d-0761-4284-8b14-37bb679c0b69}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15629,7 +15643,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ece54310-3b8d-4f5e-9280-8a3fe32b12b6}">
+          <x14:cfRule type="dataBar" id="{12f87e8b-f359-4772-bb41-f62d65e8b3dd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15643,7 +15657,7 @@
           <xm:sqref>F69 F79 F89 F99 F109 F119 F129 F139 F149 F159 F169 F179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ce3aa55-dc0e-403a-8076-d5c1ee8c02b2}">
+          <x14:cfRule type="dataBar" id="{75ad03a0-8e72-47ff-a193-7cce0b89aa74}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15652,7 +15666,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{356a31e6-4f7e-4c20-b47e-62922d784229}">
+          <x14:cfRule type="dataBar" id="{c64a43c1-3ae5-40c9-b589-020ca1dd00a5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15664,7 +15678,7 @@
           <xm:sqref>K69:K79 K85:K99 K105:K119 K125:K139 K145:K159 K165:K179 K185:K188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c35d8f4c-11a5-411b-8c4b-82ef2a071a99}">
+          <x14:cfRule type="dataBar" id="{8ec49a28-b370-4fac-b640-1932e2f49933}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15676,7 +15690,7 @@
           <xm:sqref>Y69:Y79 Y85:Y99 Y105:Y122 Y125:Y141 Y145:Y160 Y165:Y179 Y185:Y188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f5914218-5a47-4d79-ba5e-5d8cce336a7a}">
+          <x14:cfRule type="dataBar" id="{4c0fdf8f-d7f6-42a3-b2fb-29c661dda80c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15685,7 +15699,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8187efee-394b-4af3-9d3c-39298600e688}">
+          <x14:cfRule type="dataBar" id="{53bfc2fc-9310-493d-b329-b599172962a6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15697,7 +15711,7 @@
           <xm:sqref>AB69 AB89 AB109 AB129 AB149 AB169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66edc105-c931-4435-a290-10e683b20464}">
+          <x14:cfRule type="dataBar" id="{8ca38345-d480-45da-b8ea-1a005da338e5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15706,7 +15720,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bc8ddd38-d2f0-4b12-ab7e-f0180480a509}">
+          <x14:cfRule type="dataBar" id="{1369e301-62e4-4e1b-a6bd-27b45e60765e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15716,7 +15730,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB122 AB125:AB141 AB145:AB160 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a4726ca8-93a8-42db-bb68-11f5fb3c4de2}">
+          <x14:cfRule type="dataBar" id="{f1ee1300-8afe-4322-8cfe-a1bb78829b73}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15728,7 +15742,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB119 AB125:AB139 AB145:AB159 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d8199597-6d0d-480e-b67d-7c5db10c1433}">
+          <x14:cfRule type="dataBar" id="{23d7eb47-3831-4350-b261-11accb9971ad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15737,7 +15751,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{41029be4-1503-4104-8c1d-c2b92142a685}">
+          <x14:cfRule type="dataBar" id="{6bbb0353-a290-493d-ae69-162ffd534ffe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15749,7 +15763,7 @@
           <xm:sqref>K80:K84 K100:K104 K120:K124 K140:K144 K160:K164 K180:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2307146e-e07d-44e3-bbe7-3bdabc877f93}">
+          <x14:cfRule type="dataBar" id="{3b5b268d-a5a6-48ce-b2c0-b146afbc0214}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15761,7 +15775,7 @@
           <xm:sqref>Y80:Y84 Y100:Y104 Y120:Y124 Y140:Y144 Y160:Y164 Y180:Y184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f55db939-0909-4726-a92d-af2e573ff33f}">
+          <x14:cfRule type="dataBar" id="{a616a604-eb95-4ec3-ad20-8fa099904fda}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15770,7 +15784,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{79d7c617-c934-4852-ae12-d345eda47912}">
+          <x14:cfRule type="dataBar" id="{13e54fe7-4253-4788-8a49-090293778def}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15779,7 +15793,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fb24242f-59e2-4d42-b80d-b823c4ffd229}">
+          <x14:cfRule type="dataBar" id="{fe45dde1-db7d-42b7-81a0-e5ff6cc332a1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15789,7 +15803,7 @@
           <xm:sqref>AB80:AB84 AB100:AB104 AB120:AB124 AB140:AB144 AB160:AB164 AB180:AB184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7c6e6227-d3f3-4f80-ab19-e002897a420a}">
+          <x14:cfRule type="dataBar" id="{0666ce47-5caa-4387-a5bf-b70b7316fef2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15798,7 +15812,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e12dd716-df26-4bdf-aabf-ba5705bd4263}">
+          <x14:cfRule type="dataBar" id="{32d45b66-37c2-4e72-a67f-9555c84aa57d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15807,7 +15821,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b434a534-36c4-4698-99fc-fee06ff6477b}">
+          <x14:cfRule type="dataBar" id="{11039150-8a86-4f61-89ef-0821e94848de}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15819,7 +15833,7 @@
           <xm:sqref>F189 F194 F199 F204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2694520c-7473-4c18-a15a-3601f71796b3}">
+          <x14:cfRule type="dataBar" id="{8916ec62-b8f7-4917-a10d-0449fc292335}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15828,7 +15842,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24645368-5f5b-443c-993c-480f9e73969c}">
+          <x14:cfRule type="dataBar" id="{e36f687b-dca9-47fa-8fd0-60dcd60cba6d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">

--- a/外网端源码/E楼交接班容量报表空模板.xlsx
+++ b/外网端源码/E楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3569,27 +3569,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE211"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.7727272727273" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7685185185185" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1090909090909" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1111111111111" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
     <col min="20" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="12.3363636363636" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.3333333333333" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4156,15 +4156,15 @@
         <v>25</v>
       </c>
       <c r="T14" s="65"/>
-      <c r="U14" s="67">
-        <f>(U13-U12)/100</f>
-        <v>0</v>
+      <c r="U14" s="67" t="e">
+        <f>(U13-U12)/U12</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="V14" s="68"/>
       <c r="W14" s="69"/>
-      <c r="X14" s="67">
-        <f>(X13-X12)/100</f>
-        <v>0</v>
+      <c r="X14" s="67" t="e">
+        <f>(X13-X12)/X12</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="Y14" s="69"/>
       <c r="Z14" s="57"/>
@@ -13860,7 +13860,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e81aa7cb-be2c-473b-9a26-e7ff17abccff}</x14:id>
+          <x14:id>{3932aab8-bd28-4bdc-854d-a557c45adca5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13872,7 +13872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{607366ff-e314-4f9b-857b-061e45830664}</x14:id>
+          <x14:id>{82f100c7-86ea-4e27-90c7-0ddf631a5ddd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13884,7 +13884,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{429644d3-3cfd-4d55-bc6f-dc48fdfb7604}</x14:id>
+          <x14:id>{30e16290-2128-4997-a853-ed535a357b6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13896,7 +13896,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e2414fc-eddf-404e-8064-25908df78843}</x14:id>
+          <x14:id>{56ee5bd4-08ed-49d8-b894-9652ada0974b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13908,7 +13908,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eec50ee7-6dae-4c47-867a-dbc9bf938797}</x14:id>
+          <x14:id>{89d6a018-748d-4749-916e-5011ed51ab29}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13920,7 +13920,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{acc6a71a-c49c-4322-8998-cb4fffe8e619}</x14:id>
+          <x14:id>{2454dee4-1897-4708-bb81-62d13bb5c841}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13932,7 +13932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3b59f97c-9aca-4de8-803d-38e7df80526f}</x14:id>
+          <x14:id>{b5ba81fe-72b9-4525-b69c-6817651d7f15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13944,7 +13944,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{69a90e79-0c6e-48c9-948c-94f497732beb}</x14:id>
+          <x14:id>{3d4edf10-7bdc-4950-be35-c390c3f8bcc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13958,7 +13958,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{999246bd-fcc5-430a-bfaf-dbf0f3c6918d}</x14:id>
+          <x14:id>{6c2132dc-fe1e-4dc5-9a99-964d014fcaff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13970,7 +13970,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8be537db-ecd9-4be6-874a-4ea601f188df}</x14:id>
+          <x14:id>{316b3783-6ee6-4d9d-b8bf-7356ad08fe87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13982,7 +13982,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42acd88f-ff0e-4c13-87f0-38dbe452ce64}</x14:id>
+          <x14:id>{4dc53339-5ed8-4a17-8f5b-a5f578989b92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13994,7 +13994,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{54b3ceb8-aa9f-46f7-99a4-811a48cca552}</x14:id>
+          <x14:id>{db48b74a-c711-4276-8370-d94010b42055}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14006,7 +14006,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4985c0b1-bde7-402c-a10f-1f090d9f2425}</x14:id>
+          <x14:id>{232c19a8-4c02-4895-aa27-bb51a6fc35c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14018,7 +14018,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b332b9c-ab16-44d7-a327-df87c96863e5}</x14:id>
+          <x14:id>{ec68d299-6b47-406e-9f29-9c53e6bb6ff9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14030,7 +14030,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6102e441-d88c-4081-8e0f-81231818b925}</x14:id>
+          <x14:id>{83ad3bc8-74ad-44ee-9eda-745353b88311}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14042,7 +14042,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd76a7cf-6b96-42ad-ab1d-67bc41c18047}</x14:id>
+          <x14:id>{84919dcf-b023-4416-a271-2b10dd110990}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14056,7 +14056,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b319bbf-4f56-4c79-9ac7-eb8a150b9067}</x14:id>
+          <x14:id>{eab74a9e-5ada-4048-a5ce-c0c54f2eca82}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14068,7 +14068,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74ac4359-1f35-4d5f-987d-f54e56ac0890}</x14:id>
+          <x14:id>{1de9a9da-b216-4bb4-803d-85c0da33e6fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14080,7 +14080,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ec2c37c-172f-46cb-b40f-f76a48b255fa}</x14:id>
+          <x14:id>{f83118a6-43f0-4fe9-b2f5-6862b7c67e19}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14092,7 +14092,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a6e33b1-fed1-466a-8612-f3f2c98a5ee0}</x14:id>
+          <x14:id>{956e6e6f-76e2-4674-84ce-93cb6d2b234d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14104,7 +14104,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab429ed2-661b-4a6f-bb5a-44766faa9883}</x14:id>
+          <x14:id>{84b27833-047d-4b47-a68d-c6249f89c0c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14116,7 +14116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16f3ef7f-fa9b-4996-a283-531f7401421c}</x14:id>
+          <x14:id>{5a933331-de08-4b4e-a383-df8e8fbbe3f9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14128,7 +14128,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cdf20b77-e35d-4baf-9526-dbf45756b3e3}</x14:id>
+          <x14:id>{38eb80c4-d27b-4b5f-89dd-7746868ec772}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14140,7 +14140,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b335a2d5-8c6c-48b8-bb22-56c9fa018db8}</x14:id>
+          <x14:id>{d732c76a-457d-465f-97be-f1f54d47c8a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14154,7 +14154,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{85f56e96-1659-4397-b782-a522c479860f}</x14:id>
+          <x14:id>{daa6e485-8c50-4ebf-816e-9027a9bb41ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14166,7 +14166,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee5e62e7-e7fc-4614-a632-dbfb76195043}</x14:id>
+          <x14:id>{c71d4a07-c2f0-4d5c-869c-196d9d8f6d3e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14178,7 +14178,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbe88aee-28ee-4640-99ac-dae923f86d4d}</x14:id>
+          <x14:id>{d1462981-1a27-43ac-acb1-9bfc0c27b85d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14190,7 +14190,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf9ebbda-727a-48c5-bc04-aaad3d539b73}</x14:id>
+          <x14:id>{b57045fa-6969-4813-b6eb-4770c3c20c4c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14202,7 +14202,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e6e3902-845d-4b7e-911a-5e9989e92656}</x14:id>
+          <x14:id>{c1e6ce22-58da-485c-948f-8434ca9c2296}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14214,7 +14214,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9593fed4-060b-4c6f-a7d0-9280cfa88bd1}</x14:id>
+          <x14:id>{6540b8fe-ada5-455d-bd1a-d673ad6642c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14226,7 +14226,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d8fa2be3-0813-4357-8958-c5261e5e1ec5}</x14:id>
+          <x14:id>{81e656f8-8418-4a6a-b137-597d2146b767}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14238,7 +14238,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f502eb5e-6efa-4219-8e08-6caa664df6a6}</x14:id>
+          <x14:id>{967bdf2b-f914-4505-86c5-e12944c276fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14252,7 +14252,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{568d3161-e2aa-4f46-a430-41a555d0d84b}</x14:id>
+          <x14:id>{473f09d8-fcb0-44ab-995a-436bce0508e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14264,7 +14264,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d840c12-7a16-473f-85e5-9ad0b150f6b9}</x14:id>
+          <x14:id>{79cbb222-8cf5-452a-9617-678cf9662b2d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14276,7 +14276,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88a919d7-b070-4ddd-81f4-a594e55cac43}</x14:id>
+          <x14:id>{b2373a7e-9f0a-40fa-8926-ce55a11ce610}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14288,7 +14288,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb877c83-4296-4612-b7c1-5cb7fea610a8}</x14:id>
+          <x14:id>{d4e29cc3-11e0-46cf-a40a-fab2cf25d68b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14300,7 +14300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2eee616b-5d81-4ffd-a9d3-0f904459bbbc}</x14:id>
+          <x14:id>{84aad717-50f3-42c7-b510-cf4c9cad22a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14312,7 +14312,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e19afb2-df1f-4e51-8df3-3af986d2f116}</x14:id>
+          <x14:id>{787ed57b-7ca2-44ae-8f1d-4f486efdc660}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14324,7 +14324,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f773ae2-57e0-4a86-b5f4-ea3c3eb849db}</x14:id>
+          <x14:id>{738c1dc2-8e4f-411f-b37c-755f65f69589}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14336,7 +14336,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f90c8a8-eee9-4dfb-a67a-b32ec7d0176d}</x14:id>
+          <x14:id>{bab48e83-cb98-49ec-b2d5-ce5c991abddb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14350,7 +14350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76fc8c7d-be85-4d35-89cf-5944b1675599}</x14:id>
+          <x14:id>{cf0eb950-2c57-459c-92ce-0e8039b01bed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14362,7 +14362,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4dab22e7-06bd-46ec-9041-c38c3183e90a}</x14:id>
+          <x14:id>{be6139a4-f380-4664-84a4-c3d92b4a6969}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14374,7 +14374,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa6bf814-e24b-4238-98ac-dd528568c051}</x14:id>
+          <x14:id>{c84a2bd8-61d0-4429-90a1-d96450ade3f9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14386,7 +14386,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cd9daa61-330a-449b-8aee-01afde412bf1}</x14:id>
+          <x14:id>{83525fb8-f305-4507-983a-e30926b07b15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14398,7 +14398,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a04849f9-4210-4ffd-9440-7475f151111c}</x14:id>
+          <x14:id>{a6b542d5-971a-413e-b65b-135e83662c46}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14410,7 +14410,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e4dca19-d764-43b2-9c8e-b5dd48c935f3}</x14:id>
+          <x14:id>{984847ba-dadc-4795-8495-410406ddddfc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14422,7 +14422,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{87f83abb-bd4f-4c64-9a34-49483fdfe7e1}</x14:id>
+          <x14:id>{36b76f27-afa0-489f-a87c-ac534300f035}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14434,7 +14434,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{296a0e4f-c385-4e49-af28-290ad153c631}</x14:id>
+          <x14:id>{4805e399-6440-46db-9f68-c6cfc8f49a52}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14448,7 +14448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ebe442a4-b976-43b5-a5c1-a241c41ee2ad}</x14:id>
+          <x14:id>{303abf6a-334a-45ef-be5b-ce4e334978f7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14460,7 +14460,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56320c77-cdfb-4926-8288-76b018b10d84}</x14:id>
+          <x14:id>{f109ee85-9855-4d2f-96f8-7eaf123bdb90}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14472,7 +14472,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29e55750-027b-4fed-b5db-36223b4262cb}</x14:id>
+          <x14:id>{96936257-9a93-4360-86c3-8d45ba6e3298}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14484,7 +14484,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa7c311f-15c2-4b7b-943e-161150161323}</x14:id>
+          <x14:id>{93dad177-fe67-4185-b3e1-cec7751bcff3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14496,7 +14496,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc81220b-6a92-4091-a353-20c0d9a5a60e}</x14:id>
+          <x14:id>{7520bb0e-a1b9-4655-8953-084268910355}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14508,7 +14508,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7069645c-30cd-482a-8945-fc1f04461eca}</x14:id>
+          <x14:id>{5fbeb63a-2be6-4984-bb2d-241cfbcc46a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14520,7 +14520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{898cd7da-c8ea-40f1-8e9a-806d7f6945b0}</x14:id>
+          <x14:id>{2e4fe7e9-0d66-45bf-ad28-17689609d23e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14532,7 +14532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac14da52-b71c-49e8-8fbc-43025f954510}</x14:id>
+          <x14:id>{0148d49e-4ce5-4e6a-928f-27a603f454b4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14546,7 +14546,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1684ad2-e18a-4a36-acfd-41b24ffee10c}</x14:id>
+          <x14:id>{252ef752-38b2-4015-9458-b7a6f39481ca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14560,7 +14560,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{958089b0-ad58-4a94-b7a3-4daf4a5c569c}</x14:id>
+          <x14:id>{70de4c80-f137-4767-a9d2-3a371f115217}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14574,7 +14574,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{379db16a-b4ce-43bd-9b38-3efb5b89835d}</x14:id>
+          <x14:id>{4eb48a5a-e437-42aa-9b82-7625e9c5c00b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14588,7 +14588,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32206371-e472-4dda-935c-3d71cdae01f6}</x14:id>
+          <x14:id>{9d1899f9-9fee-41fd-97fe-9ba7d9623809}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14600,7 +14600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3caec8dd-10b4-4d89-b38b-56a2e7852a1c}</x14:id>
+          <x14:id>{a47feb2d-1b0f-4516-8ec3-f7b5b2b476d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14612,7 +14612,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed2952d4-3367-4760-ad47-d39f56c2f996}</x14:id>
+          <x14:id>{6e5e286f-936d-47d7-8820-ebdeb5f0fc62}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14624,7 +14624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8fbcccb9-c29e-4d07-89e1-44e099167717}</x14:id>
+          <x14:id>{7e0b5292-af90-4dba-83fa-140d62420e38}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14636,7 +14636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a390851-ebaf-4c4e-abcf-e93679d7948f}</x14:id>
+          <x14:id>{4848be0b-423b-4330-b4f0-2537490837aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14648,7 +14648,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a7c9f3f-25a6-45d5-96fe-2ffbe68284bb}</x14:id>
+          <x14:id>{02b83baf-432c-4691-8e53-9ff396208269}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14660,7 +14660,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5301e40d-0761-4284-8b14-37bb679c0b69}</x14:id>
+          <x14:id>{12d1a9e5-fc68-4aba-93fe-89532dff0257}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14672,7 +14672,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12f87e8b-f359-4772-bb41-f62d65e8b3dd}</x14:id>
+          <x14:id>{77e03c3d-2d2f-491e-8813-643cc6475233}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14686,7 +14686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75ad03a0-8e72-47ff-a193-7cce0b89aa74}</x14:id>
+          <x14:id>{ce1c1e0e-2b48-408d-84c9-2246e941f8d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14698,7 +14698,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c64a43c1-3ae5-40c9-b589-020ca1dd00a5}</x14:id>
+          <x14:id>{2bbb31e8-a27d-45cd-becb-593237e21ba1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14712,7 +14712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ec49a28-b370-4fac-b640-1932e2f49933}</x14:id>
+          <x14:id>{8baa8ba9-e80d-4d98-99db-24e10f070edc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14726,7 +14726,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4c0fdf8f-d7f6-42a3-b2fb-29c661dda80c}</x14:id>
+          <x14:id>{4ac8f49d-dfdd-47b1-a7cf-ced3c54475b8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14738,7 +14738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53bfc2fc-9310-493d-b329-b599172962a6}</x14:id>
+          <x14:id>{7f8b76eb-027e-455a-85a7-6d64eb4b557e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14752,7 +14752,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ca38345-d480-45da-b8ea-1a005da338e5}</x14:id>
+          <x14:id>{cd289d4a-878e-4b6a-b89d-2518186354ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14764,7 +14764,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1369e301-62e4-4e1b-a6bd-27b45e60765e}</x14:id>
+          <x14:id>{24e8bc63-5a66-4a93-9be0-66589f270bc0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14778,7 +14778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1ee1300-8afe-4322-8cfe-a1bb78829b73}</x14:id>
+          <x14:id>{c5d43ce1-3cd6-49bf-9ebb-ab8bd60f798d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14792,7 +14792,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23d7eb47-3831-4350-b261-11accb9971ad}</x14:id>
+          <x14:id>{946ea27f-2b5b-4d9b-a937-354f50a03d3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14804,7 +14804,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6bbb0353-a290-493d-ae69-162ffd534ffe}</x14:id>
+          <x14:id>{7dce38d9-78ca-40df-ac21-a9d474963c3c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14818,7 +14818,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3b5b268d-a5a6-48ce-b2c0-b146afbc0214}</x14:id>
+          <x14:id>{d651863c-6c1d-41ff-84d7-5c8922542ccb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14832,7 +14832,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a616a604-eb95-4ec3-ad20-8fa099904fda}</x14:id>
+          <x14:id>{5e2184b8-307c-4008-8412-e49720f5cffc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14844,7 +14844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13e54fe7-4253-4788-8a49-090293778def}</x14:id>
+          <x14:id>{280a2fd3-76b3-416e-a2e0-f32e161fb8b2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14856,7 +14856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe45dde1-db7d-42b7-81a0-e5ff6cc332a1}</x14:id>
+          <x14:id>{b95ed258-f794-4210-952a-b8473379152e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14870,7 +14870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0666ce47-5caa-4387-a5bf-b70b7316fef2}</x14:id>
+          <x14:id>{98411d6a-7ae3-4f9c-a352-d941c53028d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14882,7 +14882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32d45b66-37c2-4e72-a67f-9555c84aa57d}</x14:id>
+          <x14:id>{3c949efe-ba17-40eb-919e-4cef3445fa5c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14894,7 +14894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11039150-8a86-4f61-89ef-0821e94848de}</x14:id>
+          <x14:id>{a424e572-0a6f-48a0-94bf-00f62e290800}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14908,7 +14908,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8916ec62-b8f7-4917-a10d-0449fc292335}</x14:id>
+          <x14:id>{10b01e13-8e55-43ac-ba2e-74307942de61}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14920,7 +14920,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e36f687b-dca9-47fa-8fd0-60dcd60cba6d}</x14:id>
+          <x14:id>{e27ca86d-6af8-41d6-aae3-7dc4b93027c1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14957,7 +14957,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e81aa7cb-be2c-473b-9a26-e7ff17abccff}">
+          <x14:cfRule type="dataBar" id="{3932aab8-bd28-4bdc-854d-a557c45adca5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14966,7 +14966,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{607366ff-e314-4f9b-857b-061e45830664}">
+          <x14:cfRule type="dataBar" id="{82f100c7-86ea-4e27-90c7-0ddf631a5ddd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14975,7 +14975,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{429644d3-3cfd-4d55-bc6f-dc48fdfb7604}">
+          <x14:cfRule type="dataBar" id="{30e16290-2128-4997-a853-ed535a357b6a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14986,7 +14986,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1e2414fc-eddf-404e-8064-25908df78843}">
+          <x14:cfRule type="dataBar" id="{56ee5bd4-08ed-49d8-b894-9652ada0974b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14997,7 +14997,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{eec50ee7-6dae-4c47-867a-dbc9bf938797}">
+          <x14:cfRule type="dataBar" id="{89d6a018-748d-4749-916e-5011ed51ab29}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15008,14 +15008,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{acc6a71a-c49c-4322-8998-cb4fffe8e619}">
+          <x14:cfRule type="dataBar" id="{2454dee4-1897-4708-bb81-62d13bb5c841}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3b59f97c-9aca-4de8-803d-38e7df80526f}">
+          <x14:cfRule type="dataBar" id="{b5ba81fe-72b9-4525-b69c-6817651d7f15}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15026,7 +15026,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{69a90e79-0c6e-48c9-948c-94f497732beb}">
+          <x14:cfRule type="dataBar" id="{3d4edf10-7bdc-4950-be35-c390c3f8bcc9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15040,7 +15040,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{999246bd-fcc5-430a-bfaf-dbf0f3c6918d}">
+          <x14:cfRule type="dataBar" id="{6c2132dc-fe1e-4dc5-9a99-964d014fcaff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15049,7 +15049,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8be537db-ecd9-4be6-874a-4ea601f188df}">
+          <x14:cfRule type="dataBar" id="{316b3783-6ee6-4d9d-b8bf-7356ad08fe87}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15058,7 +15058,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{42acd88f-ff0e-4c13-87f0-38dbe452ce64}">
+          <x14:cfRule type="dataBar" id="{4dc53339-5ed8-4a17-8f5b-a5f578989b92}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15069,7 +15069,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{54b3ceb8-aa9f-46f7-99a4-811a48cca552}">
+          <x14:cfRule type="dataBar" id="{db48b74a-c711-4276-8370-d94010b42055}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15080,7 +15080,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4985c0b1-bde7-402c-a10f-1f090d9f2425}">
+          <x14:cfRule type="dataBar" id="{232c19a8-4c02-4895-aa27-bb51a6fc35c6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15091,14 +15091,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5b332b9c-ab16-44d7-a327-df87c96863e5}">
+          <x14:cfRule type="dataBar" id="{ec68d299-6b47-406e-9f29-9c53e6bb6ff9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6102e441-d88c-4081-8e0f-81231818b925}">
+          <x14:cfRule type="dataBar" id="{83ad3bc8-74ad-44ee-9eda-745353b88311}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15109,7 +15109,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dd76a7cf-6b96-42ad-ab1d-67bc41c18047}">
+          <x14:cfRule type="dataBar" id="{84919dcf-b023-4416-a271-2b10dd110990}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15123,7 +15123,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8b319bbf-4f56-4c79-9ac7-eb8a150b9067}">
+          <x14:cfRule type="dataBar" id="{eab74a9e-5ada-4048-a5ce-c0c54f2eca82}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15132,7 +15132,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{74ac4359-1f35-4d5f-987d-f54e56ac0890}">
+          <x14:cfRule type="dataBar" id="{1de9a9da-b216-4bb4-803d-85c0da33e6fb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15141,7 +15141,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0ec2c37c-172f-46cb-b40f-f76a48b255fa}">
+          <x14:cfRule type="dataBar" id="{f83118a6-43f0-4fe9-b2f5-6862b7c67e19}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15152,7 +15152,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6a6e33b1-fed1-466a-8612-f3f2c98a5ee0}">
+          <x14:cfRule type="dataBar" id="{956e6e6f-76e2-4674-84ce-93cb6d2b234d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15163,7 +15163,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ab429ed2-661b-4a6f-bb5a-44766faa9883}">
+          <x14:cfRule type="dataBar" id="{84b27833-047d-4b47-a68d-c6249f89c0c4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15174,14 +15174,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{16f3ef7f-fa9b-4996-a283-531f7401421c}">
+          <x14:cfRule type="dataBar" id="{5a933331-de08-4b4e-a383-df8e8fbbe3f9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cdf20b77-e35d-4baf-9526-dbf45756b3e3}">
+          <x14:cfRule type="dataBar" id="{38eb80c4-d27b-4b5f-89dd-7746868ec772}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15192,7 +15192,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b335a2d5-8c6c-48b8-bb22-56c9fa018db8}">
+          <x14:cfRule type="dataBar" id="{d732c76a-457d-465f-97be-f1f54d47c8a4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15206,7 +15206,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{85f56e96-1659-4397-b782-a522c479860f}">
+          <x14:cfRule type="dataBar" id="{daa6e485-8c50-4ebf-816e-9027a9bb41ab}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15215,7 +15215,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ee5e62e7-e7fc-4614-a632-dbfb76195043}">
+          <x14:cfRule type="dataBar" id="{c71d4a07-c2f0-4d5c-869c-196d9d8f6d3e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15224,7 +15224,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dbe88aee-28ee-4640-99ac-dae923f86d4d}">
+          <x14:cfRule type="dataBar" id="{d1462981-1a27-43ac-acb1-9bfc0c27b85d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15235,7 +15235,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cf9ebbda-727a-48c5-bc04-aaad3d539b73}">
+          <x14:cfRule type="dataBar" id="{b57045fa-6969-4813-b6eb-4770c3c20c4c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15246,7 +15246,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0e6e3902-845d-4b7e-911a-5e9989e92656}">
+          <x14:cfRule type="dataBar" id="{c1e6ce22-58da-485c-948f-8434ca9c2296}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15257,14 +15257,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9593fed4-060b-4c6f-a7d0-9280cfa88bd1}">
+          <x14:cfRule type="dataBar" id="{6540b8fe-ada5-455d-bd1a-d673ad6642c6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d8fa2be3-0813-4357-8958-c5261e5e1ec5}">
+          <x14:cfRule type="dataBar" id="{81e656f8-8418-4a6a-b137-597d2146b767}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15275,7 +15275,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f502eb5e-6efa-4219-8e08-6caa664df6a6}">
+          <x14:cfRule type="dataBar" id="{967bdf2b-f914-4505-86c5-e12944c276fc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15289,7 +15289,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{568d3161-e2aa-4f46-a430-41a555d0d84b}">
+          <x14:cfRule type="dataBar" id="{473f09d8-fcb0-44ab-995a-436bce0508e9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15298,7 +15298,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4d840c12-7a16-473f-85e5-9ad0b150f6b9}">
+          <x14:cfRule type="dataBar" id="{79cbb222-8cf5-452a-9617-678cf9662b2d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15307,7 +15307,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{88a919d7-b070-4ddd-81f4-a594e55cac43}">
+          <x14:cfRule type="dataBar" id="{b2373a7e-9f0a-40fa-8926-ce55a11ce610}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15318,7 +15318,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fb877c83-4296-4612-b7c1-5cb7fea610a8}">
+          <x14:cfRule type="dataBar" id="{d4e29cc3-11e0-46cf-a40a-fab2cf25d68b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15329,7 +15329,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2eee616b-5d81-4ffd-a9d3-0f904459bbbc}">
+          <x14:cfRule type="dataBar" id="{84aad717-50f3-42c7-b510-cf4c9cad22a4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15340,14 +15340,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8e19afb2-df1f-4e51-8df3-3af986d2f116}">
+          <x14:cfRule type="dataBar" id="{787ed57b-7ca2-44ae-8f1d-4f486efdc660}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0f773ae2-57e0-4a86-b5f4-ea3c3eb849db}">
+          <x14:cfRule type="dataBar" id="{738c1dc2-8e4f-411f-b37c-755f65f69589}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15358,7 +15358,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4f90c8a8-eee9-4dfb-a67a-b32ec7d0176d}">
+          <x14:cfRule type="dataBar" id="{bab48e83-cb98-49ec-b2d5-ce5c991abddb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15372,7 +15372,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{76fc8c7d-be85-4d35-89cf-5944b1675599}">
+          <x14:cfRule type="dataBar" id="{cf0eb950-2c57-459c-92ce-0e8039b01bed}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15381,7 +15381,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4dab22e7-06bd-46ec-9041-c38c3183e90a}">
+          <x14:cfRule type="dataBar" id="{be6139a4-f380-4664-84a4-c3d92b4a6969}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15390,7 +15390,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fa6bf814-e24b-4238-98ac-dd528568c051}">
+          <x14:cfRule type="dataBar" id="{c84a2bd8-61d0-4429-90a1-d96450ade3f9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15401,7 +15401,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cd9daa61-330a-449b-8aee-01afde412bf1}">
+          <x14:cfRule type="dataBar" id="{83525fb8-f305-4507-983a-e30926b07b15}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15412,7 +15412,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a04849f9-4210-4ffd-9440-7475f151111c}">
+          <x14:cfRule type="dataBar" id="{a6b542d5-971a-413e-b65b-135e83662c46}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15423,14 +15423,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2e4dca19-d764-43b2-9c8e-b5dd48c935f3}">
+          <x14:cfRule type="dataBar" id="{984847ba-dadc-4795-8495-410406ddddfc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{87f83abb-bd4f-4c64-9a34-49483fdfe7e1}">
+          <x14:cfRule type="dataBar" id="{36b76f27-afa0-489f-a87c-ac534300f035}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15441,7 +15441,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{296a0e4f-c385-4e49-af28-290ad153c631}">
+          <x14:cfRule type="dataBar" id="{4805e399-6440-46db-9f68-c6cfc8f49a52}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15455,7 +15455,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ebe442a4-b976-43b5-a5c1-a241c41ee2ad}">
+          <x14:cfRule type="dataBar" id="{303abf6a-334a-45ef-be5b-ce4e334978f7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15464,7 +15464,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{56320c77-cdfb-4926-8288-76b018b10d84}">
+          <x14:cfRule type="dataBar" id="{f109ee85-9855-4d2f-96f8-7eaf123bdb90}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15473,7 +15473,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{29e55750-027b-4fed-b5db-36223b4262cb}">
+          <x14:cfRule type="dataBar" id="{96936257-9a93-4360-86c3-8d45ba6e3298}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15484,7 +15484,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aa7c311f-15c2-4b7b-943e-161150161323}">
+          <x14:cfRule type="dataBar" id="{93dad177-fe67-4185-b3e1-cec7751bcff3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15495,7 +15495,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fc81220b-6a92-4091-a353-20c0d9a5a60e}">
+          <x14:cfRule type="dataBar" id="{7520bb0e-a1b9-4655-8953-084268910355}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15506,14 +15506,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7069645c-30cd-482a-8945-fc1f04461eca}">
+          <x14:cfRule type="dataBar" id="{5fbeb63a-2be6-4984-bb2d-241cfbcc46a5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{898cd7da-c8ea-40f1-8e9a-806d7f6945b0}">
+          <x14:cfRule type="dataBar" id="{2e4fe7e9-0d66-45bf-ad28-17689609d23e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15524,7 +15524,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ac14da52-b71c-49e8-8fbc-43025f954510}">
+          <x14:cfRule type="dataBar" id="{0148d49e-4ce5-4e6a-928f-27a603f454b4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15538,7 +15538,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a1684ad2-e18a-4a36-acfd-41b24ffee10c}">
+          <x14:cfRule type="dataBar" id="{252ef752-38b2-4015-9458-b7a6f39481ca}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15550,7 +15550,7 @@
           <xm:sqref>K189:K208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{958089b0-ad58-4a94-b7a3-4daf4a5c569c}">
+          <x14:cfRule type="dataBar" id="{70de4c80-f137-4767-a9d2-3a371f115217}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15562,7 +15562,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{379db16a-b4ce-43bd-9b38-3efb5b89835d}">
+          <x14:cfRule type="dataBar" id="{4eb48a5a-e437-42aa-9b82-7625e9c5c00b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15574,7 +15574,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32206371-e472-4dda-935c-3d71cdae01f6}">
+          <x14:cfRule type="dataBar" id="{9d1899f9-9fee-41fd-97fe-9ba7d9623809}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15583,7 +15583,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3caec8dd-10b4-4d89-b38b-56a2e7852a1c}">
+          <x14:cfRule type="dataBar" id="{a47feb2d-1b0f-4516-8ec3-f7b5b2b476d4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15592,7 +15592,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ed2952d4-3367-4760-ad47-d39f56c2f996}">
+          <x14:cfRule type="dataBar" id="{6e5e286f-936d-47d7-8820-ebdeb5f0fc62}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15603,7 +15603,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8fbcccb9-c29e-4d07-89e1-44e099167717}">
+          <x14:cfRule type="dataBar" id="{7e0b5292-af90-4dba-83fa-140d62420e38}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15614,7 +15614,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5a390851-ebaf-4c4e-abcf-e93679d7948f}">
+          <x14:cfRule type="dataBar" id="{4848be0b-423b-4330-b4f0-2537490837aa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15625,14 +15625,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6a7c9f3f-25a6-45d5-96fe-2ffbe68284bb}">
+          <x14:cfRule type="dataBar" id="{02b83baf-432c-4691-8e53-9ff396208269}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5301e40d-0761-4284-8b14-37bb679c0b69}">
+          <x14:cfRule type="dataBar" id="{12d1a9e5-fc68-4aba-93fe-89532dff0257}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15643,7 +15643,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{12f87e8b-f359-4772-bb41-f62d65e8b3dd}">
+          <x14:cfRule type="dataBar" id="{77e03c3d-2d2f-491e-8813-643cc6475233}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15657,7 +15657,7 @@
           <xm:sqref>F69 F79 F89 F99 F109 F119 F129 F139 F149 F159 F169 F179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75ad03a0-8e72-47ff-a193-7cce0b89aa74}">
+          <x14:cfRule type="dataBar" id="{ce1c1e0e-2b48-408d-84c9-2246e941f8d5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15666,7 +15666,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c64a43c1-3ae5-40c9-b589-020ca1dd00a5}">
+          <x14:cfRule type="dataBar" id="{2bbb31e8-a27d-45cd-becb-593237e21ba1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15678,7 +15678,7 @@
           <xm:sqref>K69:K79 K85:K99 K105:K119 K125:K139 K145:K159 K165:K179 K185:K188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ec49a28-b370-4fac-b640-1932e2f49933}">
+          <x14:cfRule type="dataBar" id="{8baa8ba9-e80d-4d98-99db-24e10f070edc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15690,7 +15690,7 @@
           <xm:sqref>Y69:Y79 Y85:Y99 Y105:Y122 Y125:Y141 Y145:Y160 Y165:Y179 Y185:Y188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4c0fdf8f-d7f6-42a3-b2fb-29c661dda80c}">
+          <x14:cfRule type="dataBar" id="{4ac8f49d-dfdd-47b1-a7cf-ced3c54475b8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15699,7 +15699,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{53bfc2fc-9310-493d-b329-b599172962a6}">
+          <x14:cfRule type="dataBar" id="{7f8b76eb-027e-455a-85a7-6d64eb4b557e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15711,7 +15711,7 @@
           <xm:sqref>AB69 AB89 AB109 AB129 AB149 AB169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ca38345-d480-45da-b8ea-1a005da338e5}">
+          <x14:cfRule type="dataBar" id="{cd289d4a-878e-4b6a-b89d-2518186354ec}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15720,7 +15720,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1369e301-62e4-4e1b-a6bd-27b45e60765e}">
+          <x14:cfRule type="dataBar" id="{24e8bc63-5a66-4a93-9be0-66589f270bc0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15730,7 +15730,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB122 AB125:AB141 AB145:AB160 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f1ee1300-8afe-4322-8cfe-a1bb78829b73}">
+          <x14:cfRule type="dataBar" id="{c5d43ce1-3cd6-49bf-9ebb-ab8bd60f798d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15742,7 +15742,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB119 AB125:AB139 AB145:AB159 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23d7eb47-3831-4350-b261-11accb9971ad}">
+          <x14:cfRule type="dataBar" id="{946ea27f-2b5b-4d9b-a937-354f50a03d3a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15751,7 +15751,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6bbb0353-a290-493d-ae69-162ffd534ffe}">
+          <x14:cfRule type="dataBar" id="{7dce38d9-78ca-40df-ac21-a9d474963c3c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15763,7 +15763,7 @@
           <xm:sqref>K80:K84 K100:K104 K120:K124 K140:K144 K160:K164 K180:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3b5b268d-a5a6-48ce-b2c0-b146afbc0214}">
+          <x14:cfRule type="dataBar" id="{d651863c-6c1d-41ff-84d7-5c8922542ccb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15775,7 +15775,7 @@
           <xm:sqref>Y80:Y84 Y100:Y104 Y120:Y124 Y140:Y144 Y160:Y164 Y180:Y184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a616a604-eb95-4ec3-ad20-8fa099904fda}">
+          <x14:cfRule type="dataBar" id="{5e2184b8-307c-4008-8412-e49720f5cffc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15784,7 +15784,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{13e54fe7-4253-4788-8a49-090293778def}">
+          <x14:cfRule type="dataBar" id="{280a2fd3-76b3-416e-a2e0-f32e161fb8b2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15793,7 +15793,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fe45dde1-db7d-42b7-81a0-e5ff6cc332a1}">
+          <x14:cfRule type="dataBar" id="{b95ed258-f794-4210-952a-b8473379152e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15803,7 +15803,7 @@
           <xm:sqref>AB80:AB84 AB100:AB104 AB120:AB124 AB140:AB144 AB160:AB164 AB180:AB184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0666ce47-5caa-4387-a5bf-b70b7316fef2}">
+          <x14:cfRule type="dataBar" id="{98411d6a-7ae3-4f9c-a352-d941c53028d0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15812,7 +15812,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{32d45b66-37c2-4e72-a67f-9555c84aa57d}">
+          <x14:cfRule type="dataBar" id="{3c949efe-ba17-40eb-919e-4cef3445fa5c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15821,7 +15821,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{11039150-8a86-4f61-89ef-0821e94848de}">
+          <x14:cfRule type="dataBar" id="{a424e572-0a6f-48a0-94bf-00f62e290800}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15833,7 +15833,7 @@
           <xm:sqref>F189 F194 F199 F204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8916ec62-b8f7-4917-a10d-0449fc292335}">
+          <x14:cfRule type="dataBar" id="{10b01e13-8e55-43ac-ba2e-74307942de61}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15842,7 +15842,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e36f687b-dca9-47fa-8fd0-60dcd60cba6d}">
+          <x14:cfRule type="dataBar" id="{e27ca86d-6af8-41d6-aae3-7dc4b93027c1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15863,12 +15863,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/E楼交接班容量报表空模板.xlsx
+++ b/外网端源码/E楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="22020"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="493">
   <si>
     <t>班次</t>
   </si>
@@ -3569,27 +3569,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE211"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="11.7685185185185" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7727272727273" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1111111111111" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1090909090909" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
     <col min="20" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.3363636363636" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4594,7 +4594,10 @@
       <c r="AB24" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="AC24" s="89"/>
+      <c r="AC24" s="89" t="e">
+        <f>AC29/O59*24</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AD24" s="51"/>
       <c r="AE24" s="52"/>
     </row>
@@ -4622,11 +4625,15 @@
       <c r="K25" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="L25" s="87"/>
+      <c r="L25" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="M25" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="N25" s="87"/>
+      <c r="N25" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="O25" s="54"/>
       <c r="P25" s="90" t="s">
         <v>74</v>
@@ -4649,11 +4656,15 @@
       <c r="X25" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="Y25" s="87"/>
+      <c r="Y25" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="Z25" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="AA25" s="87"/>
+      <c r="AA25" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="AB25" s="88" t="s">
         <v>77</v>
       </c>
@@ -4687,7 +4698,9 @@
       <c r="K26" s="83" t="s">
         <v>82</v>
       </c>
-      <c r="L26" s="73"/>
+      <c r="L26" s="73" t="s">
+        <v>15</v>
+      </c>
       <c r="M26" s="83" t="s">
         <v>83</v>
       </c>
@@ -4719,7 +4732,9 @@
       <c r="X26" s="83" t="s">
         <v>82</v>
       </c>
-      <c r="Y26" s="93"/>
+      <c r="Y26" s="93" t="s">
+        <v>15</v>
+      </c>
       <c r="Z26" s="83" t="s">
         <v>83</v>
       </c>
@@ -4799,13 +4814,15 @@
       <c r="K28" s="83" t="s">
         <v>88</v>
       </c>
-      <c r="L28" s="87"/>
+      <c r="L28" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="M28" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="N28" s="87">
+      <c r="N28" s="87" t="e">
         <f>N25-N26</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O28" s="54"/>
       <c r="P28" s="83" t="s">
@@ -4829,13 +4846,15 @@
       <c r="X28" s="83" t="s">
         <v>88</v>
       </c>
-      <c r="Y28" s="100"/>
+      <c r="Y28" s="100" t="s">
+        <v>15</v>
+      </c>
       <c r="Z28" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="AA28" s="87">
+      <c r="AA28" s="87" t="e">
         <f>AA25-AA26</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AB28" s="88" t="s">
         <v>90</v>
@@ -4866,11 +4885,15 @@
       <c r="K29" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="L29" s="87"/>
+      <c r="L29" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="M29" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="N29" s="87"/>
+      <c r="N29" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="O29" s="54"/>
       <c r="P29" s="83" t="s">
         <v>91</v>
@@ -4891,11 +4914,15 @@
       <c r="X29" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="Y29" s="87"/>
+      <c r="Y29" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="Z29" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="AA29" s="87"/>
+      <c r="AA29" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="AB29" s="88" t="s">
         <v>96</v>
       </c>
@@ -4928,14 +4955,16 @@
       <c r="K30" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="L30" s="73">
+      <c r="L30" s="73" t="e">
         <f>L29-L25</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M30" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="N30" s="87"/>
+      <c r="N30" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="O30" s="54"/>
       <c r="P30" s="83" t="s">
         <v>97</v>
@@ -4956,14 +4985,16 @@
       <c r="X30" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="Y30" s="73">
+      <c r="Y30" s="73" t="e">
         <f>Y29-Y25</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z30" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="AA30" s="87"/>
+      <c r="AA30" s="87" t="s">
+        <v>15</v>
+      </c>
       <c r="AB30" s="101" t="s">
         <v>102</v>
       </c>
@@ -4993,9 +5024,9 @@
       <c r="M31" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="N31" s="73">
+      <c r="N31" s="73" t="e">
         <f>N29-N30</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O31" s="54"/>
       <c r="P31" s="83" t="s">
@@ -5017,9 +5048,9 @@
       <c r="Z31" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="AA31" s="73">
+      <c r="AA31" s="73" t="e">
         <f>AA29-AA30</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AE31" s="46"/>
     </row>
@@ -5186,11 +5217,15 @@
       <c r="K35" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="L35" s="105"/>
+      <c r="L35" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="M35" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="N35" s="106"/>
+      <c r="N35" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="O35" s="54"/>
       <c r="P35" s="104" t="s">
         <v>74</v>
@@ -5213,11 +5248,15 @@
       <c r="X35" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="Y35" s="105"/>
+      <c r="Y35" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="Z35" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="AA35" s="105"/>
+      <c r="AA35" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="AB35" s="88" t="s">
         <v>108</v>
       </c>
@@ -5257,7 +5296,9 @@
       <c r="K36" s="103" t="s">
         <v>82</v>
       </c>
-      <c r="L36" s="105"/>
+      <c r="L36" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="M36" s="103" t="s">
         <v>83</v>
       </c>
@@ -5293,7 +5334,9 @@
       <c r="X36" s="103" t="s">
         <v>82</v>
       </c>
-      <c r="Y36" s="105"/>
+      <c r="Y36" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="Z36" s="103" t="s">
         <v>83</v>
       </c>
@@ -5379,13 +5422,15 @@
       <c r="K38" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="L38" s="105"/>
+      <c r="L38" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="M38" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="N38" s="106">
+      <c r="N38" s="106" t="e">
         <f>N35-N36</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O38" s="54"/>
       <c r="P38" s="103" t="s">
@@ -5413,13 +5458,15 @@
       <c r="X38" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="Y38" s="105"/>
+      <c r="Y38" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="Z38" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="AA38" s="105">
+      <c r="AA38" s="105" t="e">
         <f>AA35-AA36</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AB38" s="88" t="s">
         <v>111</v>
@@ -5456,7 +5503,9 @@
       <c r="K39" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="L39" s="105"/>
+      <c r="L39" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="M39" s="103" t="s">
         <v>95</v>
       </c>
@@ -5487,11 +5536,15 @@
       <c r="X39" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="Y39" s="105"/>
+      <c r="Y39" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="Z39" s="103" t="s">
         <v>95</v>
       </c>
-      <c r="AA39" s="105"/>
+      <c r="AA39" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="AB39" s="88" t="s">
         <v>113</v>
       </c>
@@ -5527,9 +5580,9 @@
       <c r="K40" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="L40" s="105">
+      <c r="L40" s="105" t="e">
         <f>L39-L35</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M40" s="103" t="s">
         <v>101</v>
@@ -5561,14 +5614,16 @@
       <c r="X40" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="Y40" s="105">
+      <c r="Y40" s="105" t="e">
         <f>Y39-Y35</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z40" s="103" t="s">
         <v>101</v>
       </c>
-      <c r="AA40" s="105"/>
+      <c r="AA40" s="105" t="s">
+        <v>15</v>
+      </c>
       <c r="AB40" s="88" t="s">
         <v>115</v>
       </c>
@@ -5628,9 +5683,9 @@
       <c r="Z41" s="103" t="s">
         <v>105</v>
       </c>
-      <c r="AA41" s="105">
+      <c r="AA41" s="105" t="e">
         <f>AA39-AA40</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AB41" s="80"/>
       <c r="AC41" s="81"/>
@@ -13860,7 +13915,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3932aab8-bd28-4bdc-854d-a557c45adca5}</x14:id>
+          <x14:id>{2af5cd9a-e609-4f7c-912f-2a64ab7edb53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13872,7 +13927,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82f100c7-86ea-4e27-90c7-0ddf631a5ddd}</x14:id>
+          <x14:id>{e1edc20c-7cd0-4e1c-b058-c4141b8aaada}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13884,7 +13939,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30e16290-2128-4997-a853-ed535a357b6a}</x14:id>
+          <x14:id>{fde453e9-61b4-4e9c-bf43-d053085f8366}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13896,7 +13951,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56ee5bd4-08ed-49d8-b894-9652ada0974b}</x14:id>
+          <x14:id>{e2ef6c84-0182-43cc-9c68-466d2ccbd140}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13908,7 +13963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89d6a018-748d-4749-916e-5011ed51ab29}</x14:id>
+          <x14:id>{594178f1-6b37-433a-8fed-72be2cda9a2a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13920,7 +13975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2454dee4-1897-4708-bb81-62d13bb5c841}</x14:id>
+          <x14:id>{be01c605-0e0e-4610-95af-52cb573f7dac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13932,7 +13987,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5ba81fe-72b9-4525-b69c-6817651d7f15}</x14:id>
+          <x14:id>{95f320f7-a19b-4c4d-ac27-dd48d7f6546e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13944,7 +13999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d4edf10-7bdc-4950-be35-c390c3f8bcc9}</x14:id>
+          <x14:id>{c922679c-7cda-4773-98f2-af4ab5b84258}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13958,7 +14013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6c2132dc-fe1e-4dc5-9a99-964d014fcaff}</x14:id>
+          <x14:id>{674c4bfd-a343-4f05-bfc4-08aa2cd1d93b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13970,7 +14025,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{316b3783-6ee6-4d9d-b8bf-7356ad08fe87}</x14:id>
+          <x14:id>{04325fbc-ee28-400c-9773-9267cd42f8ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13982,7 +14037,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4dc53339-5ed8-4a17-8f5b-a5f578989b92}</x14:id>
+          <x14:id>{1daf9e4c-a7a1-4476-be49-648097c72bae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13994,7 +14049,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db48b74a-c711-4276-8370-d94010b42055}</x14:id>
+          <x14:id>{71e1827a-705a-4feb-a74c-a5ed4134e298}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14006,7 +14061,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{232c19a8-4c02-4895-aa27-bb51a6fc35c6}</x14:id>
+          <x14:id>{8e2af315-4334-4320-b4d7-6f82ece95ea1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14018,7 +14073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec68d299-6b47-406e-9f29-9c53e6bb6ff9}</x14:id>
+          <x14:id>{3eb92b5f-d1e9-4c6e-8aaf-322e1b7b5a21}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14030,7 +14085,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83ad3bc8-74ad-44ee-9eda-745353b88311}</x14:id>
+          <x14:id>{4208ddda-32e4-41ff-9fcf-ff8311863f7f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14042,7 +14097,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84919dcf-b023-4416-a271-2b10dd110990}</x14:id>
+          <x14:id>{8601291a-a086-4715-8860-f31b59cd7fcc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14056,7 +14111,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eab74a9e-5ada-4048-a5ce-c0c54f2eca82}</x14:id>
+          <x14:id>{79703102-f7bc-4916-ab26-7c824f1a09bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14068,7 +14123,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1de9a9da-b216-4bb4-803d-85c0da33e6fb}</x14:id>
+          <x14:id>{70d905b2-f8f1-475e-98ec-6bab869b0153}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14080,7 +14135,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f83118a6-43f0-4fe9-b2f5-6862b7c67e19}</x14:id>
+          <x14:id>{732feee0-9503-4545-9bb0-6ef18ca4d86e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14092,7 +14147,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{956e6e6f-76e2-4674-84ce-93cb6d2b234d}</x14:id>
+          <x14:id>{582cb6c3-bce4-485a-af40-5621fe96cda7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14104,7 +14159,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84b27833-047d-4b47-a68d-c6249f89c0c4}</x14:id>
+          <x14:id>{40b03740-81b0-46aa-8ccc-eb9acd4f48f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14116,7 +14171,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a933331-de08-4b4e-a383-df8e8fbbe3f9}</x14:id>
+          <x14:id>{80f4ddd0-14d6-4829-80a4-af7c74b08880}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14128,7 +14183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38eb80c4-d27b-4b5f-89dd-7746868ec772}</x14:id>
+          <x14:id>{f83528e2-45f3-4dae-b4d2-2b3258f1fca3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14140,7 +14195,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d732c76a-457d-465f-97be-f1f54d47c8a4}</x14:id>
+          <x14:id>{d9570ff2-1f61-4e6d-a13d-ab56f9d440aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14154,7 +14209,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{daa6e485-8c50-4ebf-816e-9027a9bb41ab}</x14:id>
+          <x14:id>{653e19e9-1c0b-43d6-8021-7d4e7d296586}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14166,7 +14221,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c71d4a07-c2f0-4d5c-869c-196d9d8f6d3e}</x14:id>
+          <x14:id>{34fb31ec-f745-4105-a219-63c0c31f5654}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14178,7 +14233,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1462981-1a27-43ac-acb1-9bfc0c27b85d}</x14:id>
+          <x14:id>{f5b9b82d-2dc6-4f4f-842a-feca292acc72}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14190,7 +14245,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b57045fa-6969-4813-b6eb-4770c3c20c4c}</x14:id>
+          <x14:id>{29964e06-6124-4014-9a04-0730df4c927d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14202,7 +14257,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1e6ce22-58da-485c-948f-8434ca9c2296}</x14:id>
+          <x14:id>{fcb19eef-6d84-47ee-b0f5-ffb973a51c8f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14214,7 +14269,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6540b8fe-ada5-455d-bd1a-d673ad6642c6}</x14:id>
+          <x14:id>{67d9ef26-3ca1-4ff8-a20a-536447bc74ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14226,7 +14281,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81e656f8-8418-4a6a-b137-597d2146b767}</x14:id>
+          <x14:id>{d19c5c79-536b-44ff-919b-30125c2d60fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14238,7 +14293,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{967bdf2b-f914-4505-86c5-e12944c276fc}</x14:id>
+          <x14:id>{f6c6b123-1958-45cc-9c13-e7eb38b1443e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14252,7 +14307,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{473f09d8-fcb0-44ab-995a-436bce0508e9}</x14:id>
+          <x14:id>{f14934f0-c390-43b3-9d66-befb0bafdfee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14264,7 +14319,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79cbb222-8cf5-452a-9617-678cf9662b2d}</x14:id>
+          <x14:id>{daf9c9df-f822-4c40-b586-1736d5170e2e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14276,7 +14331,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2373a7e-9f0a-40fa-8926-ce55a11ce610}</x14:id>
+          <x14:id>{7a501ce3-7d04-4f90-b7dc-6aef602633af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14288,7 +14343,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4e29cc3-11e0-46cf-a40a-fab2cf25d68b}</x14:id>
+          <x14:id>{c65507bf-7a8c-4a11-adde-38b095257331}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14300,7 +14355,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84aad717-50f3-42c7-b510-cf4c9cad22a4}</x14:id>
+          <x14:id>{12eccc52-699f-4059-a3d4-d09ee9a7aba0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14312,7 +14367,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{787ed57b-7ca2-44ae-8f1d-4f486efdc660}</x14:id>
+          <x14:id>{c4c2c1cf-699f-4f67-bf12-53c88fd55ee2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14324,7 +14379,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{738c1dc2-8e4f-411f-b37c-755f65f69589}</x14:id>
+          <x14:id>{55c1532c-4430-4769-8d25-041f263d01fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14336,7 +14391,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bab48e83-cb98-49ec-b2d5-ce5c991abddb}</x14:id>
+          <x14:id>{22f0bd7f-13b1-4405-b82d-623e1c158f08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14350,7 +14405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf0eb950-2c57-459c-92ce-0e8039b01bed}</x14:id>
+          <x14:id>{fa7872e1-012f-410f-b3af-bb94a7759ec7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14362,7 +14417,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be6139a4-f380-4664-84a4-c3d92b4a6969}</x14:id>
+          <x14:id>{97bcde2c-2709-49af-882f-794ae033524b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14374,7 +14429,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c84a2bd8-61d0-4429-90a1-d96450ade3f9}</x14:id>
+          <x14:id>{967ced90-775e-4af3-bbfa-0b0c35ee52ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14386,7 +14441,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83525fb8-f305-4507-983a-e30926b07b15}</x14:id>
+          <x14:id>{c1291044-48e4-491c-b7d2-ed73599fa36a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14398,7 +14453,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6b542d5-971a-413e-b65b-135e83662c46}</x14:id>
+          <x14:id>{6ad17153-bccc-4a64-8d64-5069c01857ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14410,7 +14465,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{984847ba-dadc-4795-8495-410406ddddfc}</x14:id>
+          <x14:id>{f9b2f6ce-0944-47b7-b8fb-e2832dae43e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14422,7 +14477,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{36b76f27-afa0-489f-a87c-ac534300f035}</x14:id>
+          <x14:id>{b2d5b9a7-125d-4f08-957c-81878b7dea53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14434,7 +14489,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4805e399-6440-46db-9f68-c6cfc8f49a52}</x14:id>
+          <x14:id>{75d32736-baf4-4491-b888-a80ebf6895a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14448,7 +14503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{303abf6a-334a-45ef-be5b-ce4e334978f7}</x14:id>
+          <x14:id>{aae03f9f-2b9c-4700-881c-a41ad5a14e8e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14460,7 +14515,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f109ee85-9855-4d2f-96f8-7eaf123bdb90}</x14:id>
+          <x14:id>{553f68ca-f4ac-49cd-96b0-252679f3fef7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14472,7 +14527,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{96936257-9a93-4360-86c3-8d45ba6e3298}</x14:id>
+          <x14:id>{f29dcbec-0337-4ca6-a5a7-078ed53c0452}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14484,7 +14539,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93dad177-fe67-4185-b3e1-cec7751bcff3}</x14:id>
+          <x14:id>{a49f2e55-b1b1-4003-b753-9abbc51a8173}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14496,7 +14551,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7520bb0e-a1b9-4655-8953-084268910355}</x14:id>
+          <x14:id>{edafc9bc-a3e6-4a4e-ac17-fe3e3aed3d40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14508,7 +14563,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5fbeb63a-2be6-4984-bb2d-241cfbcc46a5}</x14:id>
+          <x14:id>{d879668f-7c19-4867-8cea-ffa95f7d9dad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14520,7 +14575,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e4fe7e9-0d66-45bf-ad28-17689609d23e}</x14:id>
+          <x14:id>{0c9e808e-3ce4-41d9-b9e5-4c60b73da797}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14532,7 +14587,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0148d49e-4ce5-4e6a-928f-27a603f454b4}</x14:id>
+          <x14:id>{f9cbfd66-fa8e-4cea-8c3f-730e2236fae6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14546,7 +14601,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{252ef752-38b2-4015-9458-b7a6f39481ca}</x14:id>
+          <x14:id>{6beeb1de-1a5f-4dee-81ca-137fc0601559}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14560,7 +14615,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70de4c80-f137-4767-a9d2-3a371f115217}</x14:id>
+          <x14:id>{48d84d18-b2eb-48e7-875c-0b8297d71a17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14574,7 +14629,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4eb48a5a-e437-42aa-9b82-7625e9c5c00b}</x14:id>
+          <x14:id>{2e49122d-cf81-4e2f-ad3c-6d2b27042abb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14588,7 +14643,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d1899f9-9fee-41fd-97fe-9ba7d9623809}</x14:id>
+          <x14:id>{763c1bb4-e953-472f-9465-9bdd71bed98c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14600,7 +14655,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a47feb2d-1b0f-4516-8ec3-f7b5b2b476d4}</x14:id>
+          <x14:id>{76dd35f7-5423-4910-adc6-9c71d036f0e2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14612,7 +14667,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e5e286f-936d-47d7-8820-ebdeb5f0fc62}</x14:id>
+          <x14:id>{c0d8baab-7b0d-4df9-abef-7a8de6205fa0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14624,7 +14679,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e0b5292-af90-4dba-83fa-140d62420e38}</x14:id>
+          <x14:id>{03fd9d7a-2e64-4d01-9696-92c12d9a6084}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14636,7 +14691,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4848be0b-423b-4330-b4f0-2537490837aa}</x14:id>
+          <x14:id>{b2f4e5ba-b542-4c12-86ce-efd2bb8c0f8e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14648,7 +14703,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{02b83baf-432c-4691-8e53-9ff396208269}</x14:id>
+          <x14:id>{ce794363-64f0-47bc-8266-ba0d0bdda76d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14660,7 +14715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12d1a9e5-fc68-4aba-93fe-89532dff0257}</x14:id>
+          <x14:id>{882f8a97-1033-4b3b-b8af-abb28d9744ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14672,7 +14727,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77e03c3d-2d2f-491e-8813-643cc6475233}</x14:id>
+          <x14:id>{f881801f-d19c-4b87-b293-6ca372630341}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14686,7 +14741,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce1c1e0e-2b48-408d-84c9-2246e941f8d5}</x14:id>
+          <x14:id>{bbfaa7a7-6967-4c82-a231-a35df6bd90c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14698,7 +14753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2bbb31e8-a27d-45cd-becb-593237e21ba1}</x14:id>
+          <x14:id>{3d11fd74-fa72-4380-8dd3-c2615c82f20b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14712,7 +14767,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8baa8ba9-e80d-4d98-99db-24e10f070edc}</x14:id>
+          <x14:id>{0453a3ce-4f05-43b7-b579-0b81cf798885}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14726,7 +14781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ac8f49d-dfdd-47b1-a7cf-ced3c54475b8}</x14:id>
+          <x14:id>{ace7eecc-7445-4a71-9da4-5fdc18c9125d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14738,7 +14793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f8b76eb-027e-455a-85a7-6d64eb4b557e}</x14:id>
+          <x14:id>{5bbee154-e071-42b6-9cc9-2cdbc4007784}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14752,7 +14807,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cd289d4a-878e-4b6a-b89d-2518186354ec}</x14:id>
+          <x14:id>{98ac6c31-4136-45c1-a36b-9b341cc87b37}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14764,7 +14819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24e8bc63-5a66-4a93-9be0-66589f270bc0}</x14:id>
+          <x14:id>{a21dfa89-d55f-4e78-9806-ec7e0a7eaafc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14778,7 +14833,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5d43ce1-3cd6-49bf-9ebb-ab8bd60f798d}</x14:id>
+          <x14:id>{9e6c3b43-c290-4b3d-880b-14e317420c1a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14792,7 +14847,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{946ea27f-2b5b-4d9b-a937-354f50a03d3a}</x14:id>
+          <x14:id>{1bd3d8a2-60b4-42ff-befd-bdd6e86fd70f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14804,7 +14859,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7dce38d9-78ca-40df-ac21-a9d474963c3c}</x14:id>
+          <x14:id>{24820b95-1715-4b32-b953-2083a4449190}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14818,7 +14873,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d651863c-6c1d-41ff-84d7-5c8922542ccb}</x14:id>
+          <x14:id>{51135e84-3859-4254-9f29-a142b75f6d4f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14832,7 +14887,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e2184b8-307c-4008-8412-e49720f5cffc}</x14:id>
+          <x14:id>{6f9e9af7-0540-4dc6-8707-9aa58b293d4d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14844,7 +14899,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{280a2fd3-76b3-416e-a2e0-f32e161fb8b2}</x14:id>
+          <x14:id>{29797952-4392-4302-a531-b32a59ee9214}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14856,7 +14911,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b95ed258-f794-4210-952a-b8473379152e}</x14:id>
+          <x14:id>{6fd162f3-5a2b-483c-8ecb-9b2a43da661a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14870,7 +14925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98411d6a-7ae3-4f9c-a352-d941c53028d0}</x14:id>
+          <x14:id>{ceb07929-f5b0-45be-acd9-3d08661b589f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14882,7 +14937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c949efe-ba17-40eb-919e-4cef3445fa5c}</x14:id>
+          <x14:id>{fbf61a3f-4bca-49cd-aaf0-64df60763cf9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14894,7 +14949,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a424e572-0a6f-48a0-94bf-00f62e290800}</x14:id>
+          <x14:id>{d3adc8c1-60d2-4180-b19e-929b571f64b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14908,7 +14963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{10b01e13-8e55-43ac-ba2e-74307942de61}</x14:id>
+          <x14:id>{c5e27f5e-4c84-4bf0-859a-39ee8ae56122}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14920,7 +14975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e27ca86d-6af8-41d6-aae3-7dc4b93027c1}</x14:id>
+          <x14:id>{98a09a73-5db7-47f2-84fb-56657499497f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14957,7 +15012,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3932aab8-bd28-4bdc-854d-a557c45adca5}">
+          <x14:cfRule type="dataBar" id="{2af5cd9a-e609-4f7c-912f-2a64ab7edb53}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14966,7 +15021,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{82f100c7-86ea-4e27-90c7-0ddf631a5ddd}">
+          <x14:cfRule type="dataBar" id="{e1edc20c-7cd0-4e1c-b058-c4141b8aaada}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14975,7 +15030,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{30e16290-2128-4997-a853-ed535a357b6a}">
+          <x14:cfRule type="dataBar" id="{fde453e9-61b4-4e9c-bf43-d053085f8366}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14986,7 +15041,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{56ee5bd4-08ed-49d8-b894-9652ada0974b}">
+          <x14:cfRule type="dataBar" id="{e2ef6c84-0182-43cc-9c68-466d2ccbd140}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14997,7 +15052,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{89d6a018-748d-4749-916e-5011ed51ab29}">
+          <x14:cfRule type="dataBar" id="{594178f1-6b37-433a-8fed-72be2cda9a2a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15008,14 +15063,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2454dee4-1897-4708-bb81-62d13bb5c841}">
+          <x14:cfRule type="dataBar" id="{be01c605-0e0e-4610-95af-52cb573f7dac}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b5ba81fe-72b9-4525-b69c-6817651d7f15}">
+          <x14:cfRule type="dataBar" id="{95f320f7-a19b-4c4d-ac27-dd48d7f6546e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15026,7 +15081,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3d4edf10-7bdc-4950-be35-c390c3f8bcc9}">
+          <x14:cfRule type="dataBar" id="{c922679c-7cda-4773-98f2-af4ab5b84258}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15040,7 +15095,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6c2132dc-fe1e-4dc5-9a99-964d014fcaff}">
+          <x14:cfRule type="dataBar" id="{674c4bfd-a343-4f05-bfc4-08aa2cd1d93b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15049,7 +15104,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{316b3783-6ee6-4d9d-b8bf-7356ad08fe87}">
+          <x14:cfRule type="dataBar" id="{04325fbc-ee28-400c-9773-9267cd42f8ea}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15058,7 +15113,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4dc53339-5ed8-4a17-8f5b-a5f578989b92}">
+          <x14:cfRule type="dataBar" id="{1daf9e4c-a7a1-4476-be49-648097c72bae}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15069,7 +15124,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{db48b74a-c711-4276-8370-d94010b42055}">
+          <x14:cfRule type="dataBar" id="{71e1827a-705a-4feb-a74c-a5ed4134e298}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15080,7 +15135,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{232c19a8-4c02-4895-aa27-bb51a6fc35c6}">
+          <x14:cfRule type="dataBar" id="{8e2af315-4334-4320-b4d7-6f82ece95ea1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15091,14 +15146,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ec68d299-6b47-406e-9f29-9c53e6bb6ff9}">
+          <x14:cfRule type="dataBar" id="{3eb92b5f-d1e9-4c6e-8aaf-322e1b7b5a21}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{83ad3bc8-74ad-44ee-9eda-745353b88311}">
+          <x14:cfRule type="dataBar" id="{4208ddda-32e4-41ff-9fcf-ff8311863f7f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15109,7 +15164,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{84919dcf-b023-4416-a271-2b10dd110990}">
+          <x14:cfRule type="dataBar" id="{8601291a-a086-4715-8860-f31b59cd7fcc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15123,7 +15178,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eab74a9e-5ada-4048-a5ce-c0c54f2eca82}">
+          <x14:cfRule type="dataBar" id="{79703102-f7bc-4916-ab26-7c824f1a09bd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15132,7 +15187,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1de9a9da-b216-4bb4-803d-85c0da33e6fb}">
+          <x14:cfRule type="dataBar" id="{70d905b2-f8f1-475e-98ec-6bab869b0153}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15141,7 +15196,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f83118a6-43f0-4fe9-b2f5-6862b7c67e19}">
+          <x14:cfRule type="dataBar" id="{732feee0-9503-4545-9bb0-6ef18ca4d86e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15152,7 +15207,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{956e6e6f-76e2-4674-84ce-93cb6d2b234d}">
+          <x14:cfRule type="dataBar" id="{582cb6c3-bce4-485a-af40-5621fe96cda7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15163,7 +15218,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{84b27833-047d-4b47-a68d-c6249f89c0c4}">
+          <x14:cfRule type="dataBar" id="{40b03740-81b0-46aa-8ccc-eb9acd4f48f6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15174,14 +15229,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5a933331-de08-4b4e-a383-df8e8fbbe3f9}">
+          <x14:cfRule type="dataBar" id="{80f4ddd0-14d6-4829-80a4-af7c74b08880}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{38eb80c4-d27b-4b5f-89dd-7746868ec772}">
+          <x14:cfRule type="dataBar" id="{f83528e2-45f3-4dae-b4d2-2b3258f1fca3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15192,7 +15247,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d732c76a-457d-465f-97be-f1f54d47c8a4}">
+          <x14:cfRule type="dataBar" id="{d9570ff2-1f61-4e6d-a13d-ab56f9d440aa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15206,7 +15261,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{daa6e485-8c50-4ebf-816e-9027a9bb41ab}">
+          <x14:cfRule type="dataBar" id="{653e19e9-1c0b-43d6-8021-7d4e7d296586}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15215,7 +15270,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c71d4a07-c2f0-4d5c-869c-196d9d8f6d3e}">
+          <x14:cfRule type="dataBar" id="{34fb31ec-f745-4105-a219-63c0c31f5654}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15224,7 +15279,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d1462981-1a27-43ac-acb1-9bfc0c27b85d}">
+          <x14:cfRule type="dataBar" id="{f5b9b82d-2dc6-4f4f-842a-feca292acc72}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15235,7 +15290,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b57045fa-6969-4813-b6eb-4770c3c20c4c}">
+          <x14:cfRule type="dataBar" id="{29964e06-6124-4014-9a04-0730df4c927d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15246,7 +15301,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c1e6ce22-58da-485c-948f-8434ca9c2296}">
+          <x14:cfRule type="dataBar" id="{fcb19eef-6d84-47ee-b0f5-ffb973a51c8f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15257,14 +15312,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6540b8fe-ada5-455d-bd1a-d673ad6642c6}">
+          <x14:cfRule type="dataBar" id="{67d9ef26-3ca1-4ff8-a20a-536447bc74ee}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{81e656f8-8418-4a6a-b137-597d2146b767}">
+          <x14:cfRule type="dataBar" id="{d19c5c79-536b-44ff-919b-30125c2d60fd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15275,7 +15330,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{967bdf2b-f914-4505-86c5-e12944c276fc}">
+          <x14:cfRule type="dataBar" id="{f6c6b123-1958-45cc-9c13-e7eb38b1443e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15289,7 +15344,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{473f09d8-fcb0-44ab-995a-436bce0508e9}">
+          <x14:cfRule type="dataBar" id="{f14934f0-c390-43b3-9d66-befb0bafdfee}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15298,7 +15353,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{79cbb222-8cf5-452a-9617-678cf9662b2d}">
+          <x14:cfRule type="dataBar" id="{daf9c9df-f822-4c40-b586-1736d5170e2e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15307,7 +15362,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b2373a7e-9f0a-40fa-8926-ce55a11ce610}">
+          <x14:cfRule type="dataBar" id="{7a501ce3-7d04-4f90-b7dc-6aef602633af}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15318,7 +15373,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d4e29cc3-11e0-46cf-a40a-fab2cf25d68b}">
+          <x14:cfRule type="dataBar" id="{c65507bf-7a8c-4a11-adde-38b095257331}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15329,7 +15384,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{84aad717-50f3-42c7-b510-cf4c9cad22a4}">
+          <x14:cfRule type="dataBar" id="{12eccc52-699f-4059-a3d4-d09ee9a7aba0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15340,14 +15395,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{787ed57b-7ca2-44ae-8f1d-4f486efdc660}">
+          <x14:cfRule type="dataBar" id="{c4c2c1cf-699f-4f67-bf12-53c88fd55ee2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{738c1dc2-8e4f-411f-b37c-755f65f69589}">
+          <x14:cfRule type="dataBar" id="{55c1532c-4430-4769-8d25-041f263d01fd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15358,7 +15413,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bab48e83-cb98-49ec-b2d5-ce5c991abddb}">
+          <x14:cfRule type="dataBar" id="{22f0bd7f-13b1-4405-b82d-623e1c158f08}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15372,7 +15427,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf0eb950-2c57-459c-92ce-0e8039b01bed}">
+          <x14:cfRule type="dataBar" id="{fa7872e1-012f-410f-b3af-bb94a7759ec7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15381,7 +15436,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{be6139a4-f380-4664-84a4-c3d92b4a6969}">
+          <x14:cfRule type="dataBar" id="{97bcde2c-2709-49af-882f-794ae033524b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15390,7 +15445,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c84a2bd8-61d0-4429-90a1-d96450ade3f9}">
+          <x14:cfRule type="dataBar" id="{967ced90-775e-4af3-bbfa-0b0c35ee52ee}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15401,7 +15456,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{83525fb8-f305-4507-983a-e30926b07b15}">
+          <x14:cfRule type="dataBar" id="{c1291044-48e4-491c-b7d2-ed73599fa36a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15412,7 +15467,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a6b542d5-971a-413e-b65b-135e83662c46}">
+          <x14:cfRule type="dataBar" id="{6ad17153-bccc-4a64-8d64-5069c01857ff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15423,14 +15478,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{984847ba-dadc-4795-8495-410406ddddfc}">
+          <x14:cfRule type="dataBar" id="{f9b2f6ce-0944-47b7-b8fb-e2832dae43e0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{36b76f27-afa0-489f-a87c-ac534300f035}">
+          <x14:cfRule type="dataBar" id="{b2d5b9a7-125d-4f08-957c-81878b7dea53}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15441,7 +15496,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4805e399-6440-46db-9f68-c6cfc8f49a52}">
+          <x14:cfRule type="dataBar" id="{75d32736-baf4-4491-b888-a80ebf6895a0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15455,7 +15510,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{303abf6a-334a-45ef-be5b-ce4e334978f7}">
+          <x14:cfRule type="dataBar" id="{aae03f9f-2b9c-4700-881c-a41ad5a14e8e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15464,7 +15519,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f109ee85-9855-4d2f-96f8-7eaf123bdb90}">
+          <x14:cfRule type="dataBar" id="{553f68ca-f4ac-49cd-96b0-252679f3fef7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15473,7 +15528,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{96936257-9a93-4360-86c3-8d45ba6e3298}">
+          <x14:cfRule type="dataBar" id="{f29dcbec-0337-4ca6-a5a7-078ed53c0452}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15484,7 +15539,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{93dad177-fe67-4185-b3e1-cec7751bcff3}">
+          <x14:cfRule type="dataBar" id="{a49f2e55-b1b1-4003-b753-9abbc51a8173}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15495,7 +15550,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7520bb0e-a1b9-4655-8953-084268910355}">
+          <x14:cfRule type="dataBar" id="{edafc9bc-a3e6-4a4e-ac17-fe3e3aed3d40}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15506,14 +15561,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5fbeb63a-2be6-4984-bb2d-241cfbcc46a5}">
+          <x14:cfRule type="dataBar" id="{d879668f-7c19-4867-8cea-ffa95f7d9dad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2e4fe7e9-0d66-45bf-ad28-17689609d23e}">
+          <x14:cfRule type="dataBar" id="{0c9e808e-3ce4-41d9-b9e5-4c60b73da797}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15524,7 +15579,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0148d49e-4ce5-4e6a-928f-27a603f454b4}">
+          <x14:cfRule type="dataBar" id="{f9cbfd66-fa8e-4cea-8c3f-730e2236fae6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15538,7 +15593,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{252ef752-38b2-4015-9458-b7a6f39481ca}">
+          <x14:cfRule type="dataBar" id="{6beeb1de-1a5f-4dee-81ca-137fc0601559}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15550,7 +15605,7 @@
           <xm:sqref>K189:K208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70de4c80-f137-4767-a9d2-3a371f115217}">
+          <x14:cfRule type="dataBar" id="{48d84d18-b2eb-48e7-875c-0b8297d71a17}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15562,7 +15617,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4eb48a5a-e437-42aa-9b82-7625e9c5c00b}">
+          <x14:cfRule type="dataBar" id="{2e49122d-cf81-4e2f-ad3c-6d2b27042abb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15574,7 +15629,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9d1899f9-9fee-41fd-97fe-9ba7d9623809}">
+          <x14:cfRule type="dataBar" id="{763c1bb4-e953-472f-9465-9bdd71bed98c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15583,7 +15638,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a47feb2d-1b0f-4516-8ec3-f7b5b2b476d4}">
+          <x14:cfRule type="dataBar" id="{76dd35f7-5423-4910-adc6-9c71d036f0e2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15592,7 +15647,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6e5e286f-936d-47d7-8820-ebdeb5f0fc62}">
+          <x14:cfRule type="dataBar" id="{c0d8baab-7b0d-4df9-abef-7a8de6205fa0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15603,7 +15658,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7e0b5292-af90-4dba-83fa-140d62420e38}">
+          <x14:cfRule type="dataBar" id="{03fd9d7a-2e64-4d01-9696-92c12d9a6084}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15614,7 +15669,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4848be0b-423b-4330-b4f0-2537490837aa}">
+          <x14:cfRule type="dataBar" id="{b2f4e5ba-b542-4c12-86ce-efd2bb8c0f8e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15625,14 +15680,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{02b83baf-432c-4691-8e53-9ff396208269}">
+          <x14:cfRule type="dataBar" id="{ce794363-64f0-47bc-8266-ba0d0bdda76d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{12d1a9e5-fc68-4aba-93fe-89532dff0257}">
+          <x14:cfRule type="dataBar" id="{882f8a97-1033-4b3b-b8af-abb28d9744ac}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15643,7 +15698,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{77e03c3d-2d2f-491e-8813-643cc6475233}">
+          <x14:cfRule type="dataBar" id="{f881801f-d19c-4b87-b293-6ca372630341}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15657,7 +15712,7 @@
           <xm:sqref>F69 F79 F89 F99 F109 F119 F129 F139 F149 F159 F169 F179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce1c1e0e-2b48-408d-84c9-2246e941f8d5}">
+          <x14:cfRule type="dataBar" id="{bbfaa7a7-6967-4c82-a231-a35df6bd90c6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15666,7 +15721,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2bbb31e8-a27d-45cd-becb-593237e21ba1}">
+          <x14:cfRule type="dataBar" id="{3d11fd74-fa72-4380-8dd3-c2615c82f20b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15678,7 +15733,7 @@
           <xm:sqref>K69:K79 K85:K99 K105:K119 K125:K139 K145:K159 K165:K179 K185:K188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8baa8ba9-e80d-4d98-99db-24e10f070edc}">
+          <x14:cfRule type="dataBar" id="{0453a3ce-4f05-43b7-b579-0b81cf798885}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15690,7 +15745,7 @@
           <xm:sqref>Y69:Y79 Y85:Y99 Y105:Y122 Y125:Y141 Y145:Y160 Y165:Y179 Y185:Y188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ac8f49d-dfdd-47b1-a7cf-ced3c54475b8}">
+          <x14:cfRule type="dataBar" id="{ace7eecc-7445-4a71-9da4-5fdc18c9125d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15699,7 +15754,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7f8b76eb-027e-455a-85a7-6d64eb4b557e}">
+          <x14:cfRule type="dataBar" id="{5bbee154-e071-42b6-9cc9-2cdbc4007784}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15711,7 +15766,7 @@
           <xm:sqref>AB69 AB89 AB109 AB129 AB149 AB169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cd289d4a-878e-4b6a-b89d-2518186354ec}">
+          <x14:cfRule type="dataBar" id="{98ac6c31-4136-45c1-a36b-9b341cc87b37}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15720,7 +15775,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24e8bc63-5a66-4a93-9be0-66589f270bc0}">
+          <x14:cfRule type="dataBar" id="{a21dfa89-d55f-4e78-9806-ec7e0a7eaafc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15730,7 +15785,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB122 AB125:AB141 AB145:AB160 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c5d43ce1-3cd6-49bf-9ebb-ab8bd60f798d}">
+          <x14:cfRule type="dataBar" id="{9e6c3b43-c290-4b3d-880b-14e317420c1a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15742,7 +15797,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB119 AB125:AB139 AB145:AB159 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{946ea27f-2b5b-4d9b-a937-354f50a03d3a}">
+          <x14:cfRule type="dataBar" id="{1bd3d8a2-60b4-42ff-befd-bdd6e86fd70f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15751,7 +15806,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7dce38d9-78ca-40df-ac21-a9d474963c3c}">
+          <x14:cfRule type="dataBar" id="{24820b95-1715-4b32-b953-2083a4449190}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15763,7 +15818,7 @@
           <xm:sqref>K80:K84 K100:K104 K120:K124 K140:K144 K160:K164 K180:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d651863c-6c1d-41ff-84d7-5c8922542ccb}">
+          <x14:cfRule type="dataBar" id="{51135e84-3859-4254-9f29-a142b75f6d4f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15775,7 +15830,7 @@
           <xm:sqref>Y80:Y84 Y100:Y104 Y120:Y124 Y140:Y144 Y160:Y164 Y180:Y184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5e2184b8-307c-4008-8412-e49720f5cffc}">
+          <x14:cfRule type="dataBar" id="{6f9e9af7-0540-4dc6-8707-9aa58b293d4d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15784,7 +15839,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{280a2fd3-76b3-416e-a2e0-f32e161fb8b2}">
+          <x14:cfRule type="dataBar" id="{29797952-4392-4302-a531-b32a59ee9214}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15793,7 +15848,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b95ed258-f794-4210-952a-b8473379152e}">
+          <x14:cfRule type="dataBar" id="{6fd162f3-5a2b-483c-8ecb-9b2a43da661a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15803,7 +15858,7 @@
           <xm:sqref>AB80:AB84 AB100:AB104 AB120:AB124 AB140:AB144 AB160:AB164 AB180:AB184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98411d6a-7ae3-4f9c-a352-d941c53028d0}">
+          <x14:cfRule type="dataBar" id="{ceb07929-f5b0-45be-acd9-3d08661b589f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15812,7 +15867,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3c949efe-ba17-40eb-919e-4cef3445fa5c}">
+          <x14:cfRule type="dataBar" id="{fbf61a3f-4bca-49cd-aaf0-64df60763cf9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15821,7 +15876,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a424e572-0a6f-48a0-94bf-00f62e290800}">
+          <x14:cfRule type="dataBar" id="{d3adc8c1-60d2-4180-b19e-929b571f64b7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15833,7 +15888,7 @@
           <xm:sqref>F189 F194 F199 F204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{10b01e13-8e55-43ac-ba2e-74307942de61}">
+          <x14:cfRule type="dataBar" id="{c5e27f5e-4c84-4bf0-859a-39ee8ae56122}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15842,7 +15897,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e27ca86d-6af8-41d6-aae3-7dc4b93027c1}">
+          <x14:cfRule type="dataBar" id="{98a09a73-5db7-47f2-84fb-56657499497f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15863,12 +15918,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/E楼交接班容量报表空模板.xlsx
+++ b/外网端源码/E楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3569,27 +3569,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE211"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.7727272727273" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7685185185185" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1090909090909" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1111111111111" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
     <col min="20" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="12.3363636363636" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.3333333333333" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4318,7 +4318,7 @@
         <v>51</v>
       </c>
       <c r="V18" s="27">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="W18" s="14"/>
       <c r="X18" s="27" t="s">
@@ -13915,7 +13915,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2af5cd9a-e609-4f7c-912f-2a64ab7edb53}</x14:id>
+          <x14:id>{e69025c8-559e-43fb-9393-41f9f2b6ef9a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13927,7 +13927,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e1edc20c-7cd0-4e1c-b058-c4141b8aaada}</x14:id>
+          <x14:id>{2ebddf80-93cb-4280-8aa2-0f103db5f9bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13939,7 +13939,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fde453e9-61b4-4e9c-bf43-d053085f8366}</x14:id>
+          <x14:id>{70182af8-b203-482b-b64b-511c62480cff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13951,7 +13951,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2ef6c84-0182-43cc-9c68-466d2ccbd140}</x14:id>
+          <x14:id>{17d69de9-2c40-4007-91da-96d5e2bccfc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13963,7 +13963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{594178f1-6b37-433a-8fed-72be2cda9a2a}</x14:id>
+          <x14:id>{11a3c81e-8e19-4946-bd54-2159bf47b053}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13975,7 +13975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be01c605-0e0e-4610-95af-52cb573f7dac}</x14:id>
+          <x14:id>{1c78f4da-106d-4e5c-ba80-0ffc3254fbee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13987,7 +13987,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95f320f7-a19b-4c4d-ac27-dd48d7f6546e}</x14:id>
+          <x14:id>{080992cc-6e7f-4875-a7da-02e032e668d9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13999,7 +13999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c922679c-7cda-4773-98f2-af4ab5b84258}</x14:id>
+          <x14:id>{0f87c4a9-ffab-4661-9dae-1ccd97a09aff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14013,7 +14013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{674c4bfd-a343-4f05-bfc4-08aa2cd1d93b}</x14:id>
+          <x14:id>{310aa0e6-fd63-4eec-80fd-996b8bcc183b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14025,7 +14025,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{04325fbc-ee28-400c-9773-9267cd42f8ea}</x14:id>
+          <x14:id>{72f609c2-e134-4e63-8f04-69e89a5f53ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14037,7 +14037,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1daf9e4c-a7a1-4476-be49-648097c72bae}</x14:id>
+          <x14:id>{31d1e55e-43f6-4a51-aae3-574a35aaba67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14049,7 +14049,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71e1827a-705a-4feb-a74c-a5ed4134e298}</x14:id>
+          <x14:id>{6b8d69e2-a0c2-450d-b393-8d4a4cdd42a8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14061,7 +14061,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e2af315-4334-4320-b4d7-6f82ece95ea1}</x14:id>
+          <x14:id>{975100a4-0027-4ced-9a44-b81c961f7f23}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14073,7 +14073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3eb92b5f-d1e9-4c6e-8aaf-322e1b7b5a21}</x14:id>
+          <x14:id>{fa43619a-0e47-453c-9eb2-adb49815901e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14085,7 +14085,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4208ddda-32e4-41ff-9fcf-ff8311863f7f}</x14:id>
+          <x14:id>{b789422e-e7c8-4149-8b9b-ecec20a10eb8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14097,7 +14097,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8601291a-a086-4715-8860-f31b59cd7fcc}</x14:id>
+          <x14:id>{92ba0b23-948b-4a10-9754-024f51b9697b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14111,7 +14111,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79703102-f7bc-4916-ab26-7c824f1a09bd}</x14:id>
+          <x14:id>{029ab547-7946-4c2b-8bb8-db24a5043cc7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14123,7 +14123,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70d905b2-f8f1-475e-98ec-6bab869b0153}</x14:id>
+          <x14:id>{d6ced779-0699-4f50-ba07-f6d25eec4562}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14135,7 +14135,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{732feee0-9503-4545-9bb0-6ef18ca4d86e}</x14:id>
+          <x14:id>{8711d0cc-e528-43a5-af6d-6634c254aa9b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14147,7 +14147,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{582cb6c3-bce4-485a-af40-5621fe96cda7}</x14:id>
+          <x14:id>{95f407b1-c930-458a-987e-251f02ef1a7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14159,7 +14159,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{40b03740-81b0-46aa-8ccc-eb9acd4f48f6}</x14:id>
+          <x14:id>{e91a399f-a442-435c-9d47-f939fad1fb87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14171,7 +14171,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80f4ddd0-14d6-4829-80a4-af7c74b08880}</x14:id>
+          <x14:id>{0adfdaa5-aae5-4e8e-882c-c47ab0bb8477}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14183,7 +14183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f83528e2-45f3-4dae-b4d2-2b3258f1fca3}</x14:id>
+          <x14:id>{f773e078-4ea2-4061-9315-43ccf3063d71}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14195,7 +14195,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d9570ff2-1f61-4e6d-a13d-ab56f9d440aa}</x14:id>
+          <x14:id>{195bdcec-1c2f-4184-a8be-686374fc19ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14209,7 +14209,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{653e19e9-1c0b-43d6-8021-7d4e7d296586}</x14:id>
+          <x14:id>{3b5c84ff-ac18-441a-8b0f-540739fc3fe5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14221,7 +14221,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34fb31ec-f745-4105-a219-63c0c31f5654}</x14:id>
+          <x14:id>{9e3da8cf-0407-4eae-a0eb-8d41305c0cfb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14233,7 +14233,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5b9b82d-2dc6-4f4f-842a-feca292acc72}</x14:id>
+          <x14:id>{baed23fd-0c47-4f6a-81b7-8c255e165ee1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14245,7 +14245,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29964e06-6124-4014-9a04-0730df4c927d}</x14:id>
+          <x14:id>{230ed903-e5c6-40aa-ab50-26990ec5395f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14257,7 +14257,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fcb19eef-6d84-47ee-b0f5-ffb973a51c8f}</x14:id>
+          <x14:id>{25c70917-357e-4cf6-bab6-62e069643fd5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14269,7 +14269,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67d9ef26-3ca1-4ff8-a20a-536447bc74ee}</x14:id>
+          <x14:id>{fe1dbc04-449f-4f35-8252-e20086f6b3be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14281,7 +14281,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d19c5c79-536b-44ff-919b-30125c2d60fd}</x14:id>
+          <x14:id>{b6161a8e-b84c-4837-9d8a-f0c7016f75a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14293,7 +14293,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f6c6b123-1958-45cc-9c13-e7eb38b1443e}</x14:id>
+          <x14:id>{a07ba539-32ac-48a7-8bc7-257d6a531679}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14307,7 +14307,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f14934f0-c390-43b3-9d66-befb0bafdfee}</x14:id>
+          <x14:id>{14646f47-c32a-4d79-a188-061d1e68be60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14319,7 +14319,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{daf9c9df-f822-4c40-b586-1736d5170e2e}</x14:id>
+          <x14:id>{a6a26bd8-8dac-4f9b-a943-258472e75480}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14331,7 +14331,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a501ce3-7d04-4f90-b7dc-6aef602633af}</x14:id>
+          <x14:id>{1384be7b-5a30-48bd-86a5-72efaebc5448}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14343,7 +14343,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c65507bf-7a8c-4a11-adde-38b095257331}</x14:id>
+          <x14:id>{62ada315-f903-4c0e-bbd1-b996ef440691}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14355,7 +14355,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12eccc52-699f-4059-a3d4-d09ee9a7aba0}</x14:id>
+          <x14:id>{514871e6-80f1-44ba-9a7a-78dfbba1ca41}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14367,7 +14367,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4c2c1cf-699f-4f67-bf12-53c88fd55ee2}</x14:id>
+          <x14:id>{f4a8ca59-afdd-4dea-a531-c7c6bebea75b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14379,7 +14379,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55c1532c-4430-4769-8d25-041f263d01fd}</x14:id>
+          <x14:id>{841e4f72-a497-4595-a91e-fa3747a9f405}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14391,7 +14391,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{22f0bd7f-13b1-4405-b82d-623e1c158f08}</x14:id>
+          <x14:id>{8ad6aba3-e584-4647-ada0-a4eb9ccf3c54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14405,7 +14405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa7872e1-012f-410f-b3af-bb94a7759ec7}</x14:id>
+          <x14:id>{a366fa60-1629-4cc8-9379-a94a625465ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14417,7 +14417,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97bcde2c-2709-49af-882f-794ae033524b}</x14:id>
+          <x14:id>{6d9c50a9-ed3a-4545-9233-39402ea46431}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14429,7 +14429,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{967ced90-775e-4af3-bbfa-0b0c35ee52ee}</x14:id>
+          <x14:id>{65ff1913-4277-4b8c-ab3b-b09e28cd96ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14441,7 +14441,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1291044-48e4-491c-b7d2-ed73599fa36a}</x14:id>
+          <x14:id>{720b4bd5-e4c5-45d8-af61-37f1180cbdc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14453,7 +14453,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ad17153-bccc-4a64-8d64-5069c01857ff}</x14:id>
+          <x14:id>{aab55b8a-2d1c-4eba-9f62-08850b89ec40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14465,7 +14465,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9b2f6ce-0944-47b7-b8fb-e2832dae43e0}</x14:id>
+          <x14:id>{93b33f66-a8e0-46b6-a063-16c7e23f077e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14477,7 +14477,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2d5b9a7-125d-4f08-957c-81878b7dea53}</x14:id>
+          <x14:id>{b4b5045d-fc61-4c85-977e-7af67f6958ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14489,7 +14489,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75d32736-baf4-4491-b888-a80ebf6895a0}</x14:id>
+          <x14:id>{c2000871-cf54-4cdc-8e92-bea515444809}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14503,7 +14503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aae03f9f-2b9c-4700-881c-a41ad5a14e8e}</x14:id>
+          <x14:id>{120da751-a8b0-49fc-b428-d7cffd79f71e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14515,7 +14515,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{553f68ca-f4ac-49cd-96b0-252679f3fef7}</x14:id>
+          <x14:id>{ffa15dc4-68c0-4cde-9b38-a589389f31e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14527,7 +14527,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f29dcbec-0337-4ca6-a5a7-078ed53c0452}</x14:id>
+          <x14:id>{69f08d15-215f-4fe2-a2f6-621be5a5eefe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14539,7 +14539,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a49f2e55-b1b1-4003-b753-9abbc51a8173}</x14:id>
+          <x14:id>{dceb6f28-76ec-49a9-a962-f4ff76ebd3b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14551,7 +14551,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{edafc9bc-a3e6-4a4e-ac17-fe3e3aed3d40}</x14:id>
+          <x14:id>{3502f9fb-fd37-4e33-85d5-6adb168fe990}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14563,7 +14563,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d879668f-7c19-4867-8cea-ffa95f7d9dad}</x14:id>
+          <x14:id>{8223a483-38e5-4001-a893-15de51da55bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14575,7 +14575,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c9e808e-3ce4-41d9-b9e5-4c60b73da797}</x14:id>
+          <x14:id>{b6d817ef-3bbf-42c7-bd39-2a7d7d44b24a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14587,7 +14587,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9cbfd66-fa8e-4cea-8c3f-730e2236fae6}</x14:id>
+          <x14:id>{e930c886-6555-49ab-83b9-9790e2afb679}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14601,7 +14601,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6beeb1de-1a5f-4dee-81ca-137fc0601559}</x14:id>
+          <x14:id>{3e833661-5805-4370-abde-e9ca3b7e6cd5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14615,7 +14615,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{48d84d18-b2eb-48e7-875c-0b8297d71a17}</x14:id>
+          <x14:id>{b7988f45-ed1b-48ed-84ac-2ea92f052f48}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14629,7 +14629,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e49122d-cf81-4e2f-ad3c-6d2b27042abb}</x14:id>
+          <x14:id>{d922798b-51bb-4e52-9675-c73919ce9cd0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14643,7 +14643,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{763c1bb4-e953-472f-9465-9bdd71bed98c}</x14:id>
+          <x14:id>{ea7d7bd9-065e-4d4f-84ae-c80079a43e7e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14655,7 +14655,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76dd35f7-5423-4910-adc6-9c71d036f0e2}</x14:id>
+          <x14:id>{e00784ca-3989-42f5-8481-7818a1c35790}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14667,7 +14667,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0d8baab-7b0d-4df9-abef-7a8de6205fa0}</x14:id>
+          <x14:id>{44bbb073-f394-4d53-8f88-085392ef962b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14679,7 +14679,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03fd9d7a-2e64-4d01-9696-92c12d9a6084}</x14:id>
+          <x14:id>{5b053cb1-32e9-4569-b494-16260e5b5169}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14691,7 +14691,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2f4e5ba-b542-4c12-86ce-efd2bb8c0f8e}</x14:id>
+          <x14:id>{a416daad-1a04-4210-be59-2c47aebd646b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14703,7 +14703,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce794363-64f0-47bc-8266-ba0d0bdda76d}</x14:id>
+          <x14:id>{c05bfbe1-677a-4e72-a5e9-3ddcdcd91791}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14715,7 +14715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{882f8a97-1033-4b3b-b8af-abb28d9744ac}</x14:id>
+          <x14:id>{0c3ac258-0aae-4c56-a29e-307b554459a9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14727,7 +14727,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f881801f-d19c-4b87-b293-6ca372630341}</x14:id>
+          <x14:id>{e0ffb5aa-bfd9-41a0-b2bf-1618786fbf78}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14741,7 +14741,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bbfaa7a7-6967-4c82-a231-a35df6bd90c6}</x14:id>
+          <x14:id>{2baf2adb-f5dd-4886-9484-2f91567d47fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14753,7 +14753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d11fd74-fa72-4380-8dd3-c2615c82f20b}</x14:id>
+          <x14:id>{6e992747-c1dd-4839-8937-93cda052bc90}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14767,7 +14767,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0453a3ce-4f05-43b7-b579-0b81cf798885}</x14:id>
+          <x14:id>{bcec06e0-7fdf-41bb-baeb-86db79142104}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14781,7 +14781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ace7eecc-7445-4a71-9da4-5fdc18c9125d}</x14:id>
+          <x14:id>{2bb3edf2-ef41-4b89-8eba-4336e031c8fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14793,7 +14793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5bbee154-e071-42b6-9cc9-2cdbc4007784}</x14:id>
+          <x14:id>{df963b0e-f6d0-47a1-adfc-16ce8a93bde2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14807,7 +14807,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98ac6c31-4136-45c1-a36b-9b341cc87b37}</x14:id>
+          <x14:id>{20c6f949-6053-4cc0-8075-5f8eb1a7e95e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14819,7 +14819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a21dfa89-d55f-4e78-9806-ec7e0a7eaafc}</x14:id>
+          <x14:id>{30937886-e39e-4674-8119-f01e136cb6de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14833,7 +14833,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e6c3b43-c290-4b3d-880b-14e317420c1a}</x14:id>
+          <x14:id>{e3e46d0e-063e-4d0c-accd-6d56a4bab023}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14847,7 +14847,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1bd3d8a2-60b4-42ff-befd-bdd6e86fd70f}</x14:id>
+          <x14:id>{5e2b9634-2899-42f6-b7ba-4a81d2ffaacd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14859,7 +14859,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24820b95-1715-4b32-b953-2083a4449190}</x14:id>
+          <x14:id>{8dcef961-86b5-4ad6-be71-67501977823d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14873,7 +14873,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51135e84-3859-4254-9f29-a142b75f6d4f}</x14:id>
+          <x14:id>{7504b37a-906a-4793-b586-5402b9f31916}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14887,7 +14887,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f9e9af7-0540-4dc6-8707-9aa58b293d4d}</x14:id>
+          <x14:id>{fa90b142-b3de-4bb9-bf2f-bcf29ac5b70d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14899,7 +14899,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29797952-4392-4302-a531-b32a59ee9214}</x14:id>
+          <x14:id>{fe3a71be-9773-4135-ae28-327fc91a9b67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14911,7 +14911,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6fd162f3-5a2b-483c-8ecb-9b2a43da661a}</x14:id>
+          <x14:id>{675156af-d591-420c-b24e-6bc461bc6654}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14925,7 +14925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ceb07929-f5b0-45be-acd9-3d08661b589f}</x14:id>
+          <x14:id>{a0e2513c-3c02-458e-b5c9-e59f1f4245a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14937,7 +14937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fbf61a3f-4bca-49cd-aaf0-64df60763cf9}</x14:id>
+          <x14:id>{a4f5b0fd-587b-4e58-a12e-13df145cabf0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14949,7 +14949,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d3adc8c1-60d2-4180-b19e-929b571f64b7}</x14:id>
+          <x14:id>{8fc10373-56f0-4c60-8962-b3a3eda64d8e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14963,7 +14963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5e27f5e-4c84-4bf0-859a-39ee8ae56122}</x14:id>
+          <x14:id>{342580d6-d449-4484-a60b-e6c350faf848}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14975,7 +14975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98a09a73-5db7-47f2-84fb-56657499497f}</x14:id>
+          <x14:id>{fa83018a-8b97-4db1-816e-c01086817171}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -15012,7 +15012,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2af5cd9a-e609-4f7c-912f-2a64ab7edb53}">
+          <x14:cfRule type="dataBar" id="{e69025c8-559e-43fb-9393-41f9f2b6ef9a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15021,7 +15021,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e1edc20c-7cd0-4e1c-b058-c4141b8aaada}">
+          <x14:cfRule type="dataBar" id="{2ebddf80-93cb-4280-8aa2-0f103db5f9bf}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15030,7 +15030,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fde453e9-61b4-4e9c-bf43-d053085f8366}">
+          <x14:cfRule type="dataBar" id="{70182af8-b203-482b-b64b-511c62480cff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15041,7 +15041,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e2ef6c84-0182-43cc-9c68-466d2ccbd140}">
+          <x14:cfRule type="dataBar" id="{17d69de9-2c40-4007-91da-96d5e2bccfc9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15052,7 +15052,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{594178f1-6b37-433a-8fed-72be2cda9a2a}">
+          <x14:cfRule type="dataBar" id="{11a3c81e-8e19-4946-bd54-2159bf47b053}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15063,14 +15063,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{be01c605-0e0e-4610-95af-52cb573f7dac}">
+          <x14:cfRule type="dataBar" id="{1c78f4da-106d-4e5c-ba80-0ffc3254fbee}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{95f320f7-a19b-4c4d-ac27-dd48d7f6546e}">
+          <x14:cfRule type="dataBar" id="{080992cc-6e7f-4875-a7da-02e032e668d9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15081,7 +15081,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c922679c-7cda-4773-98f2-af4ab5b84258}">
+          <x14:cfRule type="dataBar" id="{0f87c4a9-ffab-4661-9dae-1ccd97a09aff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15095,7 +15095,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{674c4bfd-a343-4f05-bfc4-08aa2cd1d93b}">
+          <x14:cfRule type="dataBar" id="{310aa0e6-fd63-4eec-80fd-996b8bcc183b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15104,7 +15104,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{04325fbc-ee28-400c-9773-9267cd42f8ea}">
+          <x14:cfRule type="dataBar" id="{72f609c2-e134-4e63-8f04-69e89a5f53ea}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15113,7 +15113,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1daf9e4c-a7a1-4476-be49-648097c72bae}">
+          <x14:cfRule type="dataBar" id="{31d1e55e-43f6-4a51-aae3-574a35aaba67}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15124,7 +15124,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{71e1827a-705a-4feb-a74c-a5ed4134e298}">
+          <x14:cfRule type="dataBar" id="{6b8d69e2-a0c2-450d-b393-8d4a4cdd42a8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15135,7 +15135,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8e2af315-4334-4320-b4d7-6f82ece95ea1}">
+          <x14:cfRule type="dataBar" id="{975100a4-0027-4ced-9a44-b81c961f7f23}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15146,14 +15146,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3eb92b5f-d1e9-4c6e-8aaf-322e1b7b5a21}">
+          <x14:cfRule type="dataBar" id="{fa43619a-0e47-453c-9eb2-adb49815901e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4208ddda-32e4-41ff-9fcf-ff8311863f7f}">
+          <x14:cfRule type="dataBar" id="{b789422e-e7c8-4149-8b9b-ecec20a10eb8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15164,7 +15164,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8601291a-a086-4715-8860-f31b59cd7fcc}">
+          <x14:cfRule type="dataBar" id="{92ba0b23-948b-4a10-9754-024f51b9697b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15178,7 +15178,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79703102-f7bc-4916-ab26-7c824f1a09bd}">
+          <x14:cfRule type="dataBar" id="{029ab547-7946-4c2b-8bb8-db24a5043cc7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15187,7 +15187,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{70d905b2-f8f1-475e-98ec-6bab869b0153}">
+          <x14:cfRule type="dataBar" id="{d6ced779-0699-4f50-ba07-f6d25eec4562}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15196,7 +15196,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{732feee0-9503-4545-9bb0-6ef18ca4d86e}">
+          <x14:cfRule type="dataBar" id="{8711d0cc-e528-43a5-af6d-6634c254aa9b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15207,7 +15207,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{582cb6c3-bce4-485a-af40-5621fe96cda7}">
+          <x14:cfRule type="dataBar" id="{95f407b1-c930-458a-987e-251f02ef1a7a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15218,7 +15218,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{40b03740-81b0-46aa-8ccc-eb9acd4f48f6}">
+          <x14:cfRule type="dataBar" id="{e91a399f-a442-435c-9d47-f939fad1fb87}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15229,14 +15229,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{80f4ddd0-14d6-4829-80a4-af7c74b08880}">
+          <x14:cfRule type="dataBar" id="{0adfdaa5-aae5-4e8e-882c-c47ab0bb8477}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f83528e2-45f3-4dae-b4d2-2b3258f1fca3}">
+          <x14:cfRule type="dataBar" id="{f773e078-4ea2-4061-9315-43ccf3063d71}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15247,7 +15247,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d9570ff2-1f61-4e6d-a13d-ab56f9d440aa}">
+          <x14:cfRule type="dataBar" id="{195bdcec-1c2f-4184-a8be-686374fc19ee}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15261,7 +15261,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{653e19e9-1c0b-43d6-8021-7d4e7d296586}">
+          <x14:cfRule type="dataBar" id="{3b5c84ff-ac18-441a-8b0f-540739fc3fe5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15270,7 +15270,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{34fb31ec-f745-4105-a219-63c0c31f5654}">
+          <x14:cfRule type="dataBar" id="{9e3da8cf-0407-4eae-a0eb-8d41305c0cfb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15279,7 +15279,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f5b9b82d-2dc6-4f4f-842a-feca292acc72}">
+          <x14:cfRule type="dataBar" id="{baed23fd-0c47-4f6a-81b7-8c255e165ee1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15290,7 +15290,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{29964e06-6124-4014-9a04-0730df4c927d}">
+          <x14:cfRule type="dataBar" id="{230ed903-e5c6-40aa-ab50-26990ec5395f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15301,7 +15301,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fcb19eef-6d84-47ee-b0f5-ffb973a51c8f}">
+          <x14:cfRule type="dataBar" id="{25c70917-357e-4cf6-bab6-62e069643fd5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15312,14 +15312,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{67d9ef26-3ca1-4ff8-a20a-536447bc74ee}">
+          <x14:cfRule type="dataBar" id="{fe1dbc04-449f-4f35-8252-e20086f6b3be}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d19c5c79-536b-44ff-919b-30125c2d60fd}">
+          <x14:cfRule type="dataBar" id="{b6161a8e-b84c-4837-9d8a-f0c7016f75a1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15330,7 +15330,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f6c6b123-1958-45cc-9c13-e7eb38b1443e}">
+          <x14:cfRule type="dataBar" id="{a07ba539-32ac-48a7-8bc7-257d6a531679}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15344,7 +15344,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f14934f0-c390-43b3-9d66-befb0bafdfee}">
+          <x14:cfRule type="dataBar" id="{14646f47-c32a-4d79-a188-061d1e68be60}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15353,7 +15353,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{daf9c9df-f822-4c40-b586-1736d5170e2e}">
+          <x14:cfRule type="dataBar" id="{a6a26bd8-8dac-4f9b-a943-258472e75480}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15362,7 +15362,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7a501ce3-7d04-4f90-b7dc-6aef602633af}">
+          <x14:cfRule type="dataBar" id="{1384be7b-5a30-48bd-86a5-72efaebc5448}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15373,7 +15373,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c65507bf-7a8c-4a11-adde-38b095257331}">
+          <x14:cfRule type="dataBar" id="{62ada315-f903-4c0e-bbd1-b996ef440691}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15384,7 +15384,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{12eccc52-699f-4059-a3d4-d09ee9a7aba0}">
+          <x14:cfRule type="dataBar" id="{514871e6-80f1-44ba-9a7a-78dfbba1ca41}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15395,14 +15395,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c4c2c1cf-699f-4f67-bf12-53c88fd55ee2}">
+          <x14:cfRule type="dataBar" id="{f4a8ca59-afdd-4dea-a531-c7c6bebea75b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{55c1532c-4430-4769-8d25-041f263d01fd}">
+          <x14:cfRule type="dataBar" id="{841e4f72-a497-4595-a91e-fa3747a9f405}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15413,7 +15413,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{22f0bd7f-13b1-4405-b82d-623e1c158f08}">
+          <x14:cfRule type="dataBar" id="{8ad6aba3-e584-4647-ada0-a4eb9ccf3c54}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15427,7 +15427,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa7872e1-012f-410f-b3af-bb94a7759ec7}">
+          <x14:cfRule type="dataBar" id="{a366fa60-1629-4cc8-9379-a94a625465ff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15436,7 +15436,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{97bcde2c-2709-49af-882f-794ae033524b}">
+          <x14:cfRule type="dataBar" id="{6d9c50a9-ed3a-4545-9233-39402ea46431}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15445,7 +15445,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{967ced90-775e-4af3-bbfa-0b0c35ee52ee}">
+          <x14:cfRule type="dataBar" id="{65ff1913-4277-4b8c-ab3b-b09e28cd96ff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15456,7 +15456,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c1291044-48e4-491c-b7d2-ed73599fa36a}">
+          <x14:cfRule type="dataBar" id="{720b4bd5-e4c5-45d8-af61-37f1180cbdc9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15467,7 +15467,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6ad17153-bccc-4a64-8d64-5069c01857ff}">
+          <x14:cfRule type="dataBar" id="{aab55b8a-2d1c-4eba-9f62-08850b89ec40}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15478,14 +15478,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f9b2f6ce-0944-47b7-b8fb-e2832dae43e0}">
+          <x14:cfRule type="dataBar" id="{93b33f66-a8e0-46b6-a063-16c7e23f077e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b2d5b9a7-125d-4f08-957c-81878b7dea53}">
+          <x14:cfRule type="dataBar" id="{b4b5045d-fc61-4c85-977e-7af67f6958ac}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15496,7 +15496,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{75d32736-baf4-4491-b888-a80ebf6895a0}">
+          <x14:cfRule type="dataBar" id="{c2000871-cf54-4cdc-8e92-bea515444809}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15510,7 +15510,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aae03f9f-2b9c-4700-881c-a41ad5a14e8e}">
+          <x14:cfRule type="dataBar" id="{120da751-a8b0-49fc-b428-d7cffd79f71e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15519,7 +15519,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{553f68ca-f4ac-49cd-96b0-252679f3fef7}">
+          <x14:cfRule type="dataBar" id="{ffa15dc4-68c0-4cde-9b38-a589389f31e8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15528,7 +15528,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f29dcbec-0337-4ca6-a5a7-078ed53c0452}">
+          <x14:cfRule type="dataBar" id="{69f08d15-215f-4fe2-a2f6-621be5a5eefe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15539,7 +15539,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a49f2e55-b1b1-4003-b753-9abbc51a8173}">
+          <x14:cfRule type="dataBar" id="{dceb6f28-76ec-49a9-a962-f4ff76ebd3b0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15550,7 +15550,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{edafc9bc-a3e6-4a4e-ac17-fe3e3aed3d40}">
+          <x14:cfRule type="dataBar" id="{3502f9fb-fd37-4e33-85d5-6adb168fe990}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15561,14 +15561,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d879668f-7c19-4867-8cea-ffa95f7d9dad}">
+          <x14:cfRule type="dataBar" id="{8223a483-38e5-4001-a893-15de51da55bf}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0c9e808e-3ce4-41d9-b9e5-4c60b73da797}">
+          <x14:cfRule type="dataBar" id="{b6d817ef-3bbf-42c7-bd39-2a7d7d44b24a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15579,7 +15579,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f9cbfd66-fa8e-4cea-8c3f-730e2236fae6}">
+          <x14:cfRule type="dataBar" id="{e930c886-6555-49ab-83b9-9790e2afb679}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15593,7 +15593,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6beeb1de-1a5f-4dee-81ca-137fc0601559}">
+          <x14:cfRule type="dataBar" id="{3e833661-5805-4370-abde-e9ca3b7e6cd5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15605,7 +15605,7 @@
           <xm:sqref>K189:K208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{48d84d18-b2eb-48e7-875c-0b8297d71a17}">
+          <x14:cfRule type="dataBar" id="{b7988f45-ed1b-48ed-84ac-2ea92f052f48}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15617,7 +15617,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2e49122d-cf81-4e2f-ad3c-6d2b27042abb}">
+          <x14:cfRule type="dataBar" id="{d922798b-51bb-4e52-9675-c73919ce9cd0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15629,7 +15629,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{763c1bb4-e953-472f-9465-9bdd71bed98c}">
+          <x14:cfRule type="dataBar" id="{ea7d7bd9-065e-4d4f-84ae-c80079a43e7e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15638,7 +15638,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{76dd35f7-5423-4910-adc6-9c71d036f0e2}">
+          <x14:cfRule type="dataBar" id="{e00784ca-3989-42f5-8481-7818a1c35790}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15647,7 +15647,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c0d8baab-7b0d-4df9-abef-7a8de6205fa0}">
+          <x14:cfRule type="dataBar" id="{44bbb073-f394-4d53-8f88-085392ef962b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15658,7 +15658,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{03fd9d7a-2e64-4d01-9696-92c12d9a6084}">
+          <x14:cfRule type="dataBar" id="{5b053cb1-32e9-4569-b494-16260e5b5169}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15669,7 +15669,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b2f4e5ba-b542-4c12-86ce-efd2bb8c0f8e}">
+          <x14:cfRule type="dataBar" id="{a416daad-1a04-4210-be59-2c47aebd646b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15680,14 +15680,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ce794363-64f0-47bc-8266-ba0d0bdda76d}">
+          <x14:cfRule type="dataBar" id="{c05bfbe1-677a-4e72-a5e9-3ddcdcd91791}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{882f8a97-1033-4b3b-b8af-abb28d9744ac}">
+          <x14:cfRule type="dataBar" id="{0c3ac258-0aae-4c56-a29e-307b554459a9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15698,7 +15698,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f881801f-d19c-4b87-b293-6ca372630341}">
+          <x14:cfRule type="dataBar" id="{e0ffb5aa-bfd9-41a0-b2bf-1618786fbf78}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15712,7 +15712,7 @@
           <xm:sqref>F69 F79 F89 F99 F109 F119 F129 F139 F149 F159 F169 F179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bbfaa7a7-6967-4c82-a231-a35df6bd90c6}">
+          <x14:cfRule type="dataBar" id="{2baf2adb-f5dd-4886-9484-2f91567d47fe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15721,7 +15721,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3d11fd74-fa72-4380-8dd3-c2615c82f20b}">
+          <x14:cfRule type="dataBar" id="{6e992747-c1dd-4839-8937-93cda052bc90}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15733,7 +15733,7 @@
           <xm:sqref>K69:K79 K85:K99 K105:K119 K125:K139 K145:K159 K165:K179 K185:K188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0453a3ce-4f05-43b7-b579-0b81cf798885}">
+          <x14:cfRule type="dataBar" id="{bcec06e0-7fdf-41bb-baeb-86db79142104}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15745,7 +15745,7 @@
           <xm:sqref>Y69:Y79 Y85:Y99 Y105:Y122 Y125:Y141 Y145:Y160 Y165:Y179 Y185:Y188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ace7eecc-7445-4a71-9da4-5fdc18c9125d}">
+          <x14:cfRule type="dataBar" id="{2bb3edf2-ef41-4b89-8eba-4336e031c8fd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15754,7 +15754,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5bbee154-e071-42b6-9cc9-2cdbc4007784}">
+          <x14:cfRule type="dataBar" id="{df963b0e-f6d0-47a1-adfc-16ce8a93bde2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15766,7 +15766,7 @@
           <xm:sqref>AB69 AB89 AB109 AB129 AB149 AB169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98ac6c31-4136-45c1-a36b-9b341cc87b37}">
+          <x14:cfRule type="dataBar" id="{20c6f949-6053-4cc0-8075-5f8eb1a7e95e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15775,7 +15775,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a21dfa89-d55f-4e78-9806-ec7e0a7eaafc}">
+          <x14:cfRule type="dataBar" id="{30937886-e39e-4674-8119-f01e136cb6de}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15785,7 +15785,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB122 AB125:AB141 AB145:AB160 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9e6c3b43-c290-4b3d-880b-14e317420c1a}">
+          <x14:cfRule type="dataBar" id="{e3e46d0e-063e-4d0c-accd-6d56a4bab023}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15797,7 +15797,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB119 AB125:AB139 AB145:AB159 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1bd3d8a2-60b4-42ff-befd-bdd6e86fd70f}">
+          <x14:cfRule type="dataBar" id="{5e2b9634-2899-42f6-b7ba-4a81d2ffaacd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15806,7 +15806,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24820b95-1715-4b32-b953-2083a4449190}">
+          <x14:cfRule type="dataBar" id="{8dcef961-86b5-4ad6-be71-67501977823d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15818,7 +15818,7 @@
           <xm:sqref>K80:K84 K100:K104 K120:K124 K140:K144 K160:K164 K180:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{51135e84-3859-4254-9f29-a142b75f6d4f}">
+          <x14:cfRule type="dataBar" id="{7504b37a-906a-4793-b586-5402b9f31916}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15830,7 +15830,7 @@
           <xm:sqref>Y80:Y84 Y100:Y104 Y120:Y124 Y140:Y144 Y160:Y164 Y180:Y184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6f9e9af7-0540-4dc6-8707-9aa58b293d4d}">
+          <x14:cfRule type="dataBar" id="{fa90b142-b3de-4bb9-bf2f-bcf29ac5b70d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15839,7 +15839,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{29797952-4392-4302-a531-b32a59ee9214}">
+          <x14:cfRule type="dataBar" id="{fe3a71be-9773-4135-ae28-327fc91a9b67}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15848,7 +15848,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6fd162f3-5a2b-483c-8ecb-9b2a43da661a}">
+          <x14:cfRule type="dataBar" id="{675156af-d591-420c-b24e-6bc461bc6654}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15858,7 +15858,7 @@
           <xm:sqref>AB80:AB84 AB100:AB104 AB120:AB124 AB140:AB144 AB160:AB164 AB180:AB184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ceb07929-f5b0-45be-acd9-3d08661b589f}">
+          <x14:cfRule type="dataBar" id="{a0e2513c-3c02-458e-b5c9-e59f1f4245a1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15867,7 +15867,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fbf61a3f-4bca-49cd-aaf0-64df60763cf9}">
+          <x14:cfRule type="dataBar" id="{a4f5b0fd-587b-4e58-a12e-13df145cabf0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15876,7 +15876,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d3adc8c1-60d2-4180-b19e-929b571f64b7}">
+          <x14:cfRule type="dataBar" id="{8fc10373-56f0-4c60-8962-b3a3eda64d8e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15888,7 +15888,7 @@
           <xm:sqref>F189 F194 F199 F204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c5e27f5e-4c84-4bf0-859a-39ee8ae56122}">
+          <x14:cfRule type="dataBar" id="{342580d6-d449-4484-a60b-e6c350faf848}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15897,7 +15897,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{98a09a73-5db7-47f2-84fb-56657499497f}">
+          <x14:cfRule type="dataBar" id="{fa83018a-8b97-4db1-816e-c01086817171}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15918,12 +15918,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/E楼交接班容量报表空模板.xlsx
+++ b/外网端源码/E楼交接班容量报表空模板.xlsx
@@ -685,39 +685,39 @@
     <t>-202-RPP-DC-001</t>
   </si>
   <si>
+    <t>-245-HVDC-112</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-003</t>
+  </si>
+  <si>
+    <t>-245-HVDC-122</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-005</t>
+  </si>
+  <si>
+    <t>-245-HVDC-132</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-007</t>
+  </si>
+  <si>
+    <t>-245-HVDC-142</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-009</t>
+  </si>
+  <si>
+    <t>-245-HVDC-152</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-011</t>
+  </si>
+  <si>
     <t>南侧</t>
   </si>
   <si>
-    <t>-245-HVDC-112</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-003</t>
-  </si>
-  <si>
-    <t>-245-HVDC-122</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-005</t>
-  </si>
-  <si>
-    <t>-245-HVDC-132</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-007</t>
-  </si>
-  <si>
-    <t>-245-HVDC-142</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-009</t>
-  </si>
-  <si>
-    <t>-245-HVDC-152</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-011</t>
-  </si>
-  <si>
     <t>-245-HVDC-162</t>
   </si>
   <si>
@@ -751,37 +751,37 @@
     <t>-202-RPP-DC-002</t>
   </si>
   <si>
+    <t>-245-HVDC-212</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-004</t>
+  </si>
+  <si>
+    <t>-245-HVDC-222</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-006</t>
+  </si>
+  <si>
+    <t>-245-HVDC-232</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-008</t>
+  </si>
+  <si>
+    <t>-245-HVDC-242</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-010</t>
+  </si>
+  <si>
+    <t>-245-HVDC-252</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-012</t>
+  </si>
+  <si>
     <t>北侧</t>
-  </si>
-  <si>
-    <t>-245-HVDC-212</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-004</t>
-  </si>
-  <si>
-    <t>-245-HVDC-222</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-006</t>
-  </si>
-  <si>
-    <t>-245-HVDC-232</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-008</t>
-  </si>
-  <si>
-    <t>-245-HVDC-242</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-010</t>
-  </si>
-  <si>
-    <t>-245-HVDC-252</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-012</t>
   </si>
   <si>
     <t>-245-HVDC-262</t>
@@ -6979,9 +6979,7 @@
         <f>20-AC69</f>
         <v>20</v>
       </c>
-      <c r="AE69" s="138" t="s">
-        <v>200</v>
-      </c>
+      <c r="AE69" s="138"/>
     </row>
     <row r="70" spans="1:31">
       <c r="A70" s="54"/>
@@ -6999,13 +6997,13 @@
       <c r="M70" s="54"/>
       <c r="N70" s="54"/>
       <c r="O70" s="146" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P70" s="147"/>
       <c r="Q70" s="147"/>
       <c r="R70" s="148"/>
       <c r="S70" s="149" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T70" s="150"/>
       <c r="U70" s="151">
@@ -7042,13 +7040,13 @@
       <c r="M71" s="54"/>
       <c r="N71" s="54"/>
       <c r="O71" s="146" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P71" s="147"/>
       <c r="Q71" s="147"/>
       <c r="R71" s="148"/>
       <c r="S71" s="149" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="T71" s="150"/>
       <c r="U71" s="151">
@@ -7085,13 +7083,13 @@
       <c r="M72" s="54"/>
       <c r="N72" s="54"/>
       <c r="O72" s="146" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P72" s="147"/>
       <c r="Q72" s="147"/>
       <c r="R72" s="148"/>
       <c r="S72" s="149" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T72" s="150"/>
       <c r="U72" s="151">
@@ -7128,13 +7126,13 @@
       <c r="M73" s="54"/>
       <c r="N73" s="54"/>
       <c r="O73" s="146" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P73" s="147"/>
       <c r="Q73" s="147"/>
       <c r="R73" s="148"/>
       <c r="S73" s="149" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T73" s="150"/>
       <c r="U73" s="151">
@@ -7171,13 +7169,13 @@
       <c r="M74" s="54"/>
       <c r="N74" s="54"/>
       <c r="O74" s="146" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P74" s="147"/>
       <c r="Q74" s="147"/>
       <c r="R74" s="148"/>
       <c r="S74" s="149" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="T74" s="150"/>
       <c r="U74" s="151">
@@ -7196,7 +7194,9 @@
       <c r="AB74" s="157"/>
       <c r="AC74" s="160"/>
       <c r="AD74" s="160"/>
-      <c r="AE74" s="138"/>
+      <c r="AE74" s="138" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="75" spans="1:31">
       <c r="A75" s="54"/>
@@ -7420,9 +7420,7 @@
       <c r="AB79" s="157"/>
       <c r="AC79" s="160"/>
       <c r="AD79" s="160"/>
-      <c r="AE79" s="147" t="s">
-        <v>222</v>
-      </c>
+      <c r="AE79" s="147"/>
     </row>
     <row r="80" spans="1:31">
       <c r="A80" s="54"/>
@@ -7440,13 +7438,13 @@
       <c r="M80" s="54"/>
       <c r="N80" s="54"/>
       <c r="O80" s="146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P80" s="147"/>
       <c r="Q80" s="147"/>
       <c r="R80" s="148"/>
       <c r="S80" s="163" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="T80" s="150"/>
       <c r="U80" s="151">
@@ -7483,13 +7481,13 @@
       <c r="M81" s="54"/>
       <c r="N81" s="54"/>
       <c r="O81" s="146" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P81" s="147"/>
       <c r="Q81" s="147"/>
       <c r="R81" s="148"/>
       <c r="S81" s="163" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T81" s="150"/>
       <c r="U81" s="151">
@@ -7526,13 +7524,13 @@
       <c r="M82" s="54"/>
       <c r="N82" s="54"/>
       <c r="O82" s="146" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P82" s="147"/>
       <c r="Q82" s="147"/>
       <c r="R82" s="148"/>
       <c r="S82" s="163" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T82" s="150"/>
       <c r="U82" s="151">
@@ -7569,13 +7567,13 @@
       <c r="M83" s="54"/>
       <c r="N83" s="54"/>
       <c r="O83" s="146" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P83" s="147"/>
       <c r="Q83" s="147"/>
       <c r="R83" s="148"/>
       <c r="S83" s="163" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="T83" s="150"/>
       <c r="U83" s="151">
@@ -7612,13 +7610,13 @@
       <c r="M84" s="54"/>
       <c r="N84" s="54"/>
       <c r="O84" s="146" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P84" s="147"/>
       <c r="Q84" s="147"/>
       <c r="R84" s="148"/>
       <c r="S84" s="163" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T84" s="150"/>
       <c r="U84" s="151">
@@ -7637,7 +7635,9 @@
       <c r="AB84" s="157"/>
       <c r="AC84" s="160"/>
       <c r="AD84" s="160"/>
-      <c r="AE84" s="138"/>
+      <c r="AE84" s="147" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="85" spans="1:31">
       <c r="A85" s="54"/>
@@ -7809,7 +7809,7 @@
       <c r="AB88" s="157"/>
       <c r="AC88" s="160"/>
       <c r="AD88" s="160"/>
-      <c r="AE88" s="54"/>
+      <c r="AE88" s="29"/>
     </row>
     <row r="89" spans="1:31">
       <c r="A89" s="138" t="s">
@@ -7890,9 +7890,7 @@
         <f>20-AC89</f>
         <v>20</v>
       </c>
-      <c r="AE89" s="138" t="s">
-        <v>200</v>
-      </c>
+      <c r="AE89" s="138"/>
     </row>
     <row r="90" spans="1:31">
       <c r="A90" s="54"/>
@@ -8107,7 +8105,9 @@
       <c r="AB94" s="157"/>
       <c r="AC94" s="160"/>
       <c r="AD94" s="160"/>
-      <c r="AE94" s="138"/>
+      <c r="AE94" s="138" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="95" spans="1:31">
       <c r="A95" s="54"/>
@@ -8331,9 +8331,7 @@
       <c r="AB99" s="157"/>
       <c r="AC99" s="160"/>
       <c r="AD99" s="160"/>
-      <c r="AE99" s="147" t="s">
-        <v>222</v>
-      </c>
+      <c r="AE99" s="147"/>
     </row>
     <row r="100" spans="1:31">
       <c r="A100" s="54"/>
@@ -8548,7 +8546,9 @@
       <c r="AB104" s="157"/>
       <c r="AC104" s="160"/>
       <c r="AD104" s="160"/>
-      <c r="AE104" s="138"/>
+      <c r="AE104" s="147" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="105" spans="1:31">
       <c r="A105" s="54"/>
@@ -8720,7 +8720,7 @@
       <c r="AB108" s="157"/>
       <c r="AC108" s="160"/>
       <c r="AD108" s="160"/>
-      <c r="AE108" s="54"/>
+      <c r="AE108" s="29"/>
     </row>
     <row r="109" spans="1:31">
       <c r="A109" s="138" t="s">
@@ -8801,9 +8801,7 @@
         <f>20-AC109</f>
         <v>20</v>
       </c>
-      <c r="AE109" s="138" t="s">
-        <v>200</v>
-      </c>
+      <c r="AE109" s="138"/>
     </row>
     <row r="110" spans="1:31">
       <c r="A110" s="54"/>
@@ -9018,7 +9016,9 @@
       <c r="AB114" s="157"/>
       <c r="AC114" s="160"/>
       <c r="AD114" s="160"/>
-      <c r="AE114" s="138"/>
+      <c r="AE114" s="138" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="115" spans="1:31">
       <c r="A115" s="54"/>
@@ -9242,9 +9242,7 @@
       <c r="AB119" s="157"/>
       <c r="AC119" s="160"/>
       <c r="AD119" s="160"/>
-      <c r="AE119" s="147" t="s">
-        <v>222</v>
-      </c>
+      <c r="AE119" s="147"/>
     </row>
     <row r="120" spans="1:31">
       <c r="A120" s="54"/>
@@ -9459,7 +9457,9 @@
       <c r="AB124" s="157"/>
       <c r="AC124" s="160"/>
       <c r="AD124" s="160"/>
-      <c r="AE124" s="138"/>
+      <c r="AE124" s="147" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="125" spans="1:31">
       <c r="A125" s="54"/>
@@ -9631,7 +9631,7 @@
       <c r="AB128" s="157"/>
       <c r="AC128" s="160"/>
       <c r="AD128" s="160"/>
-      <c r="AE128" s="54"/>
+      <c r="AE128" s="29"/>
     </row>
     <row r="129" spans="1:31">
       <c r="A129" s="138" t="s">
@@ -9712,9 +9712,7 @@
         <f>20-AC129</f>
         <v>20</v>
       </c>
-      <c r="AE129" s="138" t="s">
-        <v>200</v>
-      </c>
+      <c r="AE129" s="138"/>
     </row>
     <row r="130" spans="1:31">
       <c r="A130" s="54"/>
@@ -9929,7 +9927,9 @@
       <c r="AB134" s="157"/>
       <c r="AC134" s="160"/>
       <c r="AD134" s="160"/>
-      <c r="AE134" s="138"/>
+      <c r="AE134" s="138" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="135" spans="1:31">
       <c r="A135" s="54"/>
@@ -10153,9 +10153,7 @@
       <c r="AB139" s="157"/>
       <c r="AC139" s="160"/>
       <c r="AD139" s="160"/>
-      <c r="AE139" s="147" t="s">
-        <v>222</v>
-      </c>
+      <c r="AE139" s="147"/>
     </row>
     <row r="140" spans="1:31">
       <c r="A140" s="54"/>
@@ -10370,7 +10368,9 @@
       <c r="AB144" s="157"/>
       <c r="AC144" s="160"/>
       <c r="AD144" s="160"/>
-      <c r="AE144" s="138"/>
+      <c r="AE144" s="147" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="145" spans="1:31">
       <c r="A145" s="54"/>
@@ -10542,7 +10542,7 @@
       <c r="AB148" s="157"/>
       <c r="AC148" s="160"/>
       <c r="AD148" s="160"/>
-      <c r="AE148" s="54"/>
+      <c r="AE148" s="29"/>
     </row>
     <row r="149" spans="1:31">
       <c r="A149" s="138" t="s">
@@ -10623,9 +10623,7 @@
         <f>20-AC149</f>
         <v>20</v>
       </c>
-      <c r="AE149" s="138" t="s">
-        <v>200</v>
-      </c>
+      <c r="AE149" s="138"/>
     </row>
     <row r="150" spans="1:31">
       <c r="A150" s="54"/>
@@ -10840,7 +10838,9 @@
       <c r="AB154" s="157"/>
       <c r="AC154" s="160"/>
       <c r="AD154" s="160"/>
-      <c r="AE154" s="138"/>
+      <c r="AE154" s="138" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="155" spans="1:31">
       <c r="A155" s="54"/>
@@ -11064,9 +11064,7 @@
       <c r="AB159" s="157"/>
       <c r="AC159" s="160"/>
       <c r="AD159" s="160"/>
-      <c r="AE159" s="147" t="s">
-        <v>222</v>
-      </c>
+      <c r="AE159" s="147"/>
     </row>
     <row r="160" spans="1:31">
       <c r="A160" s="54"/>
@@ -11281,7 +11279,9 @@
       <c r="AB164" s="157"/>
       <c r="AC164" s="160"/>
       <c r="AD164" s="160"/>
-      <c r="AE164" s="138"/>
+      <c r="AE164" s="147" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="165" spans="1:31">
       <c r="A165" s="54"/>
@@ -11453,7 +11453,7 @@
       <c r="AB168" s="157"/>
       <c r="AC168" s="160"/>
       <c r="AD168" s="160"/>
-      <c r="AE168" s="54"/>
+      <c r="AE168" s="29"/>
     </row>
     <row r="169" spans="1:31">
       <c r="A169" s="138" t="s">
@@ -11534,9 +11534,7 @@
         <f>20-AC169</f>
         <v>20</v>
       </c>
-      <c r="AE169" s="138" t="s">
-        <v>200</v>
-      </c>
+      <c r="AE169" s="138"/>
     </row>
     <row r="170" spans="1:31">
       <c r="A170" s="54"/>
@@ -11751,7 +11749,9 @@
       <c r="AB174" s="174"/>
       <c r="AC174" s="147"/>
       <c r="AD174" s="147"/>
-      <c r="AE174" s="147"/>
+      <c r="AE174" s="138" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="175" spans="1:31">
       <c r="A175" s="54"/>
@@ -11923,7 +11923,7 @@
       <c r="AB178" s="174"/>
       <c r="AC178" s="147"/>
       <c r="AD178" s="147"/>
-      <c r="AE178" s="29"/>
+      <c r="AE178" s="54"/>
     </row>
     <row r="179" spans="1:31">
       <c r="A179" s="54"/>
@@ -11975,9 +11975,7 @@
       <c r="AB179" s="174"/>
       <c r="AC179" s="147"/>
       <c r="AD179" s="147"/>
-      <c r="AE179" s="147" t="s">
-        <v>222</v>
-      </c>
+      <c r="AE179" s="147"/>
     </row>
     <row r="180" spans="1:31">
       <c r="A180" s="54"/>
@@ -12192,7 +12190,9 @@
       <c r="AB184" s="174"/>
       <c r="AC184" s="147"/>
       <c r="AD184" s="147"/>
-      <c r="AE184" s="147"/>
+      <c r="AE184" s="147" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="185" spans="1:31">
       <c r="A185" s="54"/>
@@ -13915,7 +13915,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e69025c8-559e-43fb-9393-41f9f2b6ef9a}</x14:id>
+          <x14:id>{c40e1be4-278d-4106-a264-7e24c5834b93}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13927,7 +13927,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ebddf80-93cb-4280-8aa2-0f103db5f9bf}</x14:id>
+          <x14:id>{0c85f3b4-aa7f-47a5-83db-0528ca23762a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13939,7 +13939,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70182af8-b203-482b-b64b-511c62480cff}</x14:id>
+          <x14:id>{ac655ab4-f308-4c87-9e34-66966211f74b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13951,7 +13951,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17d69de9-2c40-4007-91da-96d5e2bccfc9}</x14:id>
+          <x14:id>{39f3fa74-b5bb-42a9-90a0-31b27d81a156}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13963,7 +13963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11a3c81e-8e19-4946-bd54-2159bf47b053}</x14:id>
+          <x14:id>{dc7c9479-6a77-493f-9145-7db90213dd91}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13975,7 +13975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1c78f4da-106d-4e5c-ba80-0ffc3254fbee}</x14:id>
+          <x14:id>{30c3fe1b-d5dd-44c8-b148-11530f542a1d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13987,7 +13987,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{080992cc-6e7f-4875-a7da-02e032e668d9}</x14:id>
+          <x14:id>{0b7294df-a2bb-4b0e-ab97-7ca90027e5bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13999,7 +13999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f87c4a9-ffab-4661-9dae-1ccd97a09aff}</x14:id>
+          <x14:id>{35412cb4-978f-440c-b230-f0db42b2754e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14013,7 +14013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{310aa0e6-fd63-4eec-80fd-996b8bcc183b}</x14:id>
+          <x14:id>{dd16fd2e-52e2-4aa3-831d-bf52846ced38}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14025,7 +14025,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72f609c2-e134-4e63-8f04-69e89a5f53ea}</x14:id>
+          <x14:id>{c0e07587-61e6-4e79-910f-93060dfbcbcf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14037,7 +14037,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31d1e55e-43f6-4a51-aae3-574a35aaba67}</x14:id>
+          <x14:id>{f4caf146-6bdf-4627-b2e6-c4ee091e0968}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14049,7 +14049,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6b8d69e2-a0c2-450d-b393-8d4a4cdd42a8}</x14:id>
+          <x14:id>{df0b6f11-684d-42bc-a71d-5fbfcb74a33c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14061,7 +14061,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{975100a4-0027-4ced-9a44-b81c961f7f23}</x14:id>
+          <x14:id>{6c113875-e799-4d6f-8e61-a582dc1cdef7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14073,7 +14073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa43619a-0e47-453c-9eb2-adb49815901e}</x14:id>
+          <x14:id>{e8642ac2-74de-494e-98f3-3b8a0681c56a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14085,7 +14085,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b789422e-e7c8-4149-8b9b-ecec20a10eb8}</x14:id>
+          <x14:id>{c0149164-5920-4a15-9fac-6b31478355fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14097,7 +14097,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{92ba0b23-948b-4a10-9754-024f51b9697b}</x14:id>
+          <x14:id>{5de8e3f1-4541-4290-acbf-6b8640c4d616}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14111,7 +14111,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{029ab547-7946-4c2b-8bb8-db24a5043cc7}</x14:id>
+          <x14:id>{897a118c-e709-4cb4-9ea2-09e3767f8e84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14123,7 +14123,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6ced779-0699-4f50-ba07-f6d25eec4562}</x14:id>
+          <x14:id>{f701364a-91a7-4d2f-aee2-d78e3ebafbd9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14135,7 +14135,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8711d0cc-e528-43a5-af6d-6634c254aa9b}</x14:id>
+          <x14:id>{7607fef3-d939-4f35-a1d9-cea40fcc6e4a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14147,7 +14147,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95f407b1-c930-458a-987e-251f02ef1a7a}</x14:id>
+          <x14:id>{94e02fdc-42e5-4fcd-a7b7-0652de76d0eb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14159,7 +14159,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e91a399f-a442-435c-9d47-f939fad1fb87}</x14:id>
+          <x14:id>{5aa23cf2-9cd6-4b4e-84fb-97deab5f8334}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14171,7 +14171,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0adfdaa5-aae5-4e8e-882c-c47ab0bb8477}</x14:id>
+          <x14:id>{b163d7bb-961f-461b-b611-d3514f16e8aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14183,7 +14183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f773e078-4ea2-4061-9315-43ccf3063d71}</x14:id>
+          <x14:id>{6ee7de2a-c64b-477b-bf28-1c3fa064396e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14195,7 +14195,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{195bdcec-1c2f-4184-a8be-686374fc19ee}</x14:id>
+          <x14:id>{5f657561-e127-4b6c-857b-5ed198b353ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14209,7 +14209,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3b5c84ff-ac18-441a-8b0f-540739fc3fe5}</x14:id>
+          <x14:id>{e3043095-6e12-46e7-a7a0-6d5a5358f5ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14221,7 +14221,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e3da8cf-0407-4eae-a0eb-8d41305c0cfb}</x14:id>
+          <x14:id>{57b164a5-f92d-4586-977a-113085003a0e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14233,7 +14233,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{baed23fd-0c47-4f6a-81b7-8c255e165ee1}</x14:id>
+          <x14:id>{0ca28bcd-5c4d-42cf-a372-6078af59dece}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14245,7 +14245,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{230ed903-e5c6-40aa-ab50-26990ec5395f}</x14:id>
+          <x14:id>{a17e448e-07ed-44e4-8b95-a2ad2979e999}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14257,7 +14257,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25c70917-357e-4cf6-bab6-62e069643fd5}</x14:id>
+          <x14:id>{ce8a9710-b39e-43e6-810e-f05a57791185}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14269,7 +14269,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe1dbc04-449f-4f35-8252-e20086f6b3be}</x14:id>
+          <x14:id>{3df6b351-2d04-41df-aefa-a61374bc9c65}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14281,7 +14281,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b6161a8e-b84c-4837-9d8a-f0c7016f75a1}</x14:id>
+          <x14:id>{f526af69-39d0-40c0-a5ed-13d1e7cca4a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14293,7 +14293,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a07ba539-32ac-48a7-8bc7-257d6a531679}</x14:id>
+          <x14:id>{394158f6-d98b-4c8e-8cd0-5486516e0d42}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14307,7 +14307,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{14646f47-c32a-4d79-a188-061d1e68be60}</x14:id>
+          <x14:id>{f2949406-5f7c-4870-a887-2712876dc7bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14319,7 +14319,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6a26bd8-8dac-4f9b-a943-258472e75480}</x14:id>
+          <x14:id>{89097dd5-fd26-4b44-a4a8-9b8c25fc8422}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14331,7 +14331,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1384be7b-5a30-48bd-86a5-72efaebc5448}</x14:id>
+          <x14:id>{3718532f-2ff6-492d-8042-dd0abe5080df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14343,7 +14343,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62ada315-f903-4c0e-bbd1-b996ef440691}</x14:id>
+          <x14:id>{ec2967a5-da46-4c5a-b61e-677c354e2a24}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14355,7 +14355,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{514871e6-80f1-44ba-9a7a-78dfbba1ca41}</x14:id>
+          <x14:id>{4a6a5449-c166-4316-9df4-240d723bda5f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14367,7 +14367,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4a8ca59-afdd-4dea-a531-c7c6bebea75b}</x14:id>
+          <x14:id>{60481860-bd00-4284-915f-72c5a9966c8b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14379,7 +14379,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{841e4f72-a497-4595-a91e-fa3747a9f405}</x14:id>
+          <x14:id>{3051ce84-c5aa-439c-a5ac-30465418d927}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14391,7 +14391,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ad6aba3-e584-4647-ada0-a4eb9ccf3c54}</x14:id>
+          <x14:id>{fdf3c70b-b3e6-4f21-9783-b785226562f8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14405,7 +14405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a366fa60-1629-4cc8-9379-a94a625465ff}</x14:id>
+          <x14:id>{5d22b24a-619b-4646-aefe-583694c1f3b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14417,7 +14417,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d9c50a9-ed3a-4545-9233-39402ea46431}</x14:id>
+          <x14:id>{d86ea441-ca3c-4de3-91cc-b7c7f228138d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14429,7 +14429,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65ff1913-4277-4b8c-ab3b-b09e28cd96ff}</x14:id>
+          <x14:id>{83669414-a64a-49e6-9074-04d52b5b9088}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14441,7 +14441,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{720b4bd5-e4c5-45d8-af61-37f1180cbdc9}</x14:id>
+          <x14:id>{9249d4bd-6f00-4282-956c-a540b35107d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14453,7 +14453,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aab55b8a-2d1c-4eba-9f62-08850b89ec40}</x14:id>
+          <x14:id>{fc38d306-1d05-4857-ba94-0a65cb63de36}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14465,7 +14465,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93b33f66-a8e0-46b6-a063-16c7e23f077e}</x14:id>
+          <x14:id>{c8338882-172e-409a-aac1-fd694d2aa7ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14477,7 +14477,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4b5045d-fc61-4c85-977e-7af67f6958ac}</x14:id>
+          <x14:id>{2650951a-eabb-4526-b1a8-4a0bf8a0e0aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14489,7 +14489,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c2000871-cf54-4cdc-8e92-bea515444809}</x14:id>
+          <x14:id>{036fc3dd-d7ef-450c-b80f-2a90a8010563}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14503,7 +14503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{120da751-a8b0-49fc-b428-d7cffd79f71e}</x14:id>
+          <x14:id>{1c8bb88c-e274-41d4-b450-16c6b1f9c69a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14515,7 +14515,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ffa15dc4-68c0-4cde-9b38-a589389f31e8}</x14:id>
+          <x14:id>{06bfb9c2-0037-42e2-8594-d5e57224ae5a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14527,7 +14527,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{69f08d15-215f-4fe2-a2f6-621be5a5eefe}</x14:id>
+          <x14:id>{a7e59c26-702c-4a11-8fb3-6ae198e5577a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14539,7 +14539,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dceb6f28-76ec-49a9-a962-f4ff76ebd3b0}</x14:id>
+          <x14:id>{4ac7ae8c-14cc-4b32-a0a5-0c8dcd18182b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14551,7 +14551,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3502f9fb-fd37-4e33-85d5-6adb168fe990}</x14:id>
+          <x14:id>{c07db04e-8e52-435f-b02d-890066091e2c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14563,7 +14563,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8223a483-38e5-4001-a893-15de51da55bf}</x14:id>
+          <x14:id>{a8b583c2-60b6-4949-a9f7-3db4acaddfce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14575,7 +14575,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b6d817ef-3bbf-42c7-bd39-2a7d7d44b24a}</x14:id>
+          <x14:id>{ca30cc9b-8a85-4778-a107-efe4cde796a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14587,7 +14587,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e930c886-6555-49ab-83b9-9790e2afb679}</x14:id>
+          <x14:id>{18b810cd-8d72-4ce6-b8bd-66025d4da631}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14601,7 +14601,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3e833661-5805-4370-abde-e9ca3b7e6cd5}</x14:id>
+          <x14:id>{de4713df-ccf1-4255-ad87-c2022c2b8548}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14615,7 +14615,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7988f45-ed1b-48ed-84ac-2ea92f052f48}</x14:id>
+          <x14:id>{c6ff0eaa-9a17-4cce-a01e-fb55b3744dc7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14629,7 +14629,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d922798b-51bb-4e52-9675-c73919ce9cd0}</x14:id>
+          <x14:id>{9f6ca779-035b-4889-98f7-dbd6e38f05e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14643,7 +14643,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea7d7bd9-065e-4d4f-84ae-c80079a43e7e}</x14:id>
+          <x14:id>{ccbd0073-0f96-4c36-9368-782b09cc43b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14655,7 +14655,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e00784ca-3989-42f5-8481-7818a1c35790}</x14:id>
+          <x14:id>{312a9e87-bfdd-4af4-a4cd-ea54fd284883}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14667,7 +14667,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44bbb073-f394-4d53-8f88-085392ef962b}</x14:id>
+          <x14:id>{34484f1c-dede-4c26-807c-7aa0c9b5222a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14679,7 +14679,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b053cb1-32e9-4569-b494-16260e5b5169}</x14:id>
+          <x14:id>{e553286a-a7f1-4159-8f2d-c889d995a0ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14691,7 +14691,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a416daad-1a04-4210-be59-2c47aebd646b}</x14:id>
+          <x14:id>{272bd141-86e7-4d4a-9763-24b6e9b51b46}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14703,7 +14703,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c05bfbe1-677a-4e72-a5e9-3ddcdcd91791}</x14:id>
+          <x14:id>{4422c80c-6161-4b21-9c82-f1302ed3e78d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14715,7 +14715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c3ac258-0aae-4c56-a29e-307b554459a9}</x14:id>
+          <x14:id>{01e66f98-1be7-42b7-afc8-779ed7c24498}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14727,7 +14727,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0ffb5aa-bfd9-41a0-b2bf-1618786fbf78}</x14:id>
+          <x14:id>{268da774-1dd7-4cf8-b413-0c139f5d1e92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14741,7 +14741,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2baf2adb-f5dd-4886-9484-2f91567d47fe}</x14:id>
+          <x14:id>{b89a8d9a-a668-40f0-a38c-e07ada4b5684}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14753,7 +14753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e992747-c1dd-4839-8937-93cda052bc90}</x14:id>
+          <x14:id>{c38d46eb-f1d5-4827-a62c-41375ccc41c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14767,7 +14767,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bcec06e0-7fdf-41bb-baeb-86db79142104}</x14:id>
+          <x14:id>{7bca7cf8-8dd4-4737-8f28-2bd9a2fff72a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14781,7 +14781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2bb3edf2-ef41-4b89-8eba-4336e031c8fd}</x14:id>
+          <x14:id>{cc68a2b7-4b14-4107-a2d4-fa62c6089904}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14793,7 +14793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{df963b0e-f6d0-47a1-adfc-16ce8a93bde2}</x14:id>
+          <x14:id>{476dd0d7-8df9-4e3f-9eb1-2176984aa8c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14807,7 +14807,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20c6f949-6053-4cc0-8075-5f8eb1a7e95e}</x14:id>
+          <x14:id>{4195e7ce-115d-4b6c-9733-bb54856a2382}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14819,7 +14819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30937886-e39e-4674-8119-f01e136cb6de}</x14:id>
+          <x14:id>{51d3565d-fafa-4f13-b4e0-25507d1d4f29}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14833,7 +14833,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3e46d0e-063e-4d0c-accd-6d56a4bab023}</x14:id>
+          <x14:id>{3593caf3-5d29-455c-9523-512d3cae2497}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14847,7 +14847,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e2b9634-2899-42f6-b7ba-4a81d2ffaacd}</x14:id>
+          <x14:id>{fbf79121-fdb9-4889-ac2b-a6379a6d531d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14859,7 +14859,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8dcef961-86b5-4ad6-be71-67501977823d}</x14:id>
+          <x14:id>{e3f44a6c-0207-4ba6-93f5-a92b74802171}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14873,7 +14873,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7504b37a-906a-4793-b586-5402b9f31916}</x14:id>
+          <x14:id>{e48f17ca-c21f-44a1-b4ab-4ec9ae07c35b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14887,7 +14887,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa90b142-b3de-4bb9-bf2f-bcf29ac5b70d}</x14:id>
+          <x14:id>{e08a880f-8924-48ab-80b4-76ee4df0a25f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14899,7 +14899,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe3a71be-9773-4135-ae28-327fc91a9b67}</x14:id>
+          <x14:id>{25e57e2f-5a16-4c86-ab38-ec670adce065}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14911,7 +14911,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{675156af-d591-420c-b24e-6bc461bc6654}</x14:id>
+          <x14:id>{83a64b92-9305-47ca-b4a4-b7d3e582f154}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14925,7 +14925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0e2513c-3c02-458e-b5c9-e59f1f4245a1}</x14:id>
+          <x14:id>{a971425e-24ea-4125-9f5e-5a98e4b2edc7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14937,7 +14937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4f5b0fd-587b-4e58-a12e-13df145cabf0}</x14:id>
+          <x14:id>{4df7c8ae-578e-45a0-ac53-39c0df692f16}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14949,7 +14949,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8fc10373-56f0-4c60-8962-b3a3eda64d8e}</x14:id>
+          <x14:id>{b9cdbe98-fd73-49cd-83be-3fe88a6ed795}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14963,7 +14963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{342580d6-d449-4484-a60b-e6c350faf848}</x14:id>
+          <x14:id>{55056ae2-7f42-460f-ada0-e3a57d775680}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14975,7 +14975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa83018a-8b97-4db1-816e-c01086817171}</x14:id>
+          <x14:id>{81466f92-5534-496c-88dc-62a6d1d8b070}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -15012,7 +15012,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e69025c8-559e-43fb-9393-41f9f2b6ef9a}">
+          <x14:cfRule type="dataBar" id="{c40e1be4-278d-4106-a264-7e24c5834b93}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15021,7 +15021,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2ebddf80-93cb-4280-8aa2-0f103db5f9bf}">
+          <x14:cfRule type="dataBar" id="{0c85f3b4-aa7f-47a5-83db-0528ca23762a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15030,7 +15030,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{70182af8-b203-482b-b64b-511c62480cff}">
+          <x14:cfRule type="dataBar" id="{ac655ab4-f308-4c87-9e34-66966211f74b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15041,7 +15041,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{17d69de9-2c40-4007-91da-96d5e2bccfc9}">
+          <x14:cfRule type="dataBar" id="{39f3fa74-b5bb-42a9-90a0-31b27d81a156}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15052,7 +15052,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{11a3c81e-8e19-4946-bd54-2159bf47b053}">
+          <x14:cfRule type="dataBar" id="{dc7c9479-6a77-493f-9145-7db90213dd91}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15063,14 +15063,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1c78f4da-106d-4e5c-ba80-0ffc3254fbee}">
+          <x14:cfRule type="dataBar" id="{30c3fe1b-d5dd-44c8-b148-11530f542a1d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{080992cc-6e7f-4875-a7da-02e032e668d9}">
+          <x14:cfRule type="dataBar" id="{0b7294df-a2bb-4b0e-ab97-7ca90027e5bb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15081,7 +15081,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0f87c4a9-ffab-4661-9dae-1ccd97a09aff}">
+          <x14:cfRule type="dataBar" id="{35412cb4-978f-440c-b230-f0db42b2754e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15095,7 +15095,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{310aa0e6-fd63-4eec-80fd-996b8bcc183b}">
+          <x14:cfRule type="dataBar" id="{dd16fd2e-52e2-4aa3-831d-bf52846ced38}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15104,7 +15104,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{72f609c2-e134-4e63-8f04-69e89a5f53ea}">
+          <x14:cfRule type="dataBar" id="{c0e07587-61e6-4e79-910f-93060dfbcbcf}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15113,7 +15113,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{31d1e55e-43f6-4a51-aae3-574a35aaba67}">
+          <x14:cfRule type="dataBar" id="{f4caf146-6bdf-4627-b2e6-c4ee091e0968}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15124,7 +15124,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6b8d69e2-a0c2-450d-b393-8d4a4cdd42a8}">
+          <x14:cfRule type="dataBar" id="{df0b6f11-684d-42bc-a71d-5fbfcb74a33c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15135,7 +15135,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{975100a4-0027-4ced-9a44-b81c961f7f23}">
+          <x14:cfRule type="dataBar" id="{6c113875-e799-4d6f-8e61-a582dc1cdef7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15146,14 +15146,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fa43619a-0e47-453c-9eb2-adb49815901e}">
+          <x14:cfRule type="dataBar" id="{e8642ac2-74de-494e-98f3-3b8a0681c56a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b789422e-e7c8-4149-8b9b-ecec20a10eb8}">
+          <x14:cfRule type="dataBar" id="{c0149164-5920-4a15-9fac-6b31478355fc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15164,7 +15164,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{92ba0b23-948b-4a10-9754-024f51b9697b}">
+          <x14:cfRule type="dataBar" id="{5de8e3f1-4541-4290-acbf-6b8640c4d616}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15178,7 +15178,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{029ab547-7946-4c2b-8bb8-db24a5043cc7}">
+          <x14:cfRule type="dataBar" id="{897a118c-e709-4cb4-9ea2-09e3767f8e84}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15187,7 +15187,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d6ced779-0699-4f50-ba07-f6d25eec4562}">
+          <x14:cfRule type="dataBar" id="{f701364a-91a7-4d2f-aee2-d78e3ebafbd9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15196,7 +15196,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8711d0cc-e528-43a5-af6d-6634c254aa9b}">
+          <x14:cfRule type="dataBar" id="{7607fef3-d939-4f35-a1d9-cea40fcc6e4a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15207,7 +15207,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{95f407b1-c930-458a-987e-251f02ef1a7a}">
+          <x14:cfRule type="dataBar" id="{94e02fdc-42e5-4fcd-a7b7-0652de76d0eb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15218,7 +15218,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e91a399f-a442-435c-9d47-f939fad1fb87}">
+          <x14:cfRule type="dataBar" id="{5aa23cf2-9cd6-4b4e-84fb-97deab5f8334}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15229,14 +15229,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0adfdaa5-aae5-4e8e-882c-c47ab0bb8477}">
+          <x14:cfRule type="dataBar" id="{b163d7bb-961f-461b-b611-d3514f16e8aa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f773e078-4ea2-4061-9315-43ccf3063d71}">
+          <x14:cfRule type="dataBar" id="{6ee7de2a-c64b-477b-bf28-1c3fa064396e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15247,7 +15247,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{195bdcec-1c2f-4184-a8be-686374fc19ee}">
+          <x14:cfRule type="dataBar" id="{5f657561-e127-4b6c-857b-5ed198b353ae}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15261,7 +15261,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3b5c84ff-ac18-441a-8b0f-540739fc3fe5}">
+          <x14:cfRule type="dataBar" id="{e3043095-6e12-46e7-a7a0-6d5a5358f5ae}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15270,7 +15270,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9e3da8cf-0407-4eae-a0eb-8d41305c0cfb}">
+          <x14:cfRule type="dataBar" id="{57b164a5-f92d-4586-977a-113085003a0e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15279,7 +15279,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{baed23fd-0c47-4f6a-81b7-8c255e165ee1}">
+          <x14:cfRule type="dataBar" id="{0ca28bcd-5c4d-42cf-a372-6078af59dece}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15290,7 +15290,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{230ed903-e5c6-40aa-ab50-26990ec5395f}">
+          <x14:cfRule type="dataBar" id="{a17e448e-07ed-44e4-8b95-a2ad2979e999}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15301,7 +15301,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25c70917-357e-4cf6-bab6-62e069643fd5}">
+          <x14:cfRule type="dataBar" id="{ce8a9710-b39e-43e6-810e-f05a57791185}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15312,14 +15312,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fe1dbc04-449f-4f35-8252-e20086f6b3be}">
+          <x14:cfRule type="dataBar" id="{3df6b351-2d04-41df-aefa-a61374bc9c65}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b6161a8e-b84c-4837-9d8a-f0c7016f75a1}">
+          <x14:cfRule type="dataBar" id="{f526af69-39d0-40c0-a5ed-13d1e7cca4a7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15330,7 +15330,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a07ba539-32ac-48a7-8bc7-257d6a531679}">
+          <x14:cfRule type="dataBar" id="{394158f6-d98b-4c8e-8cd0-5486516e0d42}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15344,7 +15344,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{14646f47-c32a-4d79-a188-061d1e68be60}">
+          <x14:cfRule type="dataBar" id="{f2949406-5f7c-4870-a887-2712876dc7bd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15353,7 +15353,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a6a26bd8-8dac-4f9b-a943-258472e75480}">
+          <x14:cfRule type="dataBar" id="{89097dd5-fd26-4b44-a4a8-9b8c25fc8422}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15362,7 +15362,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1384be7b-5a30-48bd-86a5-72efaebc5448}">
+          <x14:cfRule type="dataBar" id="{3718532f-2ff6-492d-8042-dd0abe5080df}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15373,7 +15373,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{62ada315-f903-4c0e-bbd1-b996ef440691}">
+          <x14:cfRule type="dataBar" id="{ec2967a5-da46-4c5a-b61e-677c354e2a24}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15384,7 +15384,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{514871e6-80f1-44ba-9a7a-78dfbba1ca41}">
+          <x14:cfRule type="dataBar" id="{4a6a5449-c166-4316-9df4-240d723bda5f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15395,14 +15395,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f4a8ca59-afdd-4dea-a531-c7c6bebea75b}">
+          <x14:cfRule type="dataBar" id="{60481860-bd00-4284-915f-72c5a9966c8b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{841e4f72-a497-4595-a91e-fa3747a9f405}">
+          <x14:cfRule type="dataBar" id="{3051ce84-c5aa-439c-a5ac-30465418d927}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15413,7 +15413,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8ad6aba3-e584-4647-ada0-a4eb9ccf3c54}">
+          <x14:cfRule type="dataBar" id="{fdf3c70b-b3e6-4f21-9783-b785226562f8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15427,7 +15427,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a366fa60-1629-4cc8-9379-a94a625465ff}">
+          <x14:cfRule type="dataBar" id="{5d22b24a-619b-4646-aefe-583694c1f3b1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15436,7 +15436,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6d9c50a9-ed3a-4545-9233-39402ea46431}">
+          <x14:cfRule type="dataBar" id="{d86ea441-ca3c-4de3-91cc-b7c7f228138d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15445,7 +15445,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{65ff1913-4277-4b8c-ab3b-b09e28cd96ff}">
+          <x14:cfRule type="dataBar" id="{83669414-a64a-49e6-9074-04d52b5b9088}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15456,7 +15456,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{720b4bd5-e4c5-45d8-af61-37f1180cbdc9}">
+          <x14:cfRule type="dataBar" id="{9249d4bd-6f00-4282-956c-a540b35107d0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15467,7 +15467,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aab55b8a-2d1c-4eba-9f62-08850b89ec40}">
+          <x14:cfRule type="dataBar" id="{fc38d306-1d05-4857-ba94-0a65cb63de36}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15478,14 +15478,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{93b33f66-a8e0-46b6-a063-16c7e23f077e}">
+          <x14:cfRule type="dataBar" id="{c8338882-172e-409a-aac1-fd694d2aa7ad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b4b5045d-fc61-4c85-977e-7af67f6958ac}">
+          <x14:cfRule type="dataBar" id="{2650951a-eabb-4526-b1a8-4a0bf8a0e0aa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15496,7 +15496,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c2000871-cf54-4cdc-8e92-bea515444809}">
+          <x14:cfRule type="dataBar" id="{036fc3dd-d7ef-450c-b80f-2a90a8010563}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15510,7 +15510,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{120da751-a8b0-49fc-b428-d7cffd79f71e}">
+          <x14:cfRule type="dataBar" id="{1c8bb88c-e274-41d4-b450-16c6b1f9c69a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15519,7 +15519,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ffa15dc4-68c0-4cde-9b38-a589389f31e8}">
+          <x14:cfRule type="dataBar" id="{06bfb9c2-0037-42e2-8594-d5e57224ae5a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15528,7 +15528,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{69f08d15-215f-4fe2-a2f6-621be5a5eefe}">
+          <x14:cfRule type="dataBar" id="{a7e59c26-702c-4a11-8fb3-6ae198e5577a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15539,7 +15539,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dceb6f28-76ec-49a9-a962-f4ff76ebd3b0}">
+          <x14:cfRule type="dataBar" id="{4ac7ae8c-14cc-4b32-a0a5-0c8dcd18182b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15550,7 +15550,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3502f9fb-fd37-4e33-85d5-6adb168fe990}">
+          <x14:cfRule type="dataBar" id="{c07db04e-8e52-435f-b02d-890066091e2c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15561,14 +15561,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8223a483-38e5-4001-a893-15de51da55bf}">
+          <x14:cfRule type="dataBar" id="{a8b583c2-60b6-4949-a9f7-3db4acaddfce}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b6d817ef-3bbf-42c7-bd39-2a7d7d44b24a}">
+          <x14:cfRule type="dataBar" id="{ca30cc9b-8a85-4778-a107-efe4cde796a0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15579,7 +15579,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e930c886-6555-49ab-83b9-9790e2afb679}">
+          <x14:cfRule type="dataBar" id="{18b810cd-8d72-4ce6-b8bd-66025d4da631}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15593,7 +15593,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3e833661-5805-4370-abde-e9ca3b7e6cd5}">
+          <x14:cfRule type="dataBar" id="{de4713df-ccf1-4255-ad87-c2022c2b8548}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15605,7 +15605,7 @@
           <xm:sqref>K189:K208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b7988f45-ed1b-48ed-84ac-2ea92f052f48}">
+          <x14:cfRule type="dataBar" id="{c6ff0eaa-9a17-4cce-a01e-fb55b3744dc7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15617,7 +15617,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d922798b-51bb-4e52-9675-c73919ce9cd0}">
+          <x14:cfRule type="dataBar" id="{9f6ca779-035b-4889-98f7-dbd6e38f05e0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15629,7 +15629,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ea7d7bd9-065e-4d4f-84ae-c80079a43e7e}">
+          <x14:cfRule type="dataBar" id="{ccbd0073-0f96-4c36-9368-782b09cc43b1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15638,7 +15638,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e00784ca-3989-42f5-8481-7818a1c35790}">
+          <x14:cfRule type="dataBar" id="{312a9e87-bfdd-4af4-a4cd-ea54fd284883}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15647,7 +15647,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{44bbb073-f394-4d53-8f88-085392ef962b}">
+          <x14:cfRule type="dataBar" id="{34484f1c-dede-4c26-807c-7aa0c9b5222a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15658,7 +15658,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5b053cb1-32e9-4569-b494-16260e5b5169}">
+          <x14:cfRule type="dataBar" id="{e553286a-a7f1-4159-8f2d-c889d995a0ad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15669,7 +15669,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a416daad-1a04-4210-be59-2c47aebd646b}">
+          <x14:cfRule type="dataBar" id="{272bd141-86e7-4d4a-9763-24b6e9b51b46}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15680,14 +15680,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c05bfbe1-677a-4e72-a5e9-3ddcdcd91791}">
+          <x14:cfRule type="dataBar" id="{4422c80c-6161-4b21-9c82-f1302ed3e78d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0c3ac258-0aae-4c56-a29e-307b554459a9}">
+          <x14:cfRule type="dataBar" id="{01e66f98-1be7-42b7-afc8-779ed7c24498}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15698,7 +15698,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e0ffb5aa-bfd9-41a0-b2bf-1618786fbf78}">
+          <x14:cfRule type="dataBar" id="{268da774-1dd7-4cf8-b413-0c139f5d1e92}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15712,7 +15712,7 @@
           <xm:sqref>F69 F79 F89 F99 F109 F119 F129 F139 F149 F159 F169 F179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2baf2adb-f5dd-4886-9484-2f91567d47fe}">
+          <x14:cfRule type="dataBar" id="{b89a8d9a-a668-40f0-a38c-e07ada4b5684}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15721,7 +15721,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6e992747-c1dd-4839-8937-93cda052bc90}">
+          <x14:cfRule type="dataBar" id="{c38d46eb-f1d5-4827-a62c-41375ccc41c3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15733,7 +15733,7 @@
           <xm:sqref>K69:K79 K85:K99 K105:K119 K125:K139 K145:K159 K165:K179 K185:K188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bcec06e0-7fdf-41bb-baeb-86db79142104}">
+          <x14:cfRule type="dataBar" id="{7bca7cf8-8dd4-4737-8f28-2bd9a2fff72a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15745,7 +15745,7 @@
           <xm:sqref>Y69:Y79 Y85:Y99 Y105:Y122 Y125:Y141 Y145:Y160 Y165:Y179 Y185:Y188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2bb3edf2-ef41-4b89-8eba-4336e031c8fd}">
+          <x14:cfRule type="dataBar" id="{cc68a2b7-4b14-4107-a2d4-fa62c6089904}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15754,7 +15754,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{df963b0e-f6d0-47a1-adfc-16ce8a93bde2}">
+          <x14:cfRule type="dataBar" id="{476dd0d7-8df9-4e3f-9eb1-2176984aa8c8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15766,7 +15766,7 @@
           <xm:sqref>AB69 AB89 AB109 AB129 AB149 AB169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20c6f949-6053-4cc0-8075-5f8eb1a7e95e}">
+          <x14:cfRule type="dataBar" id="{4195e7ce-115d-4b6c-9733-bb54856a2382}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15775,7 +15775,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{30937886-e39e-4674-8119-f01e136cb6de}">
+          <x14:cfRule type="dataBar" id="{51d3565d-fafa-4f13-b4e0-25507d1d4f29}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15785,7 +15785,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB122 AB125:AB141 AB145:AB160 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3e46d0e-063e-4d0c-accd-6d56a4bab023}">
+          <x14:cfRule type="dataBar" id="{3593caf3-5d29-455c-9523-512d3cae2497}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15797,7 +15797,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB119 AB125:AB139 AB145:AB159 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5e2b9634-2899-42f6-b7ba-4a81d2ffaacd}">
+          <x14:cfRule type="dataBar" id="{fbf79121-fdb9-4889-ac2b-a6379a6d531d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15806,7 +15806,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8dcef961-86b5-4ad6-be71-67501977823d}">
+          <x14:cfRule type="dataBar" id="{e3f44a6c-0207-4ba6-93f5-a92b74802171}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15818,7 +15818,7 @@
           <xm:sqref>K80:K84 K100:K104 K120:K124 K140:K144 K160:K164 K180:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7504b37a-906a-4793-b586-5402b9f31916}">
+          <x14:cfRule type="dataBar" id="{e48f17ca-c21f-44a1-b4ab-4ec9ae07c35b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15830,7 +15830,7 @@
           <xm:sqref>Y80:Y84 Y100:Y104 Y120:Y124 Y140:Y144 Y160:Y164 Y180:Y184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa90b142-b3de-4bb9-bf2f-bcf29ac5b70d}">
+          <x14:cfRule type="dataBar" id="{e08a880f-8924-48ab-80b4-76ee4df0a25f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15839,7 +15839,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fe3a71be-9773-4135-ae28-327fc91a9b67}">
+          <x14:cfRule type="dataBar" id="{25e57e2f-5a16-4c86-ab38-ec670adce065}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15848,7 +15848,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{675156af-d591-420c-b24e-6bc461bc6654}">
+          <x14:cfRule type="dataBar" id="{83a64b92-9305-47ca-b4a4-b7d3e582f154}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15858,7 +15858,7 @@
           <xm:sqref>AB80:AB84 AB100:AB104 AB120:AB124 AB140:AB144 AB160:AB164 AB180:AB184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a0e2513c-3c02-458e-b5c9-e59f1f4245a1}">
+          <x14:cfRule type="dataBar" id="{a971425e-24ea-4125-9f5e-5a98e4b2edc7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15867,7 +15867,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a4f5b0fd-587b-4e58-a12e-13df145cabf0}">
+          <x14:cfRule type="dataBar" id="{4df7c8ae-578e-45a0-ac53-39c0df692f16}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15876,7 +15876,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8fc10373-56f0-4c60-8962-b3a3eda64d8e}">
+          <x14:cfRule type="dataBar" id="{b9cdbe98-fd73-49cd-83be-3fe88a6ed795}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15888,7 +15888,7 @@
           <xm:sqref>F189 F194 F199 F204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{342580d6-d449-4484-a60b-e6c350faf848}">
+          <x14:cfRule type="dataBar" id="{55056ae2-7f42-460f-ada0-e3a57d775680}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15897,7 +15897,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fa83018a-8b97-4db1-816e-c01086817171}">
+          <x14:cfRule type="dataBar" id="{81466f92-5534-496c-88dc-62a6d1d8b070}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">

--- a/外网端源码/E楼交接班容量报表空模板.xlsx
+++ b/外网端源码/E楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="22020"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3569,27 +3569,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE211"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="11.7685185185185" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7727272727273" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1111111111111" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1090909090909" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
     <col min="20" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.3363636363636" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4926,10 +4926,7 @@
       <c r="AB29" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="AC29" s="86">
-        <f>(AC26+AC28)*2.25*2.25*3.14</f>
-        <v>0</v>
-      </c>
+      <c r="AC29" s="86"/>
       <c r="AD29" s="51"/>
       <c r="AE29" s="52"/>
     </row>
@@ -13915,7 +13912,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c40e1be4-278d-4106-a264-7e24c5834b93}</x14:id>
+          <x14:id>{2a2c2465-9cbe-4059-a294-fcb150c00287}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13927,7 +13924,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c85f3b4-aa7f-47a5-83db-0528ca23762a}</x14:id>
+          <x14:id>{60664661-4bf4-48da-bf41-33c4d311cfc1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13939,7 +13936,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac655ab4-f308-4c87-9e34-66966211f74b}</x14:id>
+          <x14:id>{39bf5488-c2e5-4543-8f2c-a086a0af2fff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13951,7 +13948,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39f3fa74-b5bb-42a9-90a0-31b27d81a156}</x14:id>
+          <x14:id>{de9d180d-986c-4a53-8051-6e77e0e5e51a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13963,7 +13960,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc7c9479-6a77-493f-9145-7db90213dd91}</x14:id>
+          <x14:id>{8b02f96c-5722-43bd-9a0f-c24ec2f09c83}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13975,7 +13972,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30c3fe1b-d5dd-44c8-b148-11530f542a1d}</x14:id>
+          <x14:id>{2dfc1457-42b7-4491-8754-3b8acaab34c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13987,7 +13984,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b7294df-a2bb-4b0e-ab97-7ca90027e5bb}</x14:id>
+          <x14:id>{f9013045-1599-40a5-b054-1c0ea3256e08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13999,7 +13996,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{35412cb4-978f-440c-b230-f0db42b2754e}</x14:id>
+          <x14:id>{10bff529-2451-4fd1-a442-0030786556b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14013,7 +14010,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd16fd2e-52e2-4aa3-831d-bf52846ced38}</x14:id>
+          <x14:id>{17e8ab09-d043-43c6-a5fa-db7eeaf01254}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14025,7 +14022,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0e07587-61e6-4e79-910f-93060dfbcbcf}</x14:id>
+          <x14:id>{6d5aa2ff-4473-4336-b782-7937efb05d0e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14037,7 +14034,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4caf146-6bdf-4627-b2e6-c4ee091e0968}</x14:id>
+          <x14:id>{b7c9da95-6629-4ac9-8f48-0169ba03a39a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14049,7 +14046,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{df0b6f11-684d-42bc-a71d-5fbfcb74a33c}</x14:id>
+          <x14:id>{776d3db5-a221-43eb-b53b-4b9f9449d1c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14061,7 +14058,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6c113875-e799-4d6f-8e61-a582dc1cdef7}</x14:id>
+          <x14:id>{5db2592b-9a65-4fa3-a123-05c7d0ef54f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14073,7 +14070,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8642ac2-74de-494e-98f3-3b8a0681c56a}</x14:id>
+          <x14:id>{259cc0da-6b3b-40ca-ad2e-04548061bcb7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14085,7 +14082,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0149164-5920-4a15-9fac-6b31478355fc}</x14:id>
+          <x14:id>{d0b08d30-5d17-4c18-8e28-d066c61b9175}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14097,7 +14094,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5de8e3f1-4541-4290-acbf-6b8640c4d616}</x14:id>
+          <x14:id>{7037856b-ab0a-4d0b-b62b-58b24fe13991}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14111,7 +14108,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{897a118c-e709-4cb4-9ea2-09e3767f8e84}</x14:id>
+          <x14:id>{1ce91822-6db3-440d-83ec-fce96996cc52}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14123,7 +14120,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f701364a-91a7-4d2f-aee2-d78e3ebafbd9}</x14:id>
+          <x14:id>{7161621b-d1f3-4ad8-955f-97c69b492705}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14135,7 +14132,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7607fef3-d939-4f35-a1d9-cea40fcc6e4a}</x14:id>
+          <x14:id>{b83df5e7-e4a6-4748-a041-c1ae85954415}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14147,7 +14144,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94e02fdc-42e5-4fcd-a7b7-0652de76d0eb}</x14:id>
+          <x14:id>{615c3daf-e96f-48f2-b915-31b3027739f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14159,7 +14156,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5aa23cf2-9cd6-4b4e-84fb-97deab5f8334}</x14:id>
+          <x14:id>{c8069e43-35fb-4a86-b3d4-660f535c7c4e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14171,7 +14168,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b163d7bb-961f-461b-b611-d3514f16e8aa}</x14:id>
+          <x14:id>{f9848bea-d77c-4f90-bd32-75284c0e7556}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14183,7 +14180,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ee7de2a-c64b-477b-bf28-1c3fa064396e}</x14:id>
+          <x14:id>{e979c5fe-b18d-445e-845c-f71e7f73bdef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14195,7 +14192,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f657561-e127-4b6c-857b-5ed198b353ae}</x14:id>
+          <x14:id>{c2928ba5-aa12-4acf-a2a1-5611cf430e89}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14209,7 +14206,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3043095-6e12-46e7-a7a0-6d5a5358f5ae}</x14:id>
+          <x14:id>{6b30dd63-7161-4d83-8dcd-ff25821581a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14221,7 +14218,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57b164a5-f92d-4586-977a-113085003a0e}</x14:id>
+          <x14:id>{132b64f5-9b15-4bae-8f65-1727d7ecdd59}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14233,7 +14230,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ca28bcd-5c4d-42cf-a372-6078af59dece}</x14:id>
+          <x14:id>{c6018057-4138-4807-be3b-837ad009b129}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14245,7 +14242,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a17e448e-07ed-44e4-8b95-a2ad2979e999}</x14:id>
+          <x14:id>{edfe1f0e-436b-4949-9e9e-3d70825238af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14257,7 +14254,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce8a9710-b39e-43e6-810e-f05a57791185}</x14:id>
+          <x14:id>{84c52f96-b9ba-4831-a191-217574eac302}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14269,7 +14266,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3df6b351-2d04-41df-aefa-a61374bc9c65}</x14:id>
+          <x14:id>{cc63a675-eee1-4a8f-af93-1684364366f7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14281,7 +14278,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f526af69-39d0-40c0-a5ed-13d1e7cca4a7}</x14:id>
+          <x14:id>{3c840df1-4703-4dbc-bb5f-e0fbc4dcbb23}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14293,7 +14290,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{394158f6-d98b-4c8e-8cd0-5486516e0d42}</x14:id>
+          <x14:id>{ae53b7d5-89ea-4853-9191-d6f3410ef85a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14307,7 +14304,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f2949406-5f7c-4870-a887-2712876dc7bd}</x14:id>
+          <x14:id>{0a99d4df-8188-4168-830b-971e93371ff3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14319,7 +14316,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89097dd5-fd26-4b44-a4a8-9b8c25fc8422}</x14:id>
+          <x14:id>{714f47ad-98f4-48db-a516-ed60ed61a345}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14331,7 +14328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3718532f-2ff6-492d-8042-dd0abe5080df}</x14:id>
+          <x14:id>{5d7bcb08-a093-4ea5-89f8-cb09beb52b4b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14343,7 +14340,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec2967a5-da46-4c5a-b61e-677c354e2a24}</x14:id>
+          <x14:id>{98afdc2c-91ef-4379-b6e7-87d381dc13bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14355,7 +14352,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a6a5449-c166-4316-9df4-240d723bda5f}</x14:id>
+          <x14:id>{12de7365-32b2-45b8-9322-54e32187363e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14367,7 +14364,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60481860-bd00-4284-915f-72c5a9966c8b}</x14:id>
+          <x14:id>{bedce6c4-2029-459e-81e1-24554d13a7bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14379,7 +14376,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3051ce84-c5aa-439c-a5ac-30465418d927}</x14:id>
+          <x14:id>{1a27c37f-3a93-4688-b1eb-940bff000bfe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14391,7 +14388,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fdf3c70b-b3e6-4f21-9783-b785226562f8}</x14:id>
+          <x14:id>{ce761ada-1c2e-411b-8fb8-81d4a564d17b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14405,7 +14402,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d22b24a-619b-4646-aefe-583694c1f3b1}</x14:id>
+          <x14:id>{9442d5db-3982-49dc-8b11-7dbbd45a4c3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14417,7 +14414,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d86ea441-ca3c-4de3-91cc-b7c7f228138d}</x14:id>
+          <x14:id>{a8c719b1-1195-400f-9b88-bbada0aa6cf0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14429,7 +14426,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83669414-a64a-49e6-9074-04d52b5b9088}</x14:id>
+          <x14:id>{ec68b21b-f8e5-4298-8232-acda1c5f3106}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14441,7 +14438,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9249d4bd-6f00-4282-956c-a540b35107d0}</x14:id>
+          <x14:id>{37fca897-6493-42c8-b404-cc30480ead32}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14453,7 +14450,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc38d306-1d05-4857-ba94-0a65cb63de36}</x14:id>
+          <x14:id>{8f4281eb-93f9-4bb5-a917-5d31520ab947}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14465,7 +14462,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8338882-172e-409a-aac1-fd694d2aa7ad}</x14:id>
+          <x14:id>{e3e07f98-bb83-4fb7-b661-1538626e768d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14477,7 +14474,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2650951a-eabb-4526-b1a8-4a0bf8a0e0aa}</x14:id>
+          <x14:id>{56f8458e-9a11-4af7-87fc-e63c6449fa49}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14489,7 +14486,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{036fc3dd-d7ef-450c-b80f-2a90a8010563}</x14:id>
+          <x14:id>{ada193e0-e93a-40e9-8893-bed75a6cad42}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14503,7 +14500,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1c8bb88c-e274-41d4-b450-16c6b1f9c69a}</x14:id>
+          <x14:id>{6a01d7eb-946e-4fd8-a2f3-0b32537aebd2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14515,7 +14512,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06bfb9c2-0037-42e2-8594-d5e57224ae5a}</x14:id>
+          <x14:id>{4a12e577-f4a3-4c5a-bb88-0e755b68ce31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14527,7 +14524,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7e59c26-702c-4a11-8fb3-6ae198e5577a}</x14:id>
+          <x14:id>{46737dc3-7f8d-4cd9-95e9-ad97acb99474}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14539,7 +14536,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ac7ae8c-14cc-4b32-a0a5-0c8dcd18182b}</x14:id>
+          <x14:id>{a2b0da28-620f-427d-bd25-a16970a3855a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14551,7 +14548,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c07db04e-8e52-435f-b02d-890066091e2c}</x14:id>
+          <x14:id>{97dc999a-bd38-4c40-9ab3-2c6484bf41b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14563,7 +14560,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a8b583c2-60b6-4949-a9f7-3db4acaddfce}</x14:id>
+          <x14:id>{0f4539e3-ae11-4e8e-9159-28a1edda49e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14575,7 +14572,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca30cc9b-8a85-4778-a107-efe4cde796a0}</x14:id>
+          <x14:id>{dcf8ac93-e7dc-4174-849d-f5e43d811be3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14587,7 +14584,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18b810cd-8d72-4ce6-b8bd-66025d4da631}</x14:id>
+          <x14:id>{422ca164-99bf-4659-b450-60222c166e9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14601,7 +14598,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{de4713df-ccf1-4255-ad87-c2022c2b8548}</x14:id>
+          <x14:id>{74fa9c89-46fe-4151-959f-8692e6b2b4b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14615,7 +14612,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6ff0eaa-9a17-4cce-a01e-fb55b3744dc7}</x14:id>
+          <x14:id>{956bb591-e475-4a6a-97d7-57f0f2655eb3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14629,7 +14626,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9f6ca779-035b-4889-98f7-dbd6e38f05e0}</x14:id>
+          <x14:id>{144d872f-8199-472a-9eae-b618e4eb3bdc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14643,7 +14640,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ccbd0073-0f96-4c36-9368-782b09cc43b1}</x14:id>
+          <x14:id>{774c96fc-4df3-434f-8437-6d2b5ef08316}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14655,7 +14652,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{312a9e87-bfdd-4af4-a4cd-ea54fd284883}</x14:id>
+          <x14:id>{2e08eccf-058f-4176-beaa-9760e3b60e23}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14667,7 +14664,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34484f1c-dede-4c26-807c-7aa0c9b5222a}</x14:id>
+          <x14:id>{234c38a5-6a0e-4f6f-9bd6-d41884b60382}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14679,7 +14676,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e553286a-a7f1-4159-8f2d-c889d995a0ad}</x14:id>
+          <x14:id>{b7dfe95f-2db8-439f-9742-c288eaf9f1db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14691,7 +14688,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{272bd141-86e7-4d4a-9763-24b6e9b51b46}</x14:id>
+          <x14:id>{5ab5a418-b6cf-4fa8-b1ca-a44e6903d772}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14703,7 +14700,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4422c80c-6161-4b21-9c82-f1302ed3e78d}</x14:id>
+          <x14:id>{f6b09007-b622-4931-a61d-9e62bdca3968}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14715,7 +14712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{01e66f98-1be7-42b7-afc8-779ed7c24498}</x14:id>
+          <x14:id>{e35b0d44-a651-46c4-adc9-e6b85bdfd828}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14727,7 +14724,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{268da774-1dd7-4cf8-b413-0c139f5d1e92}</x14:id>
+          <x14:id>{6731f847-25e3-4846-a291-9d9362a4042f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14741,7 +14738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b89a8d9a-a668-40f0-a38c-e07ada4b5684}</x14:id>
+          <x14:id>{7e1736a9-675c-4bf1-9efc-df3ef6b80103}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14753,7 +14750,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c38d46eb-f1d5-4827-a62c-41375ccc41c3}</x14:id>
+          <x14:id>{e2addf6e-34c4-435c-8189-21735616c8cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14767,7 +14764,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7bca7cf8-8dd4-4737-8f28-2bd9a2fff72a}</x14:id>
+          <x14:id>{402779bc-f0f7-48b0-a209-51a683b3db86}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14781,7 +14778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cc68a2b7-4b14-4107-a2d4-fa62c6089904}</x14:id>
+          <x14:id>{88656c94-176a-4b1f-86cf-f53519eff006}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14793,7 +14790,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{476dd0d7-8df9-4e3f-9eb1-2176984aa8c8}</x14:id>
+          <x14:id>{325dce8d-515e-436e-9dc1-9c3b194ec07a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14807,7 +14804,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4195e7ce-115d-4b6c-9733-bb54856a2382}</x14:id>
+          <x14:id>{eacf90e0-a5b6-48eb-a87d-7b64a49d5f07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14819,7 +14816,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51d3565d-fafa-4f13-b4e0-25507d1d4f29}</x14:id>
+          <x14:id>{ccabf301-0640-4884-bdc9-92714fdbd8f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14833,7 +14830,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3593caf3-5d29-455c-9523-512d3cae2497}</x14:id>
+          <x14:id>{c5ef9107-581a-479e-8395-322f5bb70e80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14847,7 +14844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fbf79121-fdb9-4889-ac2b-a6379a6d531d}</x14:id>
+          <x14:id>{f90cb22d-ea7a-4dbf-9092-503242a88888}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14859,7 +14856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3f44a6c-0207-4ba6-93f5-a92b74802171}</x14:id>
+          <x14:id>{73a1d383-7b26-444a-8dd5-85e97f8e47a9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14873,7 +14870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e48f17ca-c21f-44a1-b4ab-4ec9ae07c35b}</x14:id>
+          <x14:id>{2b3222c0-bb38-4dcf-941a-c3f9c3bafb4c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14887,7 +14884,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e08a880f-8924-48ab-80b4-76ee4df0a25f}</x14:id>
+          <x14:id>{fc1a3a2b-2822-4730-8fbd-7cdf8e55ef60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14899,7 +14896,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25e57e2f-5a16-4c86-ab38-ec670adce065}</x14:id>
+          <x14:id>{873f57c6-99c7-4ef3-a780-316edcbbf315}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14911,7 +14908,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83a64b92-9305-47ca-b4a4-b7d3e582f154}</x14:id>
+          <x14:id>{1941e2d8-9f56-4654-97ee-f19df384e309}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14925,7 +14922,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a971425e-24ea-4125-9f5e-5a98e4b2edc7}</x14:id>
+          <x14:id>{1d6eb9bf-dae9-4855-837d-b0872b4b71ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14937,7 +14934,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4df7c8ae-578e-45a0-ac53-39c0df692f16}</x14:id>
+          <x14:id>{34d4c11d-a0f9-4f23-a982-d230ce51a843}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14949,7 +14946,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b9cdbe98-fd73-49cd-83be-3fe88a6ed795}</x14:id>
+          <x14:id>{9bc1a219-9258-4dfa-9115-c76d05799ed4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14963,7 +14960,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55056ae2-7f42-460f-ada0-e3a57d775680}</x14:id>
+          <x14:id>{40498ad4-c6f7-4c9c-9103-c0fb66bde84f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14975,7 +14972,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81466f92-5534-496c-88dc-62a6d1d8b070}</x14:id>
+          <x14:id>{b119c34c-0b3c-4c1d-82d4-4c149339eefa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -15012,7 +15009,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c40e1be4-278d-4106-a264-7e24c5834b93}">
+          <x14:cfRule type="dataBar" id="{2a2c2465-9cbe-4059-a294-fcb150c00287}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15021,7 +15018,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0c85f3b4-aa7f-47a5-83db-0528ca23762a}">
+          <x14:cfRule type="dataBar" id="{60664661-4bf4-48da-bf41-33c4d311cfc1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15030,7 +15027,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ac655ab4-f308-4c87-9e34-66966211f74b}">
+          <x14:cfRule type="dataBar" id="{39bf5488-c2e5-4543-8f2c-a086a0af2fff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15041,7 +15038,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{39f3fa74-b5bb-42a9-90a0-31b27d81a156}">
+          <x14:cfRule type="dataBar" id="{de9d180d-986c-4a53-8051-6e77e0e5e51a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15052,7 +15049,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dc7c9479-6a77-493f-9145-7db90213dd91}">
+          <x14:cfRule type="dataBar" id="{8b02f96c-5722-43bd-9a0f-c24ec2f09c83}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15063,14 +15060,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{30c3fe1b-d5dd-44c8-b148-11530f542a1d}">
+          <x14:cfRule type="dataBar" id="{2dfc1457-42b7-4491-8754-3b8acaab34c3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0b7294df-a2bb-4b0e-ab97-7ca90027e5bb}">
+          <x14:cfRule type="dataBar" id="{f9013045-1599-40a5-b054-1c0ea3256e08}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15081,7 +15078,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{35412cb4-978f-440c-b230-f0db42b2754e}">
+          <x14:cfRule type="dataBar" id="{10bff529-2451-4fd1-a442-0030786556b9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15095,7 +15092,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd16fd2e-52e2-4aa3-831d-bf52846ced38}">
+          <x14:cfRule type="dataBar" id="{17e8ab09-d043-43c6-a5fa-db7eeaf01254}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15104,7 +15101,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c0e07587-61e6-4e79-910f-93060dfbcbcf}">
+          <x14:cfRule type="dataBar" id="{6d5aa2ff-4473-4336-b782-7937efb05d0e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15113,7 +15110,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f4caf146-6bdf-4627-b2e6-c4ee091e0968}">
+          <x14:cfRule type="dataBar" id="{b7c9da95-6629-4ac9-8f48-0169ba03a39a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15124,7 +15121,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{df0b6f11-684d-42bc-a71d-5fbfcb74a33c}">
+          <x14:cfRule type="dataBar" id="{776d3db5-a221-43eb-b53b-4b9f9449d1c2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15135,7 +15132,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6c113875-e799-4d6f-8e61-a582dc1cdef7}">
+          <x14:cfRule type="dataBar" id="{5db2592b-9a65-4fa3-a123-05c7d0ef54f6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15146,14 +15143,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e8642ac2-74de-494e-98f3-3b8a0681c56a}">
+          <x14:cfRule type="dataBar" id="{259cc0da-6b3b-40ca-ad2e-04548061bcb7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c0149164-5920-4a15-9fac-6b31478355fc}">
+          <x14:cfRule type="dataBar" id="{d0b08d30-5d17-4c18-8e28-d066c61b9175}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15164,7 +15161,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5de8e3f1-4541-4290-acbf-6b8640c4d616}">
+          <x14:cfRule type="dataBar" id="{7037856b-ab0a-4d0b-b62b-58b24fe13991}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15178,7 +15175,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{897a118c-e709-4cb4-9ea2-09e3767f8e84}">
+          <x14:cfRule type="dataBar" id="{1ce91822-6db3-440d-83ec-fce96996cc52}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15187,7 +15184,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f701364a-91a7-4d2f-aee2-d78e3ebafbd9}">
+          <x14:cfRule type="dataBar" id="{7161621b-d1f3-4ad8-955f-97c69b492705}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15196,7 +15193,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7607fef3-d939-4f35-a1d9-cea40fcc6e4a}">
+          <x14:cfRule type="dataBar" id="{b83df5e7-e4a6-4748-a041-c1ae85954415}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15207,7 +15204,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{94e02fdc-42e5-4fcd-a7b7-0652de76d0eb}">
+          <x14:cfRule type="dataBar" id="{615c3daf-e96f-48f2-b915-31b3027739f0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15218,7 +15215,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5aa23cf2-9cd6-4b4e-84fb-97deab5f8334}">
+          <x14:cfRule type="dataBar" id="{c8069e43-35fb-4a86-b3d4-660f535c7c4e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15229,14 +15226,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b163d7bb-961f-461b-b611-d3514f16e8aa}">
+          <x14:cfRule type="dataBar" id="{f9848bea-d77c-4f90-bd32-75284c0e7556}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6ee7de2a-c64b-477b-bf28-1c3fa064396e}">
+          <x14:cfRule type="dataBar" id="{e979c5fe-b18d-445e-845c-f71e7f73bdef}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15247,7 +15244,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5f657561-e127-4b6c-857b-5ed198b353ae}">
+          <x14:cfRule type="dataBar" id="{c2928ba5-aa12-4acf-a2a1-5611cf430e89}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15261,7 +15258,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3043095-6e12-46e7-a7a0-6d5a5358f5ae}">
+          <x14:cfRule type="dataBar" id="{6b30dd63-7161-4d83-8dcd-ff25821581a1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15270,7 +15267,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{57b164a5-f92d-4586-977a-113085003a0e}">
+          <x14:cfRule type="dataBar" id="{132b64f5-9b15-4bae-8f65-1727d7ecdd59}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15279,7 +15276,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0ca28bcd-5c4d-42cf-a372-6078af59dece}">
+          <x14:cfRule type="dataBar" id="{c6018057-4138-4807-be3b-837ad009b129}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15290,7 +15287,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a17e448e-07ed-44e4-8b95-a2ad2979e999}">
+          <x14:cfRule type="dataBar" id="{edfe1f0e-436b-4949-9e9e-3d70825238af}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15301,7 +15298,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ce8a9710-b39e-43e6-810e-f05a57791185}">
+          <x14:cfRule type="dataBar" id="{84c52f96-b9ba-4831-a191-217574eac302}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15312,14 +15309,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3df6b351-2d04-41df-aefa-a61374bc9c65}">
+          <x14:cfRule type="dataBar" id="{cc63a675-eee1-4a8f-af93-1684364366f7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f526af69-39d0-40c0-a5ed-13d1e7cca4a7}">
+          <x14:cfRule type="dataBar" id="{3c840df1-4703-4dbc-bb5f-e0fbc4dcbb23}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15330,7 +15327,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{394158f6-d98b-4c8e-8cd0-5486516e0d42}">
+          <x14:cfRule type="dataBar" id="{ae53b7d5-89ea-4853-9191-d6f3410ef85a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15344,7 +15341,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f2949406-5f7c-4870-a887-2712876dc7bd}">
+          <x14:cfRule type="dataBar" id="{0a99d4df-8188-4168-830b-971e93371ff3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15353,7 +15350,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{89097dd5-fd26-4b44-a4a8-9b8c25fc8422}">
+          <x14:cfRule type="dataBar" id="{714f47ad-98f4-48db-a516-ed60ed61a345}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15362,7 +15359,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3718532f-2ff6-492d-8042-dd0abe5080df}">
+          <x14:cfRule type="dataBar" id="{5d7bcb08-a093-4ea5-89f8-cb09beb52b4b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15373,7 +15370,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ec2967a5-da46-4c5a-b61e-677c354e2a24}">
+          <x14:cfRule type="dataBar" id="{98afdc2c-91ef-4379-b6e7-87d381dc13bd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15384,7 +15381,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4a6a5449-c166-4316-9df4-240d723bda5f}">
+          <x14:cfRule type="dataBar" id="{12de7365-32b2-45b8-9322-54e32187363e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15395,14 +15392,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{60481860-bd00-4284-915f-72c5a9966c8b}">
+          <x14:cfRule type="dataBar" id="{bedce6c4-2029-459e-81e1-24554d13a7bd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3051ce84-c5aa-439c-a5ac-30465418d927}">
+          <x14:cfRule type="dataBar" id="{1a27c37f-3a93-4688-b1eb-940bff000bfe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15413,7 +15410,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fdf3c70b-b3e6-4f21-9783-b785226562f8}">
+          <x14:cfRule type="dataBar" id="{ce761ada-1c2e-411b-8fb8-81d4a564d17b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15427,7 +15424,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d22b24a-619b-4646-aefe-583694c1f3b1}">
+          <x14:cfRule type="dataBar" id="{9442d5db-3982-49dc-8b11-7dbbd45a4c3a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15436,7 +15433,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d86ea441-ca3c-4de3-91cc-b7c7f228138d}">
+          <x14:cfRule type="dataBar" id="{a8c719b1-1195-400f-9b88-bbada0aa6cf0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15445,7 +15442,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{83669414-a64a-49e6-9074-04d52b5b9088}">
+          <x14:cfRule type="dataBar" id="{ec68b21b-f8e5-4298-8232-acda1c5f3106}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15456,7 +15453,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9249d4bd-6f00-4282-956c-a540b35107d0}">
+          <x14:cfRule type="dataBar" id="{37fca897-6493-42c8-b404-cc30480ead32}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15467,7 +15464,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fc38d306-1d05-4857-ba94-0a65cb63de36}">
+          <x14:cfRule type="dataBar" id="{8f4281eb-93f9-4bb5-a917-5d31520ab947}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15478,14 +15475,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c8338882-172e-409a-aac1-fd694d2aa7ad}">
+          <x14:cfRule type="dataBar" id="{e3e07f98-bb83-4fb7-b661-1538626e768d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2650951a-eabb-4526-b1a8-4a0bf8a0e0aa}">
+          <x14:cfRule type="dataBar" id="{56f8458e-9a11-4af7-87fc-e63c6449fa49}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15496,7 +15493,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{036fc3dd-d7ef-450c-b80f-2a90a8010563}">
+          <x14:cfRule type="dataBar" id="{ada193e0-e93a-40e9-8893-bed75a6cad42}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15510,7 +15507,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1c8bb88c-e274-41d4-b450-16c6b1f9c69a}">
+          <x14:cfRule type="dataBar" id="{6a01d7eb-946e-4fd8-a2f3-0b32537aebd2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15519,7 +15516,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{06bfb9c2-0037-42e2-8594-d5e57224ae5a}">
+          <x14:cfRule type="dataBar" id="{4a12e577-f4a3-4c5a-bb88-0e755b68ce31}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15528,7 +15525,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a7e59c26-702c-4a11-8fb3-6ae198e5577a}">
+          <x14:cfRule type="dataBar" id="{46737dc3-7f8d-4cd9-95e9-ad97acb99474}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15539,7 +15536,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4ac7ae8c-14cc-4b32-a0a5-0c8dcd18182b}">
+          <x14:cfRule type="dataBar" id="{a2b0da28-620f-427d-bd25-a16970a3855a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15550,7 +15547,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c07db04e-8e52-435f-b02d-890066091e2c}">
+          <x14:cfRule type="dataBar" id="{97dc999a-bd38-4c40-9ab3-2c6484bf41b7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15561,14 +15558,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a8b583c2-60b6-4949-a9f7-3db4acaddfce}">
+          <x14:cfRule type="dataBar" id="{0f4539e3-ae11-4e8e-9159-28a1edda49e1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ca30cc9b-8a85-4778-a107-efe4cde796a0}">
+          <x14:cfRule type="dataBar" id="{dcf8ac93-e7dc-4174-849d-f5e43d811be3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15579,7 +15576,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{18b810cd-8d72-4ce6-b8bd-66025d4da631}">
+          <x14:cfRule type="dataBar" id="{422ca164-99bf-4659-b450-60222c166e9d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15593,7 +15590,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{de4713df-ccf1-4255-ad87-c2022c2b8548}">
+          <x14:cfRule type="dataBar" id="{74fa9c89-46fe-4151-959f-8692e6b2b4b7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15605,7 +15602,7 @@
           <xm:sqref>K189:K208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c6ff0eaa-9a17-4cce-a01e-fb55b3744dc7}">
+          <x14:cfRule type="dataBar" id="{956bb591-e475-4a6a-97d7-57f0f2655eb3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15617,7 +15614,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9f6ca779-035b-4889-98f7-dbd6e38f05e0}">
+          <x14:cfRule type="dataBar" id="{144d872f-8199-472a-9eae-b618e4eb3bdc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15629,7 +15626,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ccbd0073-0f96-4c36-9368-782b09cc43b1}">
+          <x14:cfRule type="dataBar" id="{774c96fc-4df3-434f-8437-6d2b5ef08316}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15638,7 +15635,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{312a9e87-bfdd-4af4-a4cd-ea54fd284883}">
+          <x14:cfRule type="dataBar" id="{2e08eccf-058f-4176-beaa-9760e3b60e23}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15647,7 +15644,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{34484f1c-dede-4c26-807c-7aa0c9b5222a}">
+          <x14:cfRule type="dataBar" id="{234c38a5-6a0e-4f6f-9bd6-d41884b60382}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15658,7 +15655,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e553286a-a7f1-4159-8f2d-c889d995a0ad}">
+          <x14:cfRule type="dataBar" id="{b7dfe95f-2db8-439f-9742-c288eaf9f1db}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15669,7 +15666,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{272bd141-86e7-4d4a-9763-24b6e9b51b46}">
+          <x14:cfRule type="dataBar" id="{5ab5a418-b6cf-4fa8-b1ca-a44e6903d772}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15680,14 +15677,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4422c80c-6161-4b21-9c82-f1302ed3e78d}">
+          <x14:cfRule type="dataBar" id="{f6b09007-b622-4931-a61d-9e62bdca3968}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{01e66f98-1be7-42b7-afc8-779ed7c24498}">
+          <x14:cfRule type="dataBar" id="{e35b0d44-a651-46c4-adc9-e6b85bdfd828}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15698,7 +15695,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{268da774-1dd7-4cf8-b413-0c139f5d1e92}">
+          <x14:cfRule type="dataBar" id="{6731f847-25e3-4846-a291-9d9362a4042f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15712,7 +15709,7 @@
           <xm:sqref>F69 F79 F89 F99 F109 F119 F129 F139 F149 F159 F169 F179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b89a8d9a-a668-40f0-a38c-e07ada4b5684}">
+          <x14:cfRule type="dataBar" id="{7e1736a9-675c-4bf1-9efc-df3ef6b80103}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15721,7 +15718,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c38d46eb-f1d5-4827-a62c-41375ccc41c3}">
+          <x14:cfRule type="dataBar" id="{e2addf6e-34c4-435c-8189-21735616c8cf}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15733,7 +15730,7 @@
           <xm:sqref>K69:K79 K85:K99 K105:K119 K125:K139 K145:K159 K165:K179 K185:K188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7bca7cf8-8dd4-4737-8f28-2bd9a2fff72a}">
+          <x14:cfRule type="dataBar" id="{402779bc-f0f7-48b0-a209-51a683b3db86}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15745,7 +15742,7 @@
           <xm:sqref>Y69:Y79 Y85:Y99 Y105:Y122 Y125:Y141 Y145:Y160 Y165:Y179 Y185:Y188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cc68a2b7-4b14-4107-a2d4-fa62c6089904}">
+          <x14:cfRule type="dataBar" id="{88656c94-176a-4b1f-86cf-f53519eff006}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15754,7 +15751,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{476dd0d7-8df9-4e3f-9eb1-2176984aa8c8}">
+          <x14:cfRule type="dataBar" id="{325dce8d-515e-436e-9dc1-9c3b194ec07a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15766,7 +15763,7 @@
           <xm:sqref>AB69 AB89 AB109 AB129 AB149 AB169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4195e7ce-115d-4b6c-9733-bb54856a2382}">
+          <x14:cfRule type="dataBar" id="{eacf90e0-a5b6-48eb-a87d-7b64a49d5f07}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15775,7 +15772,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{51d3565d-fafa-4f13-b4e0-25507d1d4f29}">
+          <x14:cfRule type="dataBar" id="{ccabf301-0640-4884-bdc9-92714fdbd8f2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15785,7 +15782,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB122 AB125:AB141 AB145:AB160 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3593caf3-5d29-455c-9523-512d3cae2497}">
+          <x14:cfRule type="dataBar" id="{c5ef9107-581a-479e-8395-322f5bb70e80}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15797,7 +15794,7 @@
           <xm:sqref>AB69:AB79 AB85:AB99 AB105:AB119 AB125:AB139 AB145:AB159 AB165:AB179 AB185:AB188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fbf79121-fdb9-4889-ac2b-a6379a6d531d}">
+          <x14:cfRule type="dataBar" id="{f90cb22d-ea7a-4dbf-9092-503242a88888}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15806,7 +15803,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e3f44a6c-0207-4ba6-93f5-a92b74802171}">
+          <x14:cfRule type="dataBar" id="{73a1d383-7b26-444a-8dd5-85e97f8e47a9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15818,7 +15815,7 @@
           <xm:sqref>K80:K84 K100:K104 K120:K124 K140:K144 K160:K164 K180:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e48f17ca-c21f-44a1-b4ab-4ec9ae07c35b}">
+          <x14:cfRule type="dataBar" id="{2b3222c0-bb38-4dcf-941a-c3f9c3bafb4c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15830,7 +15827,7 @@
           <xm:sqref>Y80:Y84 Y100:Y104 Y120:Y124 Y140:Y144 Y160:Y164 Y180:Y184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e08a880f-8924-48ab-80b4-76ee4df0a25f}">
+          <x14:cfRule type="dataBar" id="{fc1a3a2b-2822-4730-8fbd-7cdf8e55ef60}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15839,7 +15836,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25e57e2f-5a16-4c86-ab38-ec670adce065}">
+          <x14:cfRule type="dataBar" id="{873f57c6-99c7-4ef3-a780-316edcbbf315}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15848,7 +15845,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{83a64b92-9305-47ca-b4a4-b7d3e582f154}">
+          <x14:cfRule type="dataBar" id="{1941e2d8-9f56-4654-97ee-f19df384e309}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15858,7 +15855,7 @@
           <xm:sqref>AB80:AB84 AB100:AB104 AB120:AB124 AB140:AB144 AB160:AB164 AB180:AB184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a971425e-24ea-4125-9f5e-5a98e4b2edc7}">
+          <x14:cfRule type="dataBar" id="{1d6eb9bf-dae9-4855-837d-b0872b4b71ab}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15867,7 +15864,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4df7c8ae-578e-45a0-ac53-39c0df692f16}">
+          <x14:cfRule type="dataBar" id="{34d4c11d-a0f9-4f23-a982-d230ce51a843}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15876,7 +15873,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b9cdbe98-fd73-49cd-83be-3fe88a6ed795}">
+          <x14:cfRule type="dataBar" id="{9bc1a219-9258-4dfa-9115-c76d05799ed4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15888,7 +15885,7 @@
           <xm:sqref>F189 F194 F199 F204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55056ae2-7f42-460f-ada0-e3a57d775680}">
+          <x14:cfRule type="dataBar" id="{40498ad4-c6f7-4c9c-9103-c0fb66bde84f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15897,7 +15894,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{81466f92-5534-496c-88dc-62a6d1d8b070}">
+          <x14:cfRule type="dataBar" id="{b119c34c-0b3c-4c1d-82d4-4c149339eefa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15918,12 +15915,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
